--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,58 +458,1558 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Test_Accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test_F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test_AUC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Params</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Test_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Test_RMSE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Test_MAE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Best_Params</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>59.93382573127747</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9895301128904705</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9997048406139315</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 49}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>101.0880675315857</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9934103815702056</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9997048406139315</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 10, 'n_estimators': 200}</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9871697425842285</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9866574217406261</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9805194805194806</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9745507805678763</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9870129870129871</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.597283363342285</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9907112896519678</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9805194805194806</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9745507805678763</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9870129870129871</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05744838714599609</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8632988425449154</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9025974025974026</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8757306007306007</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.991398212177433</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0549767017364502</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.872392295342498</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9025974025974026</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8757306007306007</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.991398212177433</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1190078258514404</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9845298973413629</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9998735031202564</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1286299228668213</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9868977307430697</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9998453927025356</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.184853553771973</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9778329373515132</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9920505871725384</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9999016135379771</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'C': 0.01, 'class_weight': None, 'max_iter': 2000, 'penalty': None, 'solver': 'lbfgs'}</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17.41702342033386</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9860832868623287</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9999578343734189</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.04170870780944824</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9159194082051126</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9220779220779221</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8969508086253368</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9880109068420757</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04834914207458496</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9177548235305235</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9220779220779221</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8969508086253368</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9880109068420757</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.224616765975952</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9893529482385016</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9824284292349985</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9996907854050711</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'max_features': 0.6, 'max_samples': 0.8, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.056440830230713</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9914820069145582</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9824284292349985</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9996907854050711</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'max_features': 0.6, 'max_samples': 0.8, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.293866395950317</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9871368975242844</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9824284292349985</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9980041603418226</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.374776363372803</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9911925468523709</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9997470062405128</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>29.8041353225708</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9991587138518518</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9995549535822634</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.4157303868736235</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2282322330336578</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>53.15427279472351</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9992837402469261</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9995451828539085</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.4202691667732273</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2274132467532568</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8800680637359619</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9988100135732582</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.9992728675816984</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.5313930479678594</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3064285714285715</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.528174877166748</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9989091594722449</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9992728675816984</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.5313930479678594</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3064285714285715</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1838645935058594</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9999313193305389</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.999951176558577</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.1376966291576827</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.076330175930234</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.2727642059326172</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9999407153367686</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.999951176558577</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1376966291576827</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.076330175930234</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0665891170501709</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9961400709277428</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9991937940340722</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.5595412624943363</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.4184629446750223</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.08024287223815918</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9978228952075805</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9991937940340722</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.5595412624943363</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.4184629446750223</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1051614284515381</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5.839703932729543e-09</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4.23403629040481e-09</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.07049655914306641</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.839703932729543e-09</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4.23403629040481e-09</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.348443269729614</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.02865719795227051</v>
+      </c>
+      <c r="E28" t="n">
         <v>0.9999999999876464</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
         <v>0.99999999998775</v>
       </c>
-      <c r="G2" t="n">
+      <c r="K28" t="n">
         <v>6.89727434653534e-05</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L28" t="n">
         <v>5.051934608765776e-05</v>
       </c>
-      <c r="I2" t="inlineStr">
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.03991985321044922</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.999999999988234</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
         <is>
           <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
         </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.99999999998775</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6.89727434653534e-05</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5.051934608765776e-05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.06925177574157715</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9999999999969686</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.5, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9999999999964098</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.733994582140021e-05</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2.734276452877381e-05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.09426283836364746</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9999999999968388</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.5, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.9999999999964098</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.733994582140021e-05</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.734276452877381e-05</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.796592235565186</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9995308080898969</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 3, 'min_samples_split': 2, 'n_estimators': 200}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9996614248307802</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.3626074032427155</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.217531223646855</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5.286661624908447</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9996176561182242</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 3, 'min_samples_split': 10, 'n_estimators': 200}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9997514131726544</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.3107049486552608</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.2144502144103884</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.851961374282837</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9993077551606934</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.9995703448167288</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.4084784432314476</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.252633484183968</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.683156490325928</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9994639056223656</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.9996531681509944</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.3670021430084903</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.2297141919817243</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7.689368009567261</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9985491167103056</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 3, 'n_estimators': 200, 'num_leaves': 31}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.9995224064768821</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.4306637610594572</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.3130241899402439</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7.992323637008667</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9991212652721163</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9995446518581431</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.4205144258328332</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2735053729299763</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.490334987640381</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9993661750125149</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9997201460968009</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.3296664859921038</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2273045995670993</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.339414834976196</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9994024065876171</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.9997201460968009</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.3296664859921038</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2273045995670993</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.620131969451904</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9999993011976304</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9999996436613721</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.01176360860315794</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.009252170390775166</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.929586410522461</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9999995124314008</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.9999996436613721</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.01176360860315794</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.009252170390775166</v>
       </c>
     </row>
   </sheetData>
@@ -522,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,58 +2054,1634 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Test_Accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test_F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test_AUC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Params</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Test_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Test_RMSE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Test_MAE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Best_Params</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>59.93382573127747</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9895301128904705</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9997048406139315</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 49}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>101.0880675315857</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9934103815702056</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9997048406139315</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 10, 'n_estimators': 200}</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9871697425842285</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9866574217406261</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9805194805194806</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9745507805678763</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9870129870129871</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.597283363342285</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9907112896519678</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9805194805194806</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9745507805678763</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9870129870129871</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05744838714599609</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8632988425449154</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9025974025974026</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8757306007306007</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.991398212177433</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0549767017364502</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.872392295342498</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9025974025974026</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8757306007306007</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.991398212177433</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1190078258514404</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9845298973413629</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9998735031202564</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1286299228668213</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9868977307430697</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9998453927025356</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.184853553771973</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9778329373515132</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9920505871725384</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9999016135379771</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'C': 0.01, 'class_weight': None, 'max_iter': 2000, 'penalty': None, 'solver': 'lbfgs'}</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17.41702342033386</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9860832868623287</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9999578343734189</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.04170870780944824</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9159194082051126</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9220779220779221</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8969508086253368</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9880109068420757</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04834914207458496</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9177548235305235</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9220779220779221</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8969508086253368</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9880109068420757</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 0.0001}</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.224616765975952</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9893529482385016</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9824284292349985</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9996907854050711</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'max_features': 0.6, 'max_samples': 0.8, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.056440830230713</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9914820069145582</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9824284292349985</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9996907854050711</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'max_features': 0.6, 'max_samples': 0.8, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.293866395950317</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9871368975242844</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9824284292349985</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9980041603418226</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.374776363372803</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9911925468523709</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9917649260714955</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9997470062405128</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CV_Folds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tuning_Time_sec</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Best_CV_Score</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Test_Accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test_F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test_AUC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Params</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Test_R2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Test_RMSE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Test_MAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.8041353225708</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9991587138518518</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9995549535822634</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.4157303868736235</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.2282322330336578</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>53.15427279472351</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9992837402469261</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9995451828539085</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4202691667732273</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2274132467532568</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8800680637359619</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9988100135732582</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9992728675816984</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5313930479678594</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3064285714285715</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.528174877166748</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9989091594722449</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9992728675816984</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5313930479678594</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3064285714285715</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1838645935058594</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9999313193305389</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.999951176558577</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1376966291576827</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.076330175930234</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2727642059326172</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9999407153367686</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.999951176558577</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1376966291576827</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.076330175930234</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0665891170501709</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9961400709277428</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9991937940340722</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.5595412624943363</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4184629446750223</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.08024287223815918</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9978228952075805</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9991937940340722</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5595412624943363</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4184629446750223</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1051614284515381</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.839703932729543e-09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.23403629040481e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.07049655914306641</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.839703932729543e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.23403629040481e-09</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.348443269729614</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.02865719795227051</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.9999999999876464</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>0.99999999998775</v>
       </c>
-      <c r="G2" t="n">
+      <c r="K12" t="n">
         <v>6.89727434653534e-05</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L12" t="n">
         <v>5.051934608765776e-05</v>
       </c>
-      <c r="I2" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03991985321044922</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.999999999988234</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
         </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.99999999998775</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.89727434653534e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.051934608765776e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.06925177574157715</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9999999999969686</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.5, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9999999999964098</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.733994582140021e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.734276452877381e-05</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.09426283836364746</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9999999999968388</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.5, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9999999999964098</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.733994582140021e-05</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.734276452877381e-05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.796592235565186</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9995308080898969</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 3, 'min_samples_split': 2, 'n_estimators': 200}</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9996614248307802</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.3626074032427155</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.217531223646855</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.286661624908447</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9996176561182242</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 3, 'min_samples_split': 10, 'n_estimators': 200}</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9997514131726544</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.3107049486552608</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2144502144103884</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.851961374282837</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9993077551606934</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9995703448167288</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.4084784432314476</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.252633484183968</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.683156490325928</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9994639056223656</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9996531681509944</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.3670021430084903</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2297141919817243</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7.689368009567261</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9985491167103056</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 3, 'n_estimators': 200, 'num_leaves': 31}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.9995224064768821</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.4306637610594572</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3130241899402439</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7.992323637008667</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9991212652721163</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9995446518581431</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.4205144258328332</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2735053729299763</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.490334987640381</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9993661750125149</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9997201460968009</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.3296664859921038</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2273045995670993</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.339414834976196</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9994024065876171</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9997201460968009</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.3296664859921038</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2273045995670993</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.620131969451904</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9999993011976304</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9999996436613721</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.01176360860315794</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.009252170390775166</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.929586410522461</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9999995124314008</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9999996436613721</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.01176360860315794</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.009252170390775166</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,30 +484,135 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.232657670974731</v>
+        <v>7.384719848632812</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9956186096202421</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9968511658570547</v>
       </c>
       <c r="G2" t="n">
-        <v>5.839703932729543e-09</v>
+        <v>9.985445827134786</v>
       </c>
       <c r="H2" t="n">
-        <v>4.23403629040481e-09</v>
+        <v>6.516757399697644</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.618981122970581</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.996369932630607</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9968511658570547</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9.985445827134786</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.516757399697644</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.586958169937134</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9966415254415318</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9968511658570547</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.985445827134786</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.516757399697644</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.590544462203979</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9967493472834448</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9968511658570547</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.985445827134786</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.516757399697644</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -522,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,30 +685,135 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.232657670974731</v>
+        <v>7.384719848632812</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9956186096202421</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9968511658570547</v>
       </c>
       <c r="G2" t="n">
-        <v>5.839703932729543e-09</v>
+        <v>9.985445827134786</v>
       </c>
       <c r="H2" t="n">
-        <v>4.23403629040481e-09</v>
+        <v>6.516757399697644</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.618981122970581</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.996369932630607</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9968511658570547</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9.985445827134786</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.516757399697644</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.586958169937134</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9966415254415318</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9968511658570547</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.985445827134786</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.516757399697644</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.590544462203979</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9967493472834448</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9968511658570547</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.985445827134786</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.516757399697644</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.384719848632812</v>
+        <v>4.127224206924438</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9956186096202421</v>
+        <v>0.9962548380768484</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G2" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H2" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.618981122970581</v>
+        <v>2.992775201797485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.996369932630607</v>
+        <v>0.9970077248654106</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G3" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H3" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>6.586958169937134</v>
+        <v>3.482832908630371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9966415254415318</v>
+        <v>0.9973717366034205</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G4" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H4" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -596,23 +596,23 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>6.590544462203979</v>
+        <v>3.67577338218689</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9967493472834448</v>
+        <v>0.9974269041414209</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G5" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H5" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -692,23 +692,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.384719848632812</v>
+        <v>4.127224206924438</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9956186096202421</v>
+        <v>0.9962548380768484</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G2" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H2" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -727,23 +727,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.618981122970581</v>
+        <v>2.992775201797485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.996369932630607</v>
+        <v>0.9970077248654106</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G3" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H3" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -762,23 +762,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>6.586958169937134</v>
+        <v>3.482832908630371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9966415254415318</v>
+        <v>0.9973717366034205</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G4" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H4" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -797,23 +797,23 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>6.590544462203979</v>
+        <v>3.67577338218689</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9967493472834448</v>
+        <v>0.9974269041414209</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G5" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H5" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,30 +484,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.127224206924438</v>
+        <v>33.1019082069397</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962548380768484</v>
+        <v>0.9918638859927142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9922241522513416</v>
       </c>
       <c r="G2" t="n">
-        <v>8.956775966344631</v>
+        <v>1.737732761114964</v>
       </c>
       <c r="H2" t="n">
-        <v>5.924799097085533</v>
+        <v>1.168828255120888</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -519,30 +519,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.992775201797485</v>
+        <v>56.16065907478333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9970077248654106</v>
+        <v>0.9922025775317673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.992189257958039</v>
       </c>
       <c r="G3" t="n">
-        <v>8.956775966344631</v>
+        <v>1.741627454233083</v>
       </c>
       <c r="H3" t="n">
-        <v>5.924799097085533</v>
+        <v>1.170346040239261</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -554,30 +554,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3.482832908630371</v>
+        <v>1.138504981994629</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9973717366034205</v>
+        <v>0.9903820314976214</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G4" t="n">
-        <v>8.956775966344631</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H4" t="n">
-        <v>5.924799097085533</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -589,30 +589,730 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.771363496780396</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9910838952932458</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9900974153757823</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.961026199042346</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.278002032101249</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.398122549057007</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9907215425595718</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9938816684425166</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.541436429431279</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9433131263880609</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.773450374603271</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.994952709138001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9938816684425166</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.541436429431279</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9433131263880609</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>KNN</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.67577338218689</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9974269041414209</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9974665152819624</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.956775966344631</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.924799097085533</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1729857921600342</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9500806472555414</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9563414289885007</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.117597323689839</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.150367965367966</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1327650547027588</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9586722896604414</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9563414289885007</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.117597323689839</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.150367965367966</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1536533832550049</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9095295397201048</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9134071819812636</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.798959174155399</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.192639414719826</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'solver': 'svd'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.274498462677002</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9087497339209655</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9134071819812641</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.79895917415538</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.192639414719824</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06342554092407227</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9095325244128653</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9134070331993437</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.798964155976802</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.192993498939789</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.08275389671325684</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9087532778197251</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9134070331993437</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.798964155976802</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.192993498939789</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1402401924133301</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9095325244128653</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9134070331993437</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.798964155976802</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.192993498939789</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'l1_ratio': 1.0, 'selection': 'random'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1987051963806152</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9087558070992785</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9133757607379048</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.800011189699457</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.193244794799755</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.7, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.090390920639038</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9964407905175324</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9981552400435884</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.846406609551614</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5817881338169909</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.720860719680786</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9975889547112533</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9981552400435884</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.846406609551614</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5817881338169909</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.283513784408569</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9965440319277402</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9979411295019519</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8941772782146106</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.596932118403447</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.65857720375061</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9974903523734235</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9983181512040402</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8081697467762399</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5709631694446908</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>33.34668922424316</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9957603155974105</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9972056385643899</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.041718565298485</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7294976117107828</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>39.18174290657043</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9965907516726771</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9972056385643899</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.041718565298485</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7294976117107828</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.937947750091553</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9916672509648135</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9926310374474091</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.691656918987547</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.079954545454545</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.616126298904419</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.991944820007945</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9924359336701404</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.713905130730069</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.105564935064935</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.385154962539673</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9919591707630674</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9931963895337861</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.625469537425023</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.102047839255723</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.595376253128052</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9922542316820335</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9931963895337861</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.625469537425023</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.102047839255723</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -627,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,30 +1385,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.127224206924438</v>
+        <v>33.1019082069397</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962548380768484</v>
+        <v>0.9918638859927142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9922241522513416</v>
       </c>
       <c r="G2" t="n">
-        <v>8.956775966344631</v>
+        <v>1.737732761114964</v>
       </c>
       <c r="H2" t="n">
-        <v>5.924799097085533</v>
+        <v>1.168828255120888</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -720,30 +1420,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.992775201797485</v>
+        <v>56.16065907478333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9970077248654106</v>
+        <v>0.9922025775317673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.992189257958039</v>
       </c>
       <c r="G3" t="n">
-        <v>8.956775966344631</v>
+        <v>1.741627454233083</v>
       </c>
       <c r="H3" t="n">
-        <v>5.924799097085533</v>
+        <v>1.170346040239261</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
@@ -755,30 +1455,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3.482832908630371</v>
+        <v>1.138504981994629</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9973717366034205</v>
+        <v>0.9903820314976214</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G4" t="n">
-        <v>8.956775966344631</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H4" t="n">
-        <v>5.924799097085533</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -790,30 +1490,730 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.771363496780396</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9910838952932458</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9900974153757823</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.961026199042346</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.278002032101249</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.398122549057007</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9907215425595718</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9938816684425166</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.541436429431279</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9433131263880609</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.773450374603271</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.994952709138001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9938816684425166</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.541436429431279</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9433131263880609</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>KNN</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.67577338218689</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9974269041414209</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9974665152819624</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.956775966344631</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.924799097085533</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1729857921600342</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9500806472555414</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9563414289885007</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.117597323689839</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.150367965367966</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1327650547027588</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9586722896604414</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9563414289885007</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.117597323689839</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.150367965367966</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1536533832550049</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9095295397201048</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9134071819812636</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.798959174155399</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.192639414719826</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'solver': 'svd'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.274498462677002</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9087497339209655</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9134071819812641</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.79895917415538</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.192639414719824</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06342554092407227</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9095325244128653</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9134070331993437</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.798964155976802</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.192993498939789</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.08275389671325684</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9087532778197251</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9134070331993437</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.798964155976802</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.192993498939789</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1402401924133301</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9095325244128653</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9134070331993437</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.798964155976802</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.192993498939789</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'l1_ratio': 1.0, 'selection': 'random'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1987051963806152</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9087558070992785</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9133757607379048</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.800011189699457</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.193244794799755</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'l1_ratio': 0.7, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.090390920639038</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9964407905175324</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9981552400435884</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.846406609551614</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5817881338169909</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.720860719680786</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9975889547112533</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9981552400435884</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.846406609551614</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5817881338169909</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.283513784408569</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9965440319277402</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9979411295019519</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8941772782146106</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.596932118403447</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.65857720375061</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9974903523734235</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9983181512040402</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8081697467762399</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5709631694446908</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>33.34668922424316</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9957603155974105</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9972056385643899</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.041718565298485</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7294976117107828</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>39.18174290657043</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9965907516726771</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9972056385643899</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.041718565298485</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7294976117107828</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.937947750091553</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9916672509648135</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9926310374474091</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.691656918987547</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.079954545454545</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.616126298904419</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.991944820007945</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9924359336701404</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.713905130730069</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.105564935064935</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.385154962539673</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9919591707630674</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9931963895337861</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.625469537425023</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.102047839255723</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.595376253128052</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9922542316820335</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9931963895337861</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.625469537425023</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.102047839255723</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,17 +457,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_R2</t>
+          <t>Test_Accuracy</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_RMSE</t>
+          <t>Test_F1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_MAE</t>
+          <t>Test_AUC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,30 +491,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>33.1019082069397</v>
+        <v>39.05030608177185</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9918638859927142</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9922241522513416</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>1.737732761114964</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168828255120888</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,30 +526,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>56.16065907478333</v>
+        <v>61.92200469970703</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9922025775317673</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.992189257958039</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>1.741627454233083</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>1.170346040239261</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,30 +561,30 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.138504981994629</v>
+        <v>0.5624017715454102</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9903820314976214</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G4" t="n">
-        <v>1.961026199042346</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H4" t="n">
-        <v>1.278002032101249</v>
+        <v>0.99375</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,100 +596,100 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.771363496780396</v>
+        <v>0.822310209274292</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9910838952932458</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G5" t="n">
-        <v>1.961026199042346</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H5" t="n">
-        <v>1.278002032101249</v>
+        <v>0.99375</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1.398122549057007</v>
+        <v>0.03340435028076172</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9907215425595718</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G6" t="n">
-        <v>1.541436429431279</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9433131263880609</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.773450374603271</v>
+        <v>0.03034567832946777</v>
       </c>
       <c r="E7" t="n">
-        <v>0.994952709138001</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G7" t="n">
-        <v>1.541436429431279</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9433131263880609</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,30 +701,30 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1729857921600342</v>
+        <v>0.1014575958251953</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9500806472555414</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G8" t="n">
-        <v>4.117597323689839</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H8" t="n">
-        <v>3.150367965367966</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,581 +736,301 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1327650547027588</v>
+        <v>0.0909726619720459</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9586722896604414</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G9" t="n">
-        <v>4.117597323689839</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H9" t="n">
-        <v>3.150367965367966</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1536533832550049</v>
+        <v>0.8491902351379395</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9095295397201048</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9134071819812636</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G10" t="n">
-        <v>5.798959174155399</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H10" t="n">
-        <v>4.192639414719826</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'solver': 'svd'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.274498462677002</v>
+        <v>1.251380681991577</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9087497339209655</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9134071819812641</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G11" t="n">
-        <v>5.79895917415538</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H11" t="n">
-        <v>4.192639414719824</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06342554092407227</v>
+        <v>0.02515745162963867</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G12" t="n">
-        <v>5.798964155976802</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H12" t="n">
-        <v>4.192993498939789</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08275389671325684</v>
+        <v>0.0369257926940918</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9087532778197251</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G13" t="n">
-        <v>5.798964155976802</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H13" t="n">
-        <v>4.192993498939789</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1402401924133301</v>
+        <v>0.9002141952514648</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G14" t="n">
-        <v>5.798964155976802</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H14" t="n">
-        <v>4.192993498939789</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 1.0, 'selection': 'random'}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1987051963806152</v>
+        <v>1.457194566726685</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9087558070992785</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9133757607379048</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G15" t="n">
-        <v>5.800011189699457</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H15" t="n">
-        <v>4.193244794799755</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.7, 'selection': 'cyclic'}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>3.090390920639038</v>
+        <v>0.7807161808013916</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9964407905175324</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G16" t="n">
-        <v>0.846406609551614</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5817881338169909</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>4.720860719680786</v>
+        <v>0.9821460247039795</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9975889547112533</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G17" t="n">
-        <v>0.846406609551614</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5817881338169909</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.283513784408569</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.9965440319277402</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.9979411295019519</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.8941772782146106</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.596932118403447</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.65857720375061</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.9974903523734235</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.9983181512040402</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.8081697467762399</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5709631694446908</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>33.34668922424316</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.9957603155974105</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.9972056385643899</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.041718565298485</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.7294976117107828</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>39.18174290657043</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.9965907516726771</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9972056385643899</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.041718565298485</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.7294976117107828</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.937947750091553</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.9916672509648135</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.9926310374474091</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.691656918987547</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.079954545454545</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.616126298904419</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.991944820007945</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9924359336701404</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.713905130730069</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.105564935064935</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.385154962539673</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.9919591707630674</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.9931963895337861</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.625469537425023</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.102047839255723</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.595376253128052</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.9922542316820335</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.9931963895337861</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.625469537425023</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.102047839255723</v>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>
@@ -1327,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1358,17 +1078,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_R2</t>
+          <t>Test_Accuracy</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_RMSE</t>
+          <t>Test_F1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_MAE</t>
+          <t>Test_AUC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1380,7 +1100,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1392,30 +1112,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>33.1019082069397</v>
+        <v>39.05030608177185</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9918638859927142</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9922241522513416</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>1.737732761114964</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168828255120888</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1427,30 +1147,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>56.16065907478333</v>
+        <v>61.92200469970703</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9922025775317673</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.992189257958039</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>1.741627454233083</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>1.170346040239261</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1462,30 +1182,30 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.138504981994629</v>
+        <v>0.5624017715454102</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9903820314976214</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G4" t="n">
-        <v>1.961026199042346</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H4" t="n">
-        <v>1.278002032101249</v>
+        <v>0.99375</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1497,100 +1217,100 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.771363496780396</v>
+        <v>0.822310209274292</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9910838952932458</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G5" t="n">
-        <v>1.961026199042346</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H5" t="n">
-        <v>1.278002032101249</v>
+        <v>0.99375</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1.398122549057007</v>
+        <v>0.03340435028076172</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9907215425595718</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G6" t="n">
-        <v>1.541436429431279</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9433131263880609</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.773450374603271</v>
+        <v>0.03034567832946777</v>
       </c>
       <c r="E7" t="n">
-        <v>0.994952709138001</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9938816684425166</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G7" t="n">
-        <v>1.541436429431279</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9433131263880609</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1602,30 +1322,30 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1729857921600342</v>
+        <v>0.1014575958251953</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9500806472555414</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G8" t="n">
-        <v>4.117597323689839</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H8" t="n">
-        <v>3.150367965367966</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1637,581 +1357,301 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1327650547027588</v>
+        <v>0.0909726619720459</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9586722896604414</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G9" t="n">
-        <v>4.117597323689839</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H9" t="n">
-        <v>3.150367965367966</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1536533832550049</v>
+        <v>0.8491902351379395</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9095295397201048</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9134071819812636</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G10" t="n">
-        <v>5.798959174155399</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H10" t="n">
-        <v>4.192639414719826</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'solver': 'svd'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.274498462677002</v>
+        <v>1.251380681991577</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9087497339209655</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9134071819812641</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G11" t="n">
-        <v>5.79895917415538</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H11" t="n">
-        <v>4.192639414719824</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'solver': 'auto'}</t>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06342554092407227</v>
+        <v>0.02515745162963867</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G12" t="n">
-        <v>5.798964155976802</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H12" t="n">
-        <v>4.192993498939789</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08275389671325684</v>
+        <v>0.0369257926940918</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9087532778197251</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G13" t="n">
-        <v>5.798964155976802</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H13" t="n">
-        <v>4.192993498939789</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1402401924133301</v>
+        <v>0.9002141952514648</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G14" t="n">
-        <v>5.798964155976802</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H14" t="n">
-        <v>4.192993498939789</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 1.0, 'selection': 'random'}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1987051963806152</v>
+        <v>1.457194566726685</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9087558070992785</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9133757607379048</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G15" t="n">
-        <v>5.800011189699457</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H15" t="n">
-        <v>4.193244794799755</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'l1_ratio': 0.7, 'selection': 'cyclic'}</t>
+          <t>{'max_features': 0.6, 'max_samples': 0.6, 'n_estimators': 25}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>3.090390920639038</v>
+        <v>0.7807161808013916</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9964407905175324</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G16" t="n">
-        <v>0.846406609551614</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5817881338169909</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>4.720860719680786</v>
+        <v>0.9821460247039795</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9975889547112533</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9981552400435884</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G17" t="n">
-        <v>0.846406609551614</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5817881338169909</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.283513784408569</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.9965440319277402</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.9979411295019519</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.8941772782146106</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.596932118403447</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.65857720375061</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.9974903523734235</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.9983181512040402</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.8081697467762399</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5709631694446908</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>33.34668922424316</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.9957603155974105</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.9972056385643899</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.041718565298485</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.7294976117107828</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>39.18174290657043</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.9965907516726771</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9972056385643899</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.041718565298485</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.7294976117107828</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.937947750091553</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.9916672509648135</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.9926310374474091</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.691656918987547</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.079954545454545</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.616126298904419</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.991944820007945</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9924359336701404</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.713905130730069</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.105564935064935</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.385154962539673</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.9919591707630674</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.9931963895337861</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.625469537425023</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.102047839255723</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.595376253128052</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.9922542316820335</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.9931963895337861</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.625469537425023</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.102047839255723</v>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,17 +457,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_R2</t>
+          <t>Test_Accuracy</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_RMSE</t>
+          <t>Test_F1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_MAE</t>
+          <t>Test_AUC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -479,280 +479,840 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>276.8292608261108</v>
+        <v>238.5478436946869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9602943270145412</v>
+        <v>0.9284964745698829</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9621496998976331</v>
+        <v>0.9487917146144994</v>
       </c>
       <c r="G2" t="n">
-        <v>34.62001331527443</v>
+        <v>0.9299714828079678</v>
       </c>
       <c r="H2" t="n">
-        <v>21.29884542120722</v>
+        <v>0.9855738312016764</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_samples_split': 5, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>354.9995188713074</v>
+        <v>542.2999491691589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9607920144022914</v>
+        <v>0.9297969871967362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9609852594920165</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="G3" t="n">
-        <v>35.14851072763138</v>
+        <v>0.9307583200797884</v>
       </c>
       <c r="H3" t="n">
-        <v>21.2876999547741</v>
+        <v>0.9854701839005708</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>20.94777989387512</v>
+        <v>1223.890587806702</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9599743843078613</v>
+        <v>0.9320954548153093</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9615880846977234</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="G4" t="n">
-        <v>34.87590026855469</v>
+        <v>0.9307583200797884</v>
       </c>
       <c r="H4" t="n">
-        <v>21.44150924682617</v>
+        <v>0.9854701839005708</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>24.31270527839661</v>
+        <v>1.825597286224365</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9605928301811218</v>
+        <v>0.9085511310346576</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9602247476577759</v>
+        <v>0.9246260069044879</v>
       </c>
       <c r="G5" t="n">
-        <v>35.48942565917969</v>
+        <v>0.8979170281613919</v>
       </c>
       <c r="H5" t="n">
-        <v>21.94902038574219</v>
+        <v>0.9514865145603006</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>62.80479264259338</v>
+        <v>4.178443670272827</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9580611716975916</v>
+        <v>0.9056173787944439</v>
       </c>
       <c r="F6" t="n">
-        <v>0.961021482177699</v>
+        <v>0.9286536248561565</v>
       </c>
       <c r="G6" t="n">
-        <v>35.13219036906995</v>
+        <v>0.9023524720893141</v>
       </c>
       <c r="H6" t="n">
-        <v>22.11323101640784</v>
+        <v>0.9010477635667318</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>80.48120641708374</v>
+        <v>6.760910749435425</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9591194549184205</v>
+        <v>0.9122842474999594</v>
       </c>
       <c r="F7" t="n">
-        <v>0.960585615565733</v>
+        <v>0.9346950517836594</v>
       </c>
       <c r="G7" t="n">
-        <v>35.32807234600131</v>
+        <v>0.9108030306884048</v>
       </c>
       <c r="H7" t="n">
-        <v>22.57109046746683</v>
+        <v>0.9103033094876798</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 50}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>773.1986422538757</v>
+        <v>23.9944543838501</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9503921749831643</v>
+        <v>0.8260553486408432</v>
       </c>
       <c r="F8" t="n">
-        <v>0.949013231773535</v>
+        <v>0.8682393555811277</v>
       </c>
       <c r="G8" t="n">
-        <v>40.1810526070136</v>
+        <v>0.8355376548696518</v>
       </c>
       <c r="H8" t="n">
-        <v>23.79068469505178</v>
+        <v>0.9440887166702797</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>28.06601738929749</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8301691337493897</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8682393555811277</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8355376548696518</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9440887166702797</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>39.27588891983032</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8343505263916757</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8682393555811277</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8355376548696518</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9440887166702797</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.018621206283569</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8013286401307914</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8765822784810127</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8213289652983488</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.91744187621938</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.456517219543457</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.81032050938439</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8765822784810127</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8213289652983488</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.91744187621938</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.075722217559814</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8106837161192055</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8760069044879172</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8238850693483192</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.918110502926512</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>84.12868881225586</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7319187167195951</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8299769850402762</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7391667698284974</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8593011597658791</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>220.4796578884125</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7328853331272454</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8288262370540852</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7371274467075601</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8584015282896162</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'C': 1, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>361.8796882629395</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7330116584649267</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.830264672036824</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.739472389794956</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8594352915673099</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2130286693572998</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.758522079737817</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8201956271576525</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7654782974318119</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8779147698533132</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1723580360412598</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7588098200722057</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8201956271576525</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7654782974318119</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8779147698533132</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2233843803405762</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7592605161401397</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.8201956271576525</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7654782974318119</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8779147698533132</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Bagging</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>20</v>
-      </c>
-      <c r="D9" t="n">
-        <v>115.5476741790771</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.9497617034790053</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.949013231773535</v>
-      </c>
-      <c r="G9" t="n">
-        <v>40.1810526070136</v>
-      </c>
-      <c r="H9" t="n">
-        <v>23.79068469505178</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>15747.45786547661</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9280699341723085</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.950517836593786</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.932054070173397</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9845430034684587</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 50}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>18.41933584213257</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.928876610929035</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9485040276179517</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9296640638468039</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9831533618758581</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 25}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>32.46850252151489</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9322375683739018</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9508055235903338</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9329165872415834</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.9847139424813932</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>44.7150092124939</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9131605579577853</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.939873417721519</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9169917656074629</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9807870872172846</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>61.17642974853516</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9193219807675821</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9413118527042578</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9190787698855583</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9801950104776356</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>137.197586774826</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9202278598090171</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.939873417721519</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9169917656074629</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.9807870872172846</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -767,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,17 +1358,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_R2</t>
+          <t>Test_Accuracy</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_RMSE</t>
+          <t>Test_F1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_MAE</t>
+          <t>Test_AUC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -820,280 +1380,840 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>276.8292608261108</v>
+        <v>238.5478436946869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9602943270145412</v>
+        <v>0.9284964745698829</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9621496998976331</v>
+        <v>0.9487917146144994</v>
       </c>
       <c r="G2" t="n">
-        <v>34.62001331527443</v>
+        <v>0.9299714828079678</v>
       </c>
       <c r="H2" t="n">
-        <v>21.29884542120722</v>
+        <v>0.9855738312016764</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_samples_split': 5, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>354.9995188713074</v>
+        <v>542.2999491691589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9607920144022914</v>
+        <v>0.9297969871967362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9609852594920165</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="G3" t="n">
-        <v>35.14851072763138</v>
+        <v>0.9307583200797884</v>
       </c>
       <c r="H3" t="n">
-        <v>21.2876999547741</v>
+        <v>0.9854701839005708</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>20.94777989387512</v>
+        <v>1223.890587806702</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9599743843078613</v>
+        <v>0.9320954548153093</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9615880846977234</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="G4" t="n">
-        <v>34.87590026855469</v>
+        <v>0.9307583200797884</v>
       </c>
       <c r="H4" t="n">
-        <v>21.44150924682617</v>
+        <v>0.9854701839005708</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>24.31270527839661</v>
+        <v>1.825597286224365</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9605928301811218</v>
+        <v>0.9085511310346576</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9602247476577759</v>
+        <v>0.9246260069044879</v>
       </c>
       <c r="G5" t="n">
-        <v>35.48942565917969</v>
+        <v>0.8979170281613919</v>
       </c>
       <c r="H5" t="n">
-        <v>21.94902038574219</v>
+        <v>0.9514865145603006</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'min_child_weight': 1, 'n_estimators': 200}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>62.80479264259338</v>
+        <v>4.178443670272827</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9580611716975916</v>
+        <v>0.9056173787944439</v>
       </c>
       <c r="F6" t="n">
-        <v>0.961021482177699</v>
+        <v>0.9286536248561565</v>
       </c>
       <c r="G6" t="n">
-        <v>35.13219036906995</v>
+        <v>0.9023524720893141</v>
       </c>
       <c r="H6" t="n">
-        <v>22.11323101640784</v>
+        <v>0.9010477635667318</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>80.48120641708374</v>
+        <v>6.760910749435425</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9591194549184205</v>
+        <v>0.9122842474999594</v>
       </c>
       <c r="F7" t="n">
-        <v>0.960585615565733</v>
+        <v>0.9346950517836594</v>
       </c>
       <c r="G7" t="n">
-        <v>35.32807234600131</v>
+        <v>0.9108030306884048</v>
       </c>
       <c r="H7" t="n">
-        <v>22.57109046746683</v>
+        <v>0.9103033094876798</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 50}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>773.1986422538757</v>
+        <v>23.9944543838501</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9503921749831643</v>
+        <v>0.8260553486408432</v>
       </c>
       <c r="F8" t="n">
-        <v>0.949013231773535</v>
+        <v>0.8682393555811277</v>
       </c>
       <c r="G8" t="n">
-        <v>40.1810526070136</v>
+        <v>0.8355376548696518</v>
       </c>
       <c r="H8" t="n">
-        <v>23.79068469505178</v>
+        <v>0.9440887166702797</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>28.06601738929749</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8301691337493897</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8682393555811277</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8355376548696518</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9440887166702797</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>39.27588891983032</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8343505263916757</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8682393555811277</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8355376548696518</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9440887166702797</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.018621206283569</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8013286401307914</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8765822784810127</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8213289652983488</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.91744187621938</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.456517219543457</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.81032050938439</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8765822784810127</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8213289652983488</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.91744187621938</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.075722217559814</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8106837161192055</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8760069044879172</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8238850693483192</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.918110502926512</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>84.12868881225586</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7319187167195951</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8299769850402762</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7391667698284974</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8593011597658791</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>220.4796578884125</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7328853331272454</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8288262370540852</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7371274467075601</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8584015282896162</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'C': 1, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>361.8796882629395</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7330116584649267</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.830264672036824</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.739472389794956</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8594352915673099</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2130286693572998</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.758522079737817</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8201956271576525</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7654782974318119</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8779147698533132</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1723580360412598</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7588098200722057</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8201956271576525</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7654782974318119</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8779147698533132</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2233843803405762</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7592605161401397</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.8201956271576525</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7654782974318119</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8779147698533132</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Bagging</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>20</v>
-      </c>
-      <c r="D9" t="n">
-        <v>115.5476741790771</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.9497617034790053</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.949013231773535</v>
-      </c>
-      <c r="G9" t="n">
-        <v>40.1810526070136</v>
-      </c>
-      <c r="H9" t="n">
-        <v>23.79068469505178</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>15747.45786547661</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9280699341723085</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.950517836593786</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.932054070173397</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9845430034684587</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 50}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>18.41933584213257</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.928876610929035</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9485040276179517</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9296640638468039</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9831533618758581</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 25}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>32.46850252151489</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9322375683739018</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9508055235903338</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9329165872415834</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.9847139424813932</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>44.7150092124939</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9131605579577853</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.939873417721519</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9169917656074629</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9807870872172846</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>61.17642974853516</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9193219807675821</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9413118527042578</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9190787698855583</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9801950104776356</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>137.197586774826</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9202278598090171</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.939873417721519</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9169917656074629</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.9807870872172846</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,17 +457,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_Accuracy</t>
+          <t>Test_R2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_F1</t>
+          <t>Test_RMSE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_AUC</t>
+          <t>Test_MAE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,30 +491,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>238.5478436946869</v>
+        <v>20.57877922058105</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9284964745698829</v>
+        <v>0.9918638859927142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9487917146144994</v>
+        <v>0.9922241522513416</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9299714828079678</v>
+        <v>1.737732761114964</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9855738312016764</v>
+        <v>1.168828255120888</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,65 +526,65 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>542.2999491691589</v>
+        <v>30.65591430664062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9297969871967362</v>
+        <v>0.9922025775317673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9493670886075949</v>
+        <v>0.992189257958039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9307583200797884</v>
+        <v>1.741627454233083</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854701839005708</v>
+        <v>1.170346040239261</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1223.890587806702</v>
+        <v>0.7613425254821777</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9320954548153093</v>
+        <v>0.9903820314976214</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9493670886075949</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9307583200797884</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9854701839005708</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,593 +593,593 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.825597286224365</v>
+        <v>1.245614767074585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9085511310346576</v>
+        <v>0.9910838952932458</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9246260069044879</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8979170281613919</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9514865145603006</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4.178443670272827</v>
+        <v>0.7682609558105469</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9056173787944439</v>
+        <v>0.9907215425595718</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9286536248561565</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9023524720893141</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9010477635667318</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>6.760910749435425</v>
+        <v>1.033361673355103</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9122842474999594</v>
+        <v>0.994952709138001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9346950517836594</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9108030306884048</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9103033094876798</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>23.9944543838501</v>
+        <v>0.1228775978088379</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8260553486408432</v>
+        <v>0.9500806472555414</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8682393555811277</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8355376548696518</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9440887166702797</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06601738929749</v>
+        <v>0.08171677589416504</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8301691337493897</v>
+        <v>0.9586722896604414</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8682393555811277</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8355376548696518</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9440887166702797</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>39.27588891983032</v>
+        <v>0.1468422412872314</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8343505263916757</v>
+        <v>0.9095323921356325</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8682393555811277</v>
+        <v>0.913391387078698</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8355376548696518</v>
+        <v>5.799488027591681</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9440887166702797</v>
+        <v>4.192952527344984</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'alpha': 0.001, 'solver': 'svd'}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3.018621206283569</v>
+        <v>0.2012887001037598</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.9087546108334023</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9133913870786986</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8213289652983488</v>
+        <v>5.799488027591662</v>
       </c>
       <c r="H11" t="n">
-        <v>0.91744187621938</v>
+        <v>4.192952527344982</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'alpha': 0.001, 'solver': 'auto'}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3.456517219543457</v>
+        <v>0.1129672527313232</v>
       </c>
       <c r="E12" t="n">
-        <v>0.81032050938439</v>
+        <v>0.9095174369097344</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8213289652983488</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H12" t="n">
-        <v>0.91744187621938</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>4.075722217559814</v>
+        <v>0.0507209300994873</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8106837161192055</v>
+        <v>0.9087447139966063</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8760069044879172</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8238850693483192</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H13" t="n">
-        <v>0.918110502926512</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>84.12868881225586</v>
+        <v>0.09876132011413574</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7319187167195951</v>
+        <v>0.9095174369097344</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8299769850402762</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7391667698284974</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8593011597658791</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>220.4796578884125</v>
+        <v>0.1238057613372803</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7328853331272454</v>
+        <v>0.9087447139966063</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8288262370540852</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7371274467075601</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8584015282896162</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'C': 1, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>361.8796882629395</v>
+        <v>1.929407596588135</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7330116584649267</v>
+        <v>0.9964407905175324</v>
       </c>
       <c r="F16" t="n">
-        <v>0.830264672036824</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G16" t="n">
-        <v>0.739472389794956</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8594352915673099</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2130286693572998</v>
+        <v>3.156977415084839</v>
       </c>
       <c r="E17" t="n">
-        <v>0.758522079737817</v>
+        <v>0.9975889547112533</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1723580360412598</v>
+        <v>3.335872411727905</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7588098200722057</v>
+        <v>0.9965440319277402</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.9979411295019519</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.8941772782146106</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.596932118403447</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2233843803405762</v>
+        <v>1.281316995620728</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7592605161401397</v>
+        <v>0.9974903523734235</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.9983181512040402</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.8081697467762399</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.5709631694446908</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>15747.45786547661</v>
+        <v>7.138336181640625</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9280699341723085</v>
+        <v>0.9957603155974105</v>
       </c>
       <c r="F20" t="n">
-        <v>0.950517836593786</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G20" t="n">
-        <v>0.932054070173397</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9845430034684587</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 50}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>18.41933584213257</v>
+        <v>6.981253623962402</v>
       </c>
       <c r="E21" t="n">
-        <v>0.928876610929035</v>
+        <v>0.9965907516726771</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9485040276179517</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9296640638468039</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9831533618758581</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 25}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1188,68 +1188,68 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>32.46850252151489</v>
+        <v>1.29323148727417</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9322375683739018</v>
+        <v>0.9916672509648135</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9508055235903338</v>
+        <v>0.9926310374474091</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9329165872415834</v>
+        <v>1.691656918987547</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9847139424813932</v>
+        <v>1.079954545454545</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>44.7150092124939</v>
+        <v>1.950638294219971</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9131605579577853</v>
+        <v>0.991944820007945</v>
       </c>
       <c r="F23" t="n">
-        <v>0.939873417721519</v>
+        <v>0.9924359336701404</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9169917656074629</v>
+        <v>1.713905130730069</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9807870872172846</v>
+        <v>1.105564935064935</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1258,33 +1258,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>61.17642974853516</v>
+        <v>1.393115043640137</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9193219807675821</v>
+        <v>0.9919591707630674</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9413118527042578</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9190787698855583</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9801950104776356</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>137.197586774826</v>
+        <v>1.58259129524231</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9202278598090171</v>
+        <v>0.9922542316820335</v>
       </c>
       <c r="F25" t="n">
-        <v>0.939873417721519</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9169917656074629</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9807870872172846</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1358,17 +1358,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_Accuracy</t>
+          <t>Test_R2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_F1</t>
+          <t>Test_RMSE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_AUC</t>
+          <t>Test_MAE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1392,30 +1392,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>238.5478436946869</v>
+        <v>20.57877922058105</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9284964745698829</v>
+        <v>0.9918638859927142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9487917146144994</v>
+        <v>0.9922241522513416</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9299714828079678</v>
+        <v>1.737732761114964</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9855738312016764</v>
+        <v>1.168828255120888</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1427,65 +1427,65 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>542.2999491691589</v>
+        <v>30.65591430664062</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9297969871967362</v>
+        <v>0.9922025775317673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9493670886075949</v>
+        <v>0.992189257958039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9307583200797884</v>
+        <v>1.741627454233083</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854701839005708</v>
+        <v>1.170346040239261</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'max_depth': 7, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1223.890587806702</v>
+        <v>0.7613425254821777</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9320954548153093</v>
+        <v>0.9903820314976214</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9493670886075949</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9307583200797884</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9854701839005708</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1494,593 +1494,593 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.825597286224365</v>
+        <v>1.245614767074585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9085511310346576</v>
+        <v>0.9910838952932458</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9246260069044879</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8979170281613919</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9514865145603006</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4.178443670272827</v>
+        <v>0.7682609558105469</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9056173787944439</v>
+        <v>0.9907215425595718</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9286536248561565</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9023524720893141</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9010477635667318</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>6.760910749435425</v>
+        <v>1.033361673355103</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9122842474999594</v>
+        <v>0.994952709138001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9346950517836594</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9108030306884048</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9103033094876798</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'C': 500, 'epsilon': 0.01, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>23.9944543838501</v>
+        <v>0.1228775978088379</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8260553486408432</v>
+        <v>0.9500806472555414</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8682393555811277</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8355376548696518</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9440887166702797</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06601738929749</v>
+        <v>0.08171677589416504</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8301691337493897</v>
+        <v>0.9586722896604414</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8682393555811277</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8355376548696518</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9440887166702797</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>39.27588891983032</v>
+        <v>0.1468422412872314</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8343505263916757</v>
+        <v>0.9095323921356325</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8682393555811277</v>
+        <v>0.913391387078698</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8355376548696518</v>
+        <v>5.799488027591681</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9440887166702797</v>
+        <v>4.192952527344984</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'alpha': 0.001, 'solver': 'svd'}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3.018621206283569</v>
+        <v>0.2012887001037598</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.9087546108334023</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9133913870786986</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8213289652983488</v>
+        <v>5.799488027591662</v>
       </c>
       <c r="H11" t="n">
-        <v>0.91744187621938</v>
+        <v>4.192952527344982</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'alpha': 0.001, 'solver': 'auto'}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3.456517219543457</v>
+        <v>0.1129672527313232</v>
       </c>
       <c r="E12" t="n">
-        <v>0.81032050938439</v>
+        <v>0.9095174369097344</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8213289652983488</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H12" t="n">
-        <v>0.91744187621938</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>4.075722217559814</v>
+        <v>0.0507209300994873</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8106837161192055</v>
+        <v>0.9087447139966063</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8760069044879172</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8238850693483192</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H13" t="n">
-        <v>0.918110502926512</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>84.12868881225586</v>
+        <v>0.09876132011413574</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7319187167195951</v>
+        <v>0.9095174369097344</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8299769850402762</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7391667698284974</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8593011597658791</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 2000, 'penalty': 'l1', 'solver': 'saga'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>220.4796578884125</v>
+        <v>0.1238057613372803</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7328853331272454</v>
+        <v>0.9087447139966063</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8288262370540852</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7371274467075601</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8584015282896162</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'C': 1, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'alpha': 0.001, 'l1_ratio': 1.0, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>361.8796882629395</v>
+        <v>1.929407596588135</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7330116584649267</v>
+        <v>0.9964407905175324</v>
       </c>
       <c r="F16" t="n">
-        <v>0.830264672036824</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G16" t="n">
-        <v>0.739472389794956</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8594352915673099</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'max_iter': 1000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2130286693572998</v>
+        <v>3.156977415084839</v>
       </c>
       <c r="E17" t="n">
-        <v>0.758522079737817</v>
+        <v>0.9975889547112533</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.9981552400435884</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.846406609551614</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.5817881338169909</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1723580360412598</v>
+        <v>3.335872411727905</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7588098200722057</v>
+        <v>0.9965440319277402</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.9979411295019519</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.8941772782146106</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.596932118403447</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2233843803405762</v>
+        <v>1.281316995620728</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7592605161401397</v>
+        <v>0.9974903523734235</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.9983181512040402</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.8081697467762399</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.5709631694446908</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 5, 'min_child_weight': 1, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>15747.45786547661</v>
+        <v>7.138336181640625</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9280699341723085</v>
+        <v>0.9957603155974105</v>
       </c>
       <c r="F20" t="n">
-        <v>0.950517836593786</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G20" t="n">
-        <v>0.932054070173397</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9845430034684587</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 50}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>18.41933584213257</v>
+        <v>6.981253623962402</v>
       </c>
       <c r="E21" t="n">
-        <v>0.928876610929035</v>
+        <v>0.9965907516726771</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9485040276179517</v>
+        <v>0.9972056385643899</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9296640638468039</v>
+        <v>1.041718565298485</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9831533618758581</v>
+        <v>0.7294976117107828</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 25}</t>
+          <t>{'learning_rate': 0.2, 'max_depth': 7, 'n_estimators': 200, 'num_leaves': 31}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2089,68 +2089,68 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>32.46850252151489</v>
+        <v>1.29323148727417</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9322375683739018</v>
+        <v>0.9916672509648135</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9508055235903338</v>
+        <v>0.9926310374474091</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9329165872415834</v>
+        <v>1.691656918987547</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9847139424813932</v>
+        <v>1.079954545454545</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'max_features': 1.0, 'max_samples': 0.6, 'n_estimators': 100}</t>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>44.7150092124939</v>
+        <v>1.950638294219971</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9131605579577853</v>
+        <v>0.991944820007945</v>
       </c>
       <c r="F23" t="n">
-        <v>0.939873417721519</v>
+        <v>0.9924359336701404</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9169917656074629</v>
+        <v>1.713905130730069</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9807870872172846</v>
+        <v>1.105564935064935</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2159,33 +2159,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>61.17642974853516</v>
+        <v>1.393115043640137</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9193219807675821</v>
+        <v>0.9919591707630674</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9413118527042578</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9190787698855583</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9801950104776356</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2194,22 +2194,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>137.197586774826</v>
+        <v>1.58259129524231</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9202278598090171</v>
+        <v>0.9922542316820335</v>
       </c>
       <c r="F25" t="n">
-        <v>0.939873417721519</v>
+        <v>0.9931963895337861</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9169917656074629</v>
+        <v>1.625469537425023</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9807870872172846</v>
+        <v>1.102047839255723</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,17 +457,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_R2</t>
+          <t>Test_Accuracy</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_RMSE</t>
+          <t>Test_F1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_MAE</t>
+          <t>Test_AUC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -479,70 +479,560 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.03185176849365</v>
+        <v>2.305255174636841</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9940702304082292</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6399832259487974</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4629059086032067</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>27.93966317176819</v>
+        <v>1.117658853530884</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9947256554325836</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6399832259487974</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4629059086032067</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04841518402099609</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983593504958139</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.05764937400817871</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.06094837188720703</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9967294558426634</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9888513513513514</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.09186434745788574</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9967253463310086</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9888513513513514</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.04705023765563965</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9885883726830831</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.07135176658630371</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9918380364236208</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.211564302444458</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9967294558426634</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4227964878082275</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.02556300163269043</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9804397703729418</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03720545768737793</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9804280526546304</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7404987812042236</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9983593504958139</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.154060363769531</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.035154342651367</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9950995611895129</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.188378095626831</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9967253463310086</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -557,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,17 +1078,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_R2</t>
+          <t>Test_Accuracy</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_RMSE</t>
+          <t>Test_F1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_MAE</t>
+          <t>Test_AUC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -610,70 +1100,560 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.03185176849365</v>
+        <v>2.305255174636841</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9940702304082292</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6399832259487974</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4629059086032067</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>27.93966317176819</v>
+        <v>1.117658853530884</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9947256554325836</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6399832259487974</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4629059086032067</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.04841518402099609</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983593504958139</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.05764937400817871</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.06094837188720703</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9967294558426634</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9888513513513514</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.09186434745788574</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9967253463310086</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9888513513513514</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.04705023765563965</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9885883726830831</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.07135176658630371</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9918380364236208</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.211564302444458</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9967294558426634</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4227964878082275</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.02556300163269043</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9804397703729418</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03720545768737793</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9804280526546304</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7404987812042236</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9983593504958139</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.154060363769531</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.035154342651367</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9950995611895129</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.188378095626831</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9967253463310086</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.305255174636841</v>
+        <v>8.916476964950562</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9259372549984396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.117658853530884</v>
+        <v>17.79089164733887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9296254451309558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04841518402099609</v>
+        <v>0.8451356887817383</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8998419434690367</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9254890678941312</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8991261138706356</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9601233380302046</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -596,23 +596,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05764937400817871</v>
+        <v>1.053424119949341</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9008461098105501</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9306674338319908</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9049920684579351</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9450958342365778</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -631,23 +631,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06094837188720703</v>
+        <v>327.696958065033</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.8329028339735882</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -666,23 +666,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09186434745788574</v>
+        <v>851.5462410449982</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.8406821430035827</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -701,23 +701,23 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04705023765563965</v>
+        <v>3.476128339767456</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.8013286401307914</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -736,23 +736,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07135176658630371</v>
+        <v>3.724423885345459</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.81032050938439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -771,23 +771,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.211564302444458</v>
+        <v>26.82263731956482</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.7318158655754914</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -806,23 +806,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4227964878082275</v>
+        <v>89.91980266571045</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.7328819229288671</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -841,19 +841,19 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02556300163269043</v>
+        <v>0.2610046863555908</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.758522079737817</v>
       </c>
       <c r="F12" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G12" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -876,19 +876,19 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03720545768737793</v>
+        <v>0.1970951557159424</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.7588098200722057</v>
       </c>
       <c r="F13" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G13" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -911,23 +911,23 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7404987812042236</v>
+        <v>6.78164267539978</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9280699341723085</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.950517836593786</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.932054070173397</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.9845430034684587</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -946,23 +946,23 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.154060363769531</v>
+        <v>12.55758929252625</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.928876610929035</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9485040276179517</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9296640638468039</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.9831533618758581</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -981,23 +981,23 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.035154342651367</v>
+        <v>74.2997670173645</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9131605579577853</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1016,23 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.188378095626831</v>
+        <v>85.74520540237427</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9193219807675821</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9413118527042578</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9190787698855583</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9801950104776356</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -1112,23 +1112,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.305255174636841</v>
+        <v>8.916476964950562</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9259372549984396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -1147,23 +1147,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.117658853530884</v>
+        <v>17.79089164733887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9296254451309558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -1182,23 +1182,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04841518402099609</v>
+        <v>0.8451356887817383</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8998419434690367</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9254890678941312</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8991261138706356</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9601233380302046</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -1217,23 +1217,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05764937400817871</v>
+        <v>1.053424119949341</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9008461098105501</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9306674338319908</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9049920684579351</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9450958342365778</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -1252,23 +1252,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06094837188720703</v>
+        <v>327.696958065033</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.8329028339735882</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -1287,23 +1287,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09186434745788574</v>
+        <v>851.5462410449982</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.8406821430035827</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -1322,23 +1322,23 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04705023765563965</v>
+        <v>3.476128339767456</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.8013286401307914</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -1357,23 +1357,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07135176658630371</v>
+        <v>3.724423885345459</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.81032050938439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -1392,23 +1392,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.211564302444458</v>
+        <v>26.82263731956482</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.7318158655754914</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -1427,23 +1427,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4227964878082275</v>
+        <v>89.91980266571045</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.7328819229288671</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -1462,19 +1462,19 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02556300163269043</v>
+        <v>0.2610046863555908</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.758522079737817</v>
       </c>
       <c r="F12" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G12" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1497,19 +1497,19 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03720545768737793</v>
+        <v>0.1970951557159424</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.7588098200722057</v>
       </c>
       <c r="F13" t="n">
-        <v>0.987012987012987</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G13" t="n">
-        <v>0.986977845425334</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1532,23 +1532,23 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7404987812042236</v>
+        <v>6.78164267539978</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9280699341723085</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.950517836593786</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.932054070173397</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.9845430034684587</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -1567,23 +1567,23 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.154060363769531</v>
+        <v>12.55758929252625</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.928876610929035</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9485040276179517</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9296640638468039</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.9831533618758581</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -1602,23 +1602,23 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.035154342651367</v>
+        <v>74.2997670173645</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9131605579577853</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -1637,23 +1637,23 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.188378095626831</v>
+        <v>85.74520540237427</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9193219807675821</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9413118527042578</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9190787698855583</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9801950104776356</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,17 +457,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_Accuracy</t>
+          <t>Test_R2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_F1</t>
+          <t>Test_RMSE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_AUC</t>
+          <t>Test_MAE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,30 +491,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.916476964950562</v>
+        <v>9.4547119140625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9259372549984396</v>
+        <v>0.440544769878822</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9490794016110472</v>
+        <v>0.5134104363845593</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9303364774002756</v>
+        <v>0.6138815401786868</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9854205054555963</v>
+        <v>0.4572289270463659</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,30 +526,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.79089164733887</v>
+        <v>11.32251524925232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9296254451309558</v>
+        <v>0.4659092559942006</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9490794016110472</v>
+        <v>0.5134104363845593</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9303364774002756</v>
+        <v>0.6138815401786868</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854205054555963</v>
+        <v>0.4572289270463659</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,30 +561,30 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8451356887817383</v>
+        <v>0.4565739631652832</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8998419434690367</v>
+        <v>0.2664539156126336</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9254890678941312</v>
+        <v>0.3205583175631379</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8991261138706356</v>
+        <v>0.7254028747236233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9601233380302046</v>
+        <v>0.5644262132689635</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,100 +596,100 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.053424119949341</v>
+        <v>0.8697562217712402</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9008461098105501</v>
+        <v>0.2705979812094531</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9306674338319908</v>
+        <v>0.3205583175631379</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9049920684579351</v>
+        <v>0.7254028747236233</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9450958342365778</v>
+        <v>0.5644262132689635</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>327.696958065033</v>
+        <v>45.87179636955261</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8329028339735882</v>
+        <v>-0.5020893562381507</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8918296892980437</v>
+        <v>-0.1463506699197445</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.942240838910085</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.5998887566777964</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>851.5462410449982</v>
+        <v>80.76652526855469</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8406821430035827</v>
+        <v>-0.4289905192472201</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8918296892980437</v>
+        <v>-0.1463506699197445</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.942240838910085</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.5998887566777964</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,30 +701,30 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3.476128339767456</v>
+        <v>0.4088060855865479</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.4611791357184896</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91744187621938</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,301 +736,581 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.724423885345459</v>
+        <v>0.4109337329864502</v>
       </c>
       <c r="E9" t="n">
-        <v>0.81032050938439</v>
+        <v>0.4869014791301536</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H9" t="n">
-        <v>0.91744187621938</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>26.82263731956482</v>
+        <v>0.08863043785095215</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7318158655754914</v>
+        <v>0.2756427052041309</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>89.91980266571045</v>
+        <v>0.1423959732055664</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7328819229288671</v>
+        <v>0.2772285011706008</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2610046863555908</v>
+        <v>0.0574958324432373</v>
       </c>
       <c r="E12" t="n">
-        <v>0.758522079737817</v>
+        <v>0.2762198267065196</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.2642087227138233</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.7548844799725748</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.5870174989191963</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1970951557159424</v>
+        <v>0.06962919235229492</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7588098200722057</v>
+        <v>0.2776218701339047</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.2642022548184634</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.7548877978313523</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.5870198778151539</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>6.78164267539978</v>
+        <v>0.07013201713562012</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9280699341723085</v>
+        <v>0.2766903121172088</v>
       </c>
       <c r="F14" t="n">
-        <v>0.950517836593786</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G14" t="n">
-        <v>0.932054070173397</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9845430034684587</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>12.55758929252625</v>
+        <v>0.08591938018798828</v>
       </c>
       <c r="E15" t="n">
-        <v>0.928876610929035</v>
+        <v>0.2779434303402907</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9485040276179517</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9296640638468039</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9831533618758581</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>74.2997670173645</v>
+        <v>5.46375560760498</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9131605579577853</v>
+        <v>0.4348747454254791</v>
       </c>
       <c r="F16" t="n">
-        <v>0.939873417721519</v>
+        <v>0.5068453595120126</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9169917656074629</v>
+        <v>0.618008916640357</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9807870872172846</v>
+        <v>0.4624842125736865</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.000943183898926</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.4664842237832341</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5068453595120126</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.618008916640357</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4624842125736865</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.641574144363403</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.4397318959236145</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5523912906646729</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5887791514396667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4128801226615906</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.78523850440979</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.4812644481658935</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5523912906646729</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5887791514396667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4128801226615906</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>27.8353750705719</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.420906216843518</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.515182664165955</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6127625988621126</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4577562623078762</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>66.20461487770081</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4558916021332542</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.515182664165955</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6127625988621126</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4577562623078762</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.515264987945557</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.4705013619511558</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5601484541981341</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5836550403591331</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4202984693877552</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8.012170791625977</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.4966990621142527</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5601484541981341</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5836550403591331</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4202984693877552</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Stacking</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>85.74520540237427</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9193219807675821</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9413118527042578</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9190787698855583</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.9801950104776356</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8.325294256210327</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4623585754058815</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5476623229282194</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5918812206686007</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4270981493479949</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11.31248903274536</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.48977812589358</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5476623229282194</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.5918812206686007</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4270981493479949</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
         </is>
@@ -1047,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1078,17 +1358,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_Accuracy</t>
+          <t>Test_R2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_F1</t>
+          <t>Test_RMSE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_AUC</t>
+          <t>Test_MAE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1100,7 +1380,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1112,30 +1392,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.916476964950562</v>
+        <v>9.4547119140625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9259372549984396</v>
+        <v>0.440544769878822</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9490794016110472</v>
+        <v>0.5134104363845593</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9303364774002756</v>
+        <v>0.6138815401786868</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9854205054555963</v>
+        <v>0.4572289270463659</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1147,30 +1427,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.79089164733887</v>
+        <v>11.32251524925232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9296254451309558</v>
+        <v>0.4659092559942006</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9490794016110472</v>
+        <v>0.5134104363845593</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9303364774002756</v>
+        <v>0.6138815401786868</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854205054555963</v>
+        <v>0.4572289270463659</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1182,30 +1462,30 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8451356887817383</v>
+        <v>0.4565739631652832</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8998419434690367</v>
+        <v>0.2664539156126336</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9254890678941312</v>
+        <v>0.3205583175631379</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8991261138706356</v>
+        <v>0.7254028747236233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9601233380302046</v>
+        <v>0.5644262132689635</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1217,100 +1497,100 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.053424119949341</v>
+        <v>0.8697562217712402</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9008461098105501</v>
+        <v>0.2705979812094531</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9306674338319908</v>
+        <v>0.3205583175631379</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9049920684579351</v>
+        <v>0.7254028747236233</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9450958342365778</v>
+        <v>0.5644262132689635</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>327.696958065033</v>
+        <v>45.87179636955261</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8329028339735882</v>
+        <v>-0.5020893562381507</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8918296892980437</v>
+        <v>-0.1463506699197445</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.942240838910085</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.5998887566777964</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>851.5462410449982</v>
+        <v>80.76652526855469</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8406821430035827</v>
+        <v>-0.4289905192472201</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8918296892980437</v>
+        <v>-0.1463506699197445</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.942240838910085</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.5998887566777964</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1322,30 +1602,30 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3.476128339767456</v>
+        <v>0.4088060855865479</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.4611791357184896</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91744187621938</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1357,301 +1637,581 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.724423885345459</v>
+        <v>0.4109337329864502</v>
       </c>
       <c r="E9" t="n">
-        <v>0.81032050938439</v>
+        <v>0.4869014791301536</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H9" t="n">
-        <v>0.91744187621938</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>26.82263731956482</v>
+        <v>0.08863043785095215</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7318158655754914</v>
+        <v>0.2756427052041309</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>89.91980266571045</v>
+        <v>0.1423959732055664</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7328819229288671</v>
+        <v>0.2772285011706008</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.5863230154211657</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2610046863555908</v>
+        <v>0.0574958324432373</v>
       </c>
       <c r="E12" t="n">
-        <v>0.758522079737817</v>
+        <v>0.2762198267065196</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.2642087227138233</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.7548844799725748</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.5870174989191963</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1970951557159424</v>
+        <v>0.06962919235229492</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7588098200722057</v>
+        <v>0.2776218701339047</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8201956271576525</v>
+        <v>0.2642022548184634</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7654782974318119</v>
+        <v>0.7548877978313523</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8779147698533132</v>
+        <v>0.5870198778151539</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>6.78164267539978</v>
+        <v>0.07013201713562012</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9280699341723085</v>
+        <v>0.2766903121172088</v>
       </c>
       <c r="F14" t="n">
-        <v>0.950517836593786</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G14" t="n">
-        <v>0.932054070173397</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9845430034684587</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>12.55758929252625</v>
+        <v>0.08591938018798828</v>
       </c>
       <c r="E15" t="n">
-        <v>0.928876610929035</v>
+        <v>0.2779434303402907</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9485040276179517</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9296640638468039</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9831533618758581</v>
+        <v>0.5882492388088877</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>74.2997670173645</v>
+        <v>5.46375560760498</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9131605579577853</v>
+        <v>0.4348747454254791</v>
       </c>
       <c r="F16" t="n">
-        <v>0.939873417721519</v>
+        <v>0.5068453595120126</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9169917656074629</v>
+        <v>0.618008916640357</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9807870872172846</v>
+        <v>0.4624842125736865</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.000943183898926</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.4664842237832341</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5068453595120126</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.618008916640357</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4624842125736865</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.641574144363403</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.4397318959236145</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5523912906646729</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5887791514396667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4128801226615906</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.78523850440979</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.4812644481658935</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5523912906646729</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5887791514396667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4128801226615906</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>27.8353750705719</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.420906216843518</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.515182664165955</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6127625988621126</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4577562623078762</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>66.20461487770081</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4558916021332542</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.515182664165955</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6127625988621126</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4577562623078762</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.515264987945557</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.4705013619511558</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5601484541981341</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5836550403591331</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4202984693877552</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8.012170791625977</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.4966990621142527</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5601484541981341</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5836550403591331</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4202984693877552</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Stacking</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>85.74520540237427</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9193219807675821</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9413118527042578</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9190787698855583</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.9801950104776356</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8.325294256210327</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4623585754058815</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5476623229282194</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5918812206686007</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4270981493479949</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11.31248903274536</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.48977812589358</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5476623229282194</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.5918812206686007</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4270981493479949</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
         </is>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,17 +457,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_R2</t>
+          <t>Test_Accuracy</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_RMSE</t>
+          <t>Test_F1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_MAE</t>
+          <t>Test_AUC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,30 +491,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4547119140625</v>
+        <v>46.42610740661621</v>
       </c>
       <c r="E2" t="n">
-        <v>0.440544769878822</v>
+        <v>0.7424679277285154</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5134104363845593</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6138815401786868</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4572289270463659</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,30 +526,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.32251524925232</v>
+        <v>67.93033361434937</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4659092559942006</v>
+        <v>0.7591605966879464</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5134104363845593</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6138815401786868</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4572289270463659</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,30 +561,30 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4565739631652832</v>
+        <v>0.715111255645752</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2664539156126336</v>
+        <v>0.7178455340929982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3205583175631379</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7254028747236233</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5644262132689635</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,100 +596,100 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8697562217712402</v>
+        <v>1.173915863037109</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2705979812094531</v>
+        <v>0.7296280924933435</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3205583175631379</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7254028747236233</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5644262132689635</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>45.87179636955261</v>
+        <v>20413.65140247345</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5020893562381507</v>
+        <v>0.7749083896227867</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1463506699197445</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G6" t="n">
-        <v>0.942240838910085</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5998887566777964</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>80.76652526855469</v>
+        <v>25779.20336675644</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4289905192472201</v>
+        <v>0.7829275385741383</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1463506699197445</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G7" t="n">
-        <v>0.942240838910085</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5998887566777964</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,30 +701,30 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4088060855865479</v>
+        <v>4.328197240829468</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4611791357184896</v>
+        <v>0.7816443157726987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G8" t="n">
-        <v>0.593756937122587</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3799547808937107</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,581 +736,301 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4109337329864502</v>
+        <v>3.765619277954102</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4869014791301536</v>
+        <v>0.7887837510961361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G9" t="n">
-        <v>0.593756937122587</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3799547808937107</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08863043785095215</v>
+        <v>1.760576009750366</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2756427052041309</v>
+        <v>0.5708386073605726</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.7322016721560679</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7543978232164172</v>
+        <v>0.5792004344384017</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5863230154211657</v>
+        <v>0.7940013503316254</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1423959732055664</v>
+        <v>3.360211372375488</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2772285011706008</v>
+        <v>0.5714566683306512</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.7332151000760071</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7543978232164172</v>
+        <v>0.5799855750471964</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5863230154211657</v>
+        <v>0.7939449541284403</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0574958324432373</v>
+        <v>0.221412181854248</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2762198267065196</v>
+        <v>0.5534276352203948</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2642087227138233</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7548844799725748</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5870174989191963</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06962919235229492</v>
+        <v>0.2061653137207031</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2776218701339047</v>
+        <v>0.5584974950698796</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2642022548184634</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7548877978313523</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5870198778151539</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07013201713562012</v>
+        <v>29.3004412651062</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2766903121172088</v>
+        <v>0.7521014360203813</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.9450215353432987</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7561766858252632</v>
+        <v>0.7897204739826351</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5882492388088877</v>
+        <v>0.9349533341276461</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08591938018798828</v>
+        <v>57.42630863189697</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2779434303402907</v>
+        <v>0.7677588908801928</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.9445148213833291</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7561766858252632</v>
+        <v>0.7926083122896885</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5882492388088877</v>
+        <v>0.9250530203741212</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>5.46375560760498</v>
+        <v>55.87844181060791</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4348747454254791</v>
+        <v>0.7663753818038094</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5068453595120126</v>
+        <v>0.9467950342031923</v>
       </c>
       <c r="G16" t="n">
-        <v>0.618008916640357</v>
+        <v>0.8046094877089758</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4624842125736865</v>
+        <v>0.9339814925136026</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>9.000943183898926</v>
+        <v>80.65231132507324</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4664842237832341</v>
+        <v>0.7834056300532612</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5068453595120126</v>
+        <v>0.9447681783633139</v>
       </c>
       <c r="G17" t="n">
-        <v>0.618008916640357</v>
+        <v>0.7965198332895054</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4624842125736865</v>
+        <v>0.9337574963263038</v>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.641574144363403</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.4397318959236145</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.5523912906646729</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.5887791514396667</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.4128801226615906</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.78523850440979</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.4812644481658935</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5523912906646729</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.5887791514396667</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.4128801226615906</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>27.8353750705719</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.420906216843518</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.515182664165955</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.6127625988621126</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.4577562623078762</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>66.20461487770081</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.4558916021332542</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.515182664165955</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.6127625988621126</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.4577562623078762</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4.515264987945557</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.4705013619511558</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5601484541981341</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.5836550403591331</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.4202984693877552</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>8.012170791625977</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.4966990621142527</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5601484541981341</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.5836550403591331</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.4202984693877552</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>8.325294256210327</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.4623585754058815</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.5476623229282194</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.5918812206686007</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.4270981493479949</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'cv': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>11.31248903274536</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.48977812589358</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.5476623229282194</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.5918812206686007</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.4270981493479949</v>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
         </is>
@@ -1327,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1358,17 +1078,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_R2</t>
+          <t>Test_Accuracy</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_RMSE</t>
+          <t>Test_F1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_MAE</t>
+          <t>Test_AUC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1380,7 +1100,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1392,30 +1112,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4547119140625</v>
+        <v>46.42610740661621</v>
       </c>
       <c r="E2" t="n">
-        <v>0.440544769878822</v>
+        <v>0.7424679277285154</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5134104363845593</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6138815401786868</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4572289270463659</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1427,30 +1147,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.32251524925232</v>
+        <v>67.93033361434937</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4659092559942006</v>
+        <v>0.7591605966879464</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5134104363845593</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6138815401786868</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4572289270463659</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1462,30 +1182,30 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4565739631652832</v>
+        <v>0.715111255645752</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2664539156126336</v>
+        <v>0.7178455340929982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3205583175631379</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7254028747236233</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5644262132689635</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1497,100 +1217,100 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8697562217712402</v>
+        <v>1.173915863037109</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2705979812094531</v>
+        <v>0.7296280924933435</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3205583175631379</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7254028747236233</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5644262132689635</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>45.87179636955261</v>
+        <v>20413.65140247345</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5020893562381507</v>
+        <v>0.7749083896227867</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1463506699197445</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G6" t="n">
-        <v>0.942240838910085</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5998887566777964</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>80.76652526855469</v>
+        <v>25779.20336675644</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4289905192472201</v>
+        <v>0.7829275385741383</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1463506699197445</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G7" t="n">
-        <v>0.942240838910085</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5998887566777964</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'degree': 1, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1602,30 +1322,30 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4088060855865479</v>
+        <v>4.328197240829468</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4611791357184896</v>
+        <v>0.7816443157726987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G8" t="n">
-        <v>0.593756937122587</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3799547808937107</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1637,581 +1357,301 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4109337329864502</v>
+        <v>3.765619277954102</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4869014791301536</v>
+        <v>0.7887837510961361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G9" t="n">
-        <v>0.593756937122587</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3799547808937107</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08863043785095215</v>
+        <v>1.760576009750366</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2756427052041309</v>
+        <v>0.5708386073605726</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.7322016721560679</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7543978232164172</v>
+        <v>0.5792004344384017</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5863230154211657</v>
+        <v>0.7940013503316254</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1423959732055664</v>
+        <v>3.360211372375488</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2772285011706008</v>
+        <v>0.5714566683306512</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2651571125229343</v>
+        <v>0.7332151000760071</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7543978232164172</v>
+        <v>0.5799855750471964</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5863230154211657</v>
+        <v>0.7939449541284403</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0574958324432373</v>
+        <v>0.221412181854248</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2762198267065196</v>
+        <v>0.5534276352203948</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2642087227138233</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7548844799725748</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5870174989191963</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06962919235229492</v>
+        <v>0.2061653137207031</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2776218701339047</v>
+        <v>0.5584974950698796</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2642022548184634</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7548877978313523</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5870198778151539</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07013201713562012</v>
+        <v>29.3004412651062</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2766903121172088</v>
+        <v>0.7521014360203813</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.9450215353432987</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7561766858252632</v>
+        <v>0.7897204739826351</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5882492388088877</v>
+        <v>0.9349533341276461</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08591938018798828</v>
+        <v>57.42630863189697</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2779434303402907</v>
+        <v>0.7677588908801928</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2616875221828251</v>
+        <v>0.9445148213833291</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7561766858252632</v>
+        <v>0.7926083122896885</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5882492388088877</v>
+        <v>0.9250530203741212</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.01}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>5.46375560760498</v>
+        <v>55.87844181060791</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4348747454254791</v>
+        <v>0.7663753818038094</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5068453595120126</v>
+        <v>0.9467950342031923</v>
       </c>
       <c r="G16" t="n">
-        <v>0.618008916640357</v>
+        <v>0.8046094877089758</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4624842125736865</v>
+        <v>0.9339814925136026</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>9.000943183898926</v>
+        <v>80.65231132507324</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4664842237832341</v>
+        <v>0.7834056300532612</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5068453595120126</v>
+        <v>0.9447681783633139</v>
       </c>
       <c r="G17" t="n">
-        <v>0.618008916640357</v>
+        <v>0.7965198332895054</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4624842125736865</v>
+        <v>0.9337574963263038</v>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.641574144363403</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.4397318959236145</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.5523912906646729</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.5887791514396667</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.4128801226615906</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.78523850440979</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.4812644481658935</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5523912906646729</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.5887791514396667</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.4128801226615906</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>27.8353750705719</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.420906216843518</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.515182664165955</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.6127625988621126</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.4577562623078762</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>66.20461487770081</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.4558916021332542</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.515182664165955</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.6127625988621126</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.4577562623078762</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4.515264987945557</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.4705013619511558</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5601484541981341</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.5836550403591331</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.4202984693877552</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>8.012170791625977</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.4966990621142527</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5601484541981341</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.5836550403591331</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.4202984693877552</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>8.325294256210327</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.4623585754058815</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.5476623229282194</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.5918812206686007</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.4270981493479949</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'cv': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>11.31248903274536</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.48977812589358</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.5476623229282194</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.5918812206686007</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.4270981493479949</v>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
         </is>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>46.42610740661621</v>
+        <v>2.268043518066406</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7424679277285154</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.90826124945391</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>67.93033361434937</v>
+        <v>1.16223406791687</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7591605966879464</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.90826124945391</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.715111255645752</v>
+        <v>0.04831504821777344</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7178455340929982</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -596,23 +596,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.173915863037109</v>
+        <v>0.06014561653137207</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7296280924933435</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -631,23 +631,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>20413.65140247345</v>
+        <v>0.06463313102722168</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7749083896227867</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -666,23 +666,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>25779.20336675644</v>
+        <v>0.1030514240264893</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7829275385741383</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -701,23 +701,23 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4.328197240829468</v>
+        <v>0.06473898887634277</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7816443157726987</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -736,23 +736,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.765619277954102</v>
+        <v>0.06860542297363281</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7887837510961361</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -771,23 +771,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.760576009750366</v>
+        <v>0.1705286502838135</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5708386073605726</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7322016721560679</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5792004344384017</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7940013503316254</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -806,23 +806,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3.360211372375488</v>
+        <v>0.3486030101776123</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5714566683306512</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7332151000760071</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5799855750471964</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7939449541284403</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -841,19 +841,19 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.221412181854248</v>
+        <v>0.02712750434875488</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5534276352203948</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -876,19 +876,19 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2061653137207031</v>
+        <v>0.02701616287231445</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5584974950698796</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -911,19 +911,19 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>29.3004412651062</v>
+        <v>0.7135782241821289</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7521014360203813</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9450215353432987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7897204739826351</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9349533341276461</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -946,23 +946,23 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>57.42630863189697</v>
+        <v>1.323484182357788</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7677588908801928</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9445148213833291</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7926083122896885</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9250530203741212</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -981,23 +981,23 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>55.87844181060791</v>
+        <v>0.9087929725646973</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7663753818038094</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9467950342031923</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8046094877089758</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9339814925136026</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1016,23 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>80.65231132507324</v>
+        <v>1.191066265106201</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7834056300532612</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9447681783633139</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7965198332895054</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9337574963263038</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -1112,23 +1112,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>46.42610740661621</v>
+        <v>2.268043518066406</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7424679277285154</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.90826124945391</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -1147,23 +1147,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>67.93033361434937</v>
+        <v>1.16223406791687</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7591605966879464</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.90826124945391</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -1182,23 +1182,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.715111255645752</v>
+        <v>0.04831504821777344</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7178455340929982</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -1217,23 +1217,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.173915863037109</v>
+        <v>0.06014561653137207</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7296280924933435</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -1252,23 +1252,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>20413.65140247345</v>
+        <v>0.06463313102722168</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7749083896227867</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -1287,23 +1287,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>25779.20336675644</v>
+        <v>0.1030514240264893</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7829275385741383</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -1322,23 +1322,23 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4.328197240829468</v>
+        <v>0.06473898887634277</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7816443157726987</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -1357,23 +1357,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.765619277954102</v>
+        <v>0.06860542297363281</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7887837510961361</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -1392,23 +1392,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.760576009750366</v>
+        <v>0.1705286502838135</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5708386073605726</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7322016721560679</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5792004344384017</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7940013503316254</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -1427,23 +1427,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3.360211372375488</v>
+        <v>0.3486030101776123</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5714566683306512</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7332151000760071</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5799855750471964</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7939449541284403</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -1462,19 +1462,19 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.221412181854248</v>
+        <v>0.02712750434875488</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5534276352203948</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1497,19 +1497,19 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2061653137207031</v>
+        <v>0.02701616287231445</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5584974950698796</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1532,19 +1532,19 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>29.3004412651062</v>
+        <v>0.7135782241821289</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7521014360203813</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9450215353432987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7897204739826351</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9349533341276461</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1567,23 +1567,23 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>57.42630863189697</v>
+        <v>1.323484182357788</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7677588908801928</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9445148213833291</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7926083122896885</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9250530203741212</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -1602,23 +1602,23 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>55.87844181060791</v>
+        <v>0.9087929725646973</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7663753818038094</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9467950342031923</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8046094877089758</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9339814925136026</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -1637,23 +1637,23 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>80.65231132507324</v>
+        <v>1.191066265106201</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7834056300532612</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9447681783633139</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7965198332895054</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9337574963263038</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.268043518066406</v>
+        <v>2.095865249633789</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16223406791687</v>
+        <v>1.0072021484375</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04831504821777344</v>
+        <v>0.0374138355255127</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983593504958139</v>
@@ -596,7 +596,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06014561653137207</v>
+        <v>0.04952788352966309</v>
       </c>
       <c r="E5" t="n">
         <v>0.9983552409841592</v>
@@ -631,7 +631,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06463313102722168</v>
+        <v>0.05411744117736816</v>
       </c>
       <c r="E6" t="n">
         <v>0.9967294558426634</v>
@@ -666,7 +666,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1030514240264893</v>
+        <v>0.08301877975463867</v>
       </c>
       <c r="E7" t="n">
         <v>0.9967253463310086</v>
@@ -701,7 +701,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06473898887634277</v>
+        <v>0.0462803840637207</v>
       </c>
       <c r="E8" t="n">
         <v>0.9885883726830831</v>
@@ -736,7 +736,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06860542297363281</v>
+        <v>0.04892253875732422</v>
       </c>
       <c r="E9" t="n">
         <v>0.9918380364236208</v>
@@ -771,7 +771,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1705286502838135</v>
+        <v>0.1674644947052002</v>
       </c>
       <c r="E10" t="n">
         <v>0.9967294558426634</v>
@@ -806,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3486030101776123</v>
+        <v>0.3419375419616699</v>
       </c>
       <c r="E11" t="n">
         <v>0.9983552409841592</v>
@@ -841,7 +841,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02712750434875488</v>
+        <v>0.02542209625244141</v>
       </c>
       <c r="E12" t="n">
         <v>0.9804397703729418</v>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02701616287231445</v>
+        <v>0.03789854049682617</v>
       </c>
       <c r="E13" t="n">
         <v>0.9804280526546304</v>
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7135782241821289</v>
+        <v>0.649118185043335</v>
       </c>
       <c r="E14" t="n">
         <v>0.9983593504958139</v>
@@ -946,7 +946,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.323484182357788</v>
+        <v>1.075996160507202</v>
       </c>
       <c r="E15" t="n">
         <v>0.9983552409841592</v>
@@ -981,7 +981,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9087929725646973</v>
+        <v>0.8377194404602051</v>
       </c>
       <c r="E16" t="n">
         <v>0.9950995611895129</v>
@@ -1016,7 +1016,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.191066265106201</v>
+        <v>1.073031425476074</v>
       </c>
       <c r="E17" t="n">
         <v>0.9967253463310086</v>
@@ -1112,7 +1112,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.268043518066406</v>
+        <v>2.095865249633789</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -1147,7 +1147,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16223406791687</v>
+        <v>1.0072021484375</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -1182,7 +1182,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04831504821777344</v>
+        <v>0.0374138355255127</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983593504958139</v>
@@ -1217,7 +1217,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06014561653137207</v>
+        <v>0.04952788352966309</v>
       </c>
       <c r="E5" t="n">
         <v>0.9983552409841592</v>
@@ -1252,7 +1252,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06463313102722168</v>
+        <v>0.05411744117736816</v>
       </c>
       <c r="E6" t="n">
         <v>0.9967294558426634</v>
@@ -1287,7 +1287,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1030514240264893</v>
+        <v>0.08301877975463867</v>
       </c>
       <c r="E7" t="n">
         <v>0.9967253463310086</v>
@@ -1322,7 +1322,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06473898887634277</v>
+        <v>0.0462803840637207</v>
       </c>
       <c r="E8" t="n">
         <v>0.9885883726830831</v>
@@ -1357,7 +1357,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06860542297363281</v>
+        <v>0.04892253875732422</v>
       </c>
       <c r="E9" t="n">
         <v>0.9918380364236208</v>
@@ -1392,7 +1392,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1705286502838135</v>
+        <v>0.1674644947052002</v>
       </c>
       <c r="E10" t="n">
         <v>0.9967294558426634</v>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3486030101776123</v>
+        <v>0.3419375419616699</v>
       </c>
       <c r="E11" t="n">
         <v>0.9983552409841592</v>
@@ -1462,7 +1462,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02712750434875488</v>
+        <v>0.02542209625244141</v>
       </c>
       <c r="E12" t="n">
         <v>0.9804397703729418</v>
@@ -1497,7 +1497,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02701616287231445</v>
+        <v>0.03789854049682617</v>
       </c>
       <c r="E13" t="n">
         <v>0.9804280526546304</v>
@@ -1532,7 +1532,7 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7135782241821289</v>
+        <v>0.649118185043335</v>
       </c>
       <c r="E14" t="n">
         <v>0.9983593504958139</v>
@@ -1567,7 +1567,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.323484182357788</v>
+        <v>1.075996160507202</v>
       </c>
       <c r="E15" t="n">
         <v>0.9983552409841592</v>
@@ -1602,7 +1602,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9087929725646973</v>
+        <v>0.8377194404602051</v>
       </c>
       <c r="E16" t="n">
         <v>0.9950995611895129</v>
@@ -1637,7 +1637,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.191066265106201</v>
+        <v>1.073031425476074</v>
       </c>
       <c r="E17" t="n">
         <v>0.9967253463310086</v>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.095865249633789</v>
+        <v>2.091913223266602</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0072021484375</v>
+        <v>1.044002771377563</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0374138355255127</v>
+        <v>0.04878354072570801</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983593504958139</v>
@@ -596,7 +596,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04952788352966309</v>
+        <v>0.04909563064575195</v>
       </c>
       <c r="E5" t="n">
         <v>0.9983552409841592</v>
@@ -631,7 +631,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05411744117736816</v>
+        <v>0.07068085670471191</v>
       </c>
       <c r="E6" t="n">
         <v>0.9967294558426634</v>
@@ -666,7 +666,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08301877975463867</v>
+        <v>0.09784936904907227</v>
       </c>
       <c r="E7" t="n">
         <v>0.9967253463310086</v>
@@ -701,7 +701,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0462803840637207</v>
+        <v>0.04709029197692871</v>
       </c>
       <c r="E8" t="n">
         <v>0.9885883726830831</v>
@@ -736,7 +736,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04892253875732422</v>
+        <v>0.07294321060180664</v>
       </c>
       <c r="E9" t="n">
         <v>0.9918380364236208</v>
@@ -771,7 +771,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1674644947052002</v>
+        <v>0.168318510055542</v>
       </c>
       <c r="E10" t="n">
         <v>0.9967294558426634</v>
@@ -806,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3419375419616699</v>
+        <v>0.3358554840087891</v>
       </c>
       <c r="E11" t="n">
         <v>0.9983552409841592</v>
@@ -841,7 +841,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02542209625244141</v>
+        <v>0.03090858459472656</v>
       </c>
       <c r="E12" t="n">
         <v>0.9804397703729418</v>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03789854049682617</v>
+        <v>0.03694772720336914</v>
       </c>
       <c r="E13" t="n">
         <v>0.9804280526546304</v>
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.649118185043335</v>
+        <v>0.6855957508087158</v>
       </c>
       <c r="E14" t="n">
         <v>0.9983593504958139</v>
@@ -946,7 +946,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.075996160507202</v>
+        <v>1.136143445968628</v>
       </c>
       <c r="E15" t="n">
         <v>0.9983552409841592</v>
@@ -981,7 +981,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8377194404602051</v>
+        <v>0.7824199199676514</v>
       </c>
       <c r="E16" t="n">
         <v>0.9950995611895129</v>
@@ -1016,7 +1016,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.073031425476074</v>
+        <v>1.052121877670288</v>
       </c>
       <c r="E17" t="n">
         <v>0.9967253463310086</v>
@@ -1112,7 +1112,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.095865249633789</v>
+        <v>2.091913223266602</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -1147,7 +1147,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0072021484375</v>
+        <v>1.044002771377563</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -1182,7 +1182,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0374138355255127</v>
+        <v>0.04878354072570801</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983593504958139</v>
@@ -1217,7 +1217,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04952788352966309</v>
+        <v>0.04909563064575195</v>
       </c>
       <c r="E5" t="n">
         <v>0.9983552409841592</v>
@@ -1252,7 +1252,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05411744117736816</v>
+        <v>0.07068085670471191</v>
       </c>
       <c r="E6" t="n">
         <v>0.9967294558426634</v>
@@ -1287,7 +1287,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08301877975463867</v>
+        <v>0.09784936904907227</v>
       </c>
       <c r="E7" t="n">
         <v>0.9967253463310086</v>
@@ -1322,7 +1322,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0462803840637207</v>
+        <v>0.04709029197692871</v>
       </c>
       <c r="E8" t="n">
         <v>0.9885883726830831</v>
@@ -1357,7 +1357,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04892253875732422</v>
+        <v>0.07294321060180664</v>
       </c>
       <c r="E9" t="n">
         <v>0.9918380364236208</v>
@@ -1392,7 +1392,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1674644947052002</v>
+        <v>0.168318510055542</v>
       </c>
       <c r="E10" t="n">
         <v>0.9967294558426634</v>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3419375419616699</v>
+        <v>0.3358554840087891</v>
       </c>
       <c r="E11" t="n">
         <v>0.9983552409841592</v>
@@ -1462,7 +1462,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02542209625244141</v>
+        <v>0.03090858459472656</v>
       </c>
       <c r="E12" t="n">
         <v>0.9804397703729418</v>
@@ -1497,7 +1497,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03789854049682617</v>
+        <v>0.03694772720336914</v>
       </c>
       <c r="E13" t="n">
         <v>0.9804280526546304</v>
@@ -1532,7 +1532,7 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.649118185043335</v>
+        <v>0.6855957508087158</v>
       </c>
       <c r="E14" t="n">
         <v>0.9983593504958139</v>
@@ -1567,7 +1567,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.075996160507202</v>
+        <v>1.136143445968628</v>
       </c>
       <c r="E15" t="n">
         <v>0.9983552409841592</v>
@@ -1602,7 +1602,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8377194404602051</v>
+        <v>0.7824199199676514</v>
       </c>
       <c r="E16" t="n">
         <v>0.9950995611895129</v>
@@ -1637,7 +1637,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.073031425476074</v>
+        <v>1.052121877670288</v>
       </c>
       <c r="E17" t="n">
         <v>0.9967253463310086</v>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,17 +484,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.091913223266602</v>
+        <v>2.142980337142944</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
@@ -503,11 +503,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.044002771377563</v>
+        <v>0.1519787311553955</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F3" t="n">
         <v>0.9935064935064936</v>
@@ -538,11 +538,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -554,17 +554,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04878354072570801</v>
+        <v>0.1360764503479004</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9918326672831579</v>
       </c>
       <c r="F4" t="n">
         <v>0.9935064935064936</v>
@@ -573,11 +573,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9936655405405406</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -589,17 +589,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04909563064575195</v>
+        <v>0.316514253616333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F5" t="n">
         <v>0.9935064935064936</v>
@@ -608,11 +608,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -624,17 +624,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07068085670471191</v>
+        <v>0.4219343662261963</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F6" t="n">
         <v>0.9935064935064936</v>
@@ -643,11 +643,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9888513513513514</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -659,17 +659,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09784936904907227</v>
+        <v>1.122652053833008</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9967124678275436</v>
       </c>
       <c r="F7" t="n">
         <v>0.9935064935064936</v>
@@ -678,11 +678,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9888513513513514</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -694,30 +694,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04709029197692871</v>
+        <v>0.05379128456115723</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -729,30 +729,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07294321060180664</v>
+        <v>0.08011054992675781</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -764,30 +764,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.168318510055542</v>
+        <v>0.06212043762207031</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.9804441893856517</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3358554840087891</v>
+        <v>1.096622705459595</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F11" t="n">
         <v>0.9935064935064936</v>
@@ -822,7 +822,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -834,30 +834,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03090858459472656</v>
+        <v>1.609349012374878</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F12" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G12" t="n">
-        <v>0.986977845425334</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9863175675675676</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -869,30 +869,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03694772720336914</v>
+        <v>2.971560955047607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.9983535762483131</v>
       </c>
       <c r="F13" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G13" t="n">
-        <v>0.986977845425334</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9863175675675676</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6855957508087158</v>
+        <v>1.180825710296631</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F14" t="n">
         <v>0.9935064935064936</v>
@@ -923,11 +923,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.136143445968628</v>
+        <v>1.669695138931274</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F15" t="n">
         <v>0.9935064935064936</v>
@@ -958,11 +958,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7824199199676514</v>
+        <v>2.459268569946289</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9967368878519636</v>
       </c>
       <c r="F16" t="n">
         <v>0.9935064935064936</v>
@@ -998,41 +998,6 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.052121877670288</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9967253463310086</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.9998310810810811</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1105,17 +1070,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.091913223266602</v>
+        <v>2.142980337142944</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
@@ -1124,11 +1089,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -1140,17 +1105,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.044002771377563</v>
+        <v>0.1519787311553955</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F3" t="n">
         <v>0.9935064935064936</v>
@@ -1159,11 +1124,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1140,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04878354072570801</v>
+        <v>0.1360764503479004</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9918326672831579</v>
       </c>
       <c r="F4" t="n">
         <v>0.9935064935064936</v>
@@ -1194,11 +1159,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9936655405405406</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -1210,17 +1175,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04909563064575195</v>
+        <v>0.316514253616333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F5" t="n">
         <v>0.9935064935064936</v>
@@ -1229,11 +1194,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9999155405405405</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1210,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07068085670471191</v>
+        <v>0.4219343662261963</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F6" t="n">
         <v>0.9935064935064936</v>
@@ -1264,11 +1229,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9888513513513514</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1245,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09784936904907227</v>
+        <v>1.122652053833008</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9967124678275436</v>
       </c>
       <c r="F7" t="n">
         <v>0.9935064935064936</v>
@@ -1299,11 +1264,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9888513513513514</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -1315,30 +1280,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04709029197692871</v>
+        <v>0.05379128456115723</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.9804397703729418</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -1350,30 +1315,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07294321060180664</v>
+        <v>0.08011054992675781</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.9804280526546304</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -1385,30 +1350,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.168318510055542</v>
+        <v>0.06212043762207031</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.9804441893856517</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.986977845425334</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9863175675675676</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
     </row>
@@ -1420,17 +1385,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3358554840087891</v>
+        <v>1.096622705459595</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F11" t="n">
         <v>0.9935064935064936</v>
@@ -1443,7 +1408,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1420,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03090858459472656</v>
+        <v>1.609349012374878</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F12" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G12" t="n">
-        <v>0.986977845425334</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9863175675675676</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -1490,30 +1455,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03694772720336914</v>
+        <v>2.971560955047607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.9983535762483131</v>
       </c>
       <c r="F13" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G13" t="n">
-        <v>0.986977845425334</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9863175675675676</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
     </row>
@@ -1525,17 +1490,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6855957508087158</v>
+        <v>1.180825710296631</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9950995611895129</v>
       </c>
       <c r="F14" t="n">
         <v>0.9935064935064936</v>
@@ -1544,11 +1509,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
     </row>
@@ -1560,17 +1525,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.136143445968628</v>
+        <v>1.669695138931274</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F15" t="n">
         <v>0.9935064935064936</v>
@@ -1579,11 +1544,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -1599,13 +1564,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7824199199676514</v>
+        <v>2.459268569946289</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9967368878519636</v>
       </c>
       <c r="F16" t="n">
         <v>0.9935064935064936</v>
@@ -1619,41 +1584,6 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.052121877670288</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9967253463310086</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.9998310810810811</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,17 +484,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.142980337142944</v>
+        <v>2.815093755722046</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
@@ -503,11 +503,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1519787311553955</v>
+        <v>1.426376581192017</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
         <v>0.9935064935064936</v>
@@ -538,11 +538,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -554,17 +554,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1360764503479004</v>
+        <v>2.55407977104187</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9918326672831579</v>
+        <v>0.9983535762483131</v>
       </c>
       <c r="F4" t="n">
         <v>0.9935064935064936</v>
@@ -573,11 +573,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9936655405405406</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -589,17 +589,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.316514253616333</v>
+        <v>0.1134634017944336</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F5" t="n">
         <v>0.9935064935064936</v>
@@ -608,11 +608,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -624,14 +624,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4219343662261963</v>
+        <v>0.07774615287780762</v>
       </c>
       <c r="E6" t="n">
         <v>0.9983552409841592</v>
@@ -643,11 +643,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -659,17 +659,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>1.122652053833008</v>
+        <v>0.167536735534668</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9967124678275436</v>
+        <v>0.9983535762483131</v>
       </c>
       <c r="F7" t="n">
         <v>0.9935064935064936</v>
@@ -678,11 +678,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -694,30 +694,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05379128456115723</v>
+        <v>0.08736753463745117</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F8" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G8" t="n">
-        <v>0.986977845425334</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -729,30 +729,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08011054992675781</v>
+        <v>0.1757090091705322</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F9" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.986977845425334</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -764,30 +764,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06212043762207031</v>
+        <v>0.2211108207702637</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9804441893856517</v>
+        <v>0.9967071524966261</v>
       </c>
       <c r="F10" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G10" t="n">
-        <v>0.986977845425334</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9863175675675676</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.096622705459595</v>
+        <v>0.1147856712341309</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F11" t="n">
         <v>0.9935064935064936</v>
@@ -818,11 +818,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -834,17 +834,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.609349012374878</v>
+        <v>0.08343935012817383</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F12" t="n">
         <v>0.9935064935064936</v>
@@ -853,11 +853,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -869,17 +869,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>2.971560955047607</v>
+        <v>0.1888899803161621</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9983535762483131</v>
+        <v>0.9918326672831579</v>
       </c>
       <c r="F13" t="n">
         <v>0.9935064935064936</v>
@@ -888,11 +888,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.9936655405405406</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1.180825710296631</v>
+        <v>0.2196180820465088</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F14" t="n">
         <v>0.9935064935064936</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.669695138931274</v>
+        <v>0.4867086410522461</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F15" t="n">
         <v>0.9935064935064936</v>
@@ -958,11 +958,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9998310810810811</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -974,28 +974,343 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>2.459268569946289</v>
+        <v>1.127304553985596</v>
       </c>
       <c r="E16" t="n">
+        <v>0.9967124678275436</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03718662261962891</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9804397703729418</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.06055116653442383</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9804280526546304</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.06001806259155273</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9804441893856517</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8900933265686035</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9983593504958139</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.469369411468506</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.90601921081543</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.073341608047485</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9950995611895129</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.492615699768066</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9967253463310086</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.971936702728271</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.9967368878519636</v>
       </c>
-      <c r="F16" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H16" t="n">
+      <c r="F25" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H25" t="n">
         <v>0.9998310810810811</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
         </is>
@@ -1012,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,17 +1385,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.142980337142944</v>
+        <v>2.815093755722046</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
@@ -1089,11 +1404,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998310810810811</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1420,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1519787311553955</v>
+        <v>1.426376581192017</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
         <v>0.9935064935064936</v>
@@ -1124,11 +1439,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998310810810811</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -1140,17 +1455,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1360764503479004</v>
+        <v>2.55407977104187</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9918326672831579</v>
+        <v>0.9983535762483131</v>
       </c>
       <c r="F4" t="n">
         <v>0.9935064935064936</v>
@@ -1159,11 +1474,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9936655405405406</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1490,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.316514253616333</v>
+        <v>0.1134634017944336</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F5" t="n">
         <v>0.9935064935064936</v>
@@ -1194,11 +1509,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -1210,14 +1525,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4219343662261963</v>
+        <v>0.07774615287780762</v>
       </c>
       <c r="E6" t="n">
         <v>0.9983552409841592</v>
@@ -1229,11 +1544,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1560,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>1.122652053833008</v>
+        <v>0.167536735534668</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9967124678275436</v>
+        <v>0.9983535762483131</v>
       </c>
       <c r="F7" t="n">
         <v>0.9935064935064936</v>
@@ -1264,11 +1579,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.9999155405405405</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
     </row>
@@ -1280,30 +1595,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05379128456115723</v>
+        <v>0.08736753463745117</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F8" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G8" t="n">
-        <v>0.986977845425334</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -1315,30 +1630,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08011054992675781</v>
+        <v>0.1757090091705322</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F9" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.986977845425334</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9863175675675676</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -1350,30 +1665,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06212043762207031</v>
+        <v>0.2211108207702637</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9804441893856517</v>
+        <v>0.9967071524966261</v>
       </c>
       <c r="F10" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G10" t="n">
-        <v>0.986977845425334</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9863175675675676</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1700,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.096622705459595</v>
+        <v>0.1147856712341309</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9885883726830831</v>
       </c>
       <c r="F11" t="n">
         <v>0.9935064935064936</v>
@@ -1404,11 +1719,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -1420,17 +1735,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.609349012374878</v>
+        <v>0.08343935012817383</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9918380364236208</v>
       </c>
       <c r="F12" t="n">
         <v>0.9935064935064936</v>
@@ -1439,11 +1754,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.9998310810810811</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -1455,17 +1770,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>2.971560955047607</v>
+        <v>0.1888899803161621</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9983535762483131</v>
+        <v>0.9918326672831579</v>
       </c>
       <c r="F13" t="n">
         <v>0.9935064935064936</v>
@@ -1474,11 +1789,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.9936655405405406</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1805,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1.180825710296631</v>
+        <v>0.2196180820465088</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F14" t="n">
         <v>0.9935064935064936</v>
@@ -1513,7 +1828,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
     </row>
@@ -1525,17 +1840,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.669695138931274</v>
+        <v>0.4867086410522461</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F15" t="n">
         <v>0.9935064935064936</v>
@@ -1544,11 +1859,11 @@
         <v>0.9934996412139632</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9998310810810811</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -1560,28 +1875,343 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>2.459268569946289</v>
+        <v>1.127304553985596</v>
       </c>
       <c r="E16" t="n">
+        <v>0.9967124678275436</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03718662261962891</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9804397703729418</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.06055116653442383</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9804280526546304</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.06001806259155273</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9804441893856517</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8900933265686035</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9983593504958139</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.469369411468506</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.90601921081543</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.073341608047485</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9950995611895129</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.492615699768066</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9967253463310086</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.971936702728271</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.9967368878519636</v>
       </c>
-      <c r="F16" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H16" t="n">
+      <c r="F25" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H25" t="n">
         <v>0.9998310810810811</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>{'cv': 3}</t>
         </is>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,17 +457,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_Accuracy</t>
+          <t>Test_R2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_F1</t>
+          <t>Test_RMSE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_AUC</t>
+          <t>Test_MAE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,30 +491,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.815093755722046</v>
+        <v>2.596037626266479</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.991165133416164</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,30 +526,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.426376581192017</v>
+        <v>1.166927576065063</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9915514893368013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,30 +561,30 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.55407977104187</v>
+        <v>2.238911151885986</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9983535762483131</v>
+        <v>0.9918184774008527</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,30 +596,30 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1134634017944336</v>
+        <v>0.0916285514831543</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9884016004359877</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9999155405405405</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,30 +631,30 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07774615287780762</v>
+        <v>0.09849262237548828</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9891276364518466</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9999155405405405</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,135 +666,135 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>0.167536735534668</v>
+        <v>0.1757726669311523</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9983535762483131</v>
+        <v>0.9888184370756603</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9879219094649494</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9934996412139632</v>
+        <v>2.165749660258334</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9999155405405405</v>
+        <v>1.344318181818182</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08736753463745117</v>
+        <v>0.3363256454467773</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.9493173645748553</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9934996412139632</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9888513513513514</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1757090091705322</v>
+        <v>0.6418373584747314</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9593934708973952</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9934996412139632</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9888513513513514</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2211108207702637</v>
+        <v>1.121366262435913</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9967071524966261</v>
+        <v>0.9663252049059585</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9934996412139632</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,30 +806,30 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1147856712341309</v>
+        <v>0.05839180946350098</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9998310810810811</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,30 +841,30 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08343935012817383</v>
+        <v>0.1200497150421143</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9998310810810811</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,443 +876,863 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1888899803161621</v>
+        <v>0.1213326454162598</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9918326672831579</v>
+        <v>0.9829335526451433</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9936655405405406</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2196180820465088</v>
+        <v>0.1164255142211914</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.909534101018917</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9133644072758389</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.800391268359031</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9998310810810811</v>
+        <v>4.193312097150674</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4867086410522461</v>
+        <v>0.07103991508483887</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9087605182651902</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9133644072815305</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.8003912681685</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4.193312096705474</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>1.127304553985596</v>
+        <v>0.1252851486206055</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9967124678275436</v>
+        <v>0.909045741479711</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9128511910101398</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.817546224259836</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>4.201707106444708</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03718662261962891</v>
+        <v>0.04096603393554688</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.9095314697018355</v>
       </c>
       <c r="F17" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9133925467063826</v>
       </c>
       <c r="G17" t="n">
-        <v>0.986977845425334</v>
+        <v>5.799449201953228</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9863175675675676</v>
+        <v>4.192818052928173</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.06055116653442383</v>
+        <v>0.05547475814819336</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.9087547686315594</v>
       </c>
       <c r="F18" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9133935968581072</v>
       </c>
       <c r="G18" t="n">
-        <v>0.986977845425334</v>
+        <v>5.799414041468699</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9863175675675676</v>
+        <v>4.192899764404125</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06001806259155273</v>
+        <v>0.08036041259765625</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9804441893856517</v>
+        <v>0.9090587832930842</v>
       </c>
       <c r="F19" t="n">
-        <v>0.987012987012987</v>
+        <v>0.913146287430656</v>
       </c>
       <c r="G19" t="n">
-        <v>0.986977845425334</v>
+        <v>5.807688414253744</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9863175675675676</v>
+        <v>4.197174702000158</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8900933265686035</v>
+        <v>0.0965423583984375</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.909533215133945</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.469369411468506</v>
+        <v>0.1260969638824463</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9087632939524625</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>2.90601921081543</v>
+        <v>0.2260673046112061</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9983535762483131</v>
+        <v>0.9090849528753845</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9131240810741543</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.808430808292843</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>4.197240504719623</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>1.073341608047485</v>
+        <v>0.7079942226409912</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9962821294270688</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9978246390639918</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9191254197681974</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.6382677938619158</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.492615699768066</v>
+        <v>1.160781383514404</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9974229884587255</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>1.971936702728271</v>
+        <v>2.040958404541016</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9967368878519636</v>
+        <v>0.9978558588089712</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.5017249584198</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9965485258873344</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.4978578090667725</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9974346204770498</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.7781908512115479</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9977164520836048</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5.712222814559937</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9959430744288776</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.613202571868896</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9967680026539419</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4.955340147018433</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9969284949233164</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.25133228302002</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9914238516975447</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9920354917748463</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.758687177428648</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.129233766233765</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.473863124847412</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9918212871921988</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.109712337662338</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4.299732208251953</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9918118579963269</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.109712337662338</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.444255590438843</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9911019302061744</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.9923490394853252</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.723721485354504</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.110294250898904</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.722037076950073</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9916725619279564</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.068923415563526</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.804654598236084</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.991650272801923</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.068923415563526</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1358,17 +1778,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_Accuracy</t>
+          <t>Test_R2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_F1</t>
+          <t>Test_RMSE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_AUC</t>
+          <t>Test_MAE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1380,7 +1800,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1392,30 +1812,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.815093755722046</v>
+        <v>2.596037626266479</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.991165133416164</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1427,30 +1847,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.426376581192017</v>
+        <v>1.166927576065063</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9915514893368013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1462,30 +1882,30 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.55407977104187</v>
+        <v>2.238911151885986</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9983535762483131</v>
+        <v>0.9918184774008527</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.991777204955937</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.786976524979942</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>1.198261096007184</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1497,30 +1917,30 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1134634017944336</v>
+        <v>0.0916285514831543</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9884016004359877</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9999155405405405</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1532,30 +1952,30 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07774615287780762</v>
+        <v>0.09849262237548828</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9891276364518466</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9999155405405405</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1567,135 +1987,135 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>0.167536735534668</v>
+        <v>0.1757726669311523</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9983535762483131</v>
+        <v>0.9888184370756603</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9879219094649494</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9934996412139632</v>
+        <v>2.165749660258334</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9999155405405405</v>
+        <v>1.344318181818182</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08736753463745117</v>
+        <v>0.3363256454467773</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.9493173645748553</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9934996412139632</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9888513513513514</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1757090091705322</v>
+        <v>0.6418373584747314</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9593934708973952</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9934996412139632</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9888513513513514</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2211108207702637</v>
+        <v>1.121366262435913</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9967071524966261</v>
+        <v>0.9663252049059585</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9776640607919219</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9934996412139632</v>
+        <v>2.945175805228017</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>1.933262226803274</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1707,30 +2127,30 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1147856712341309</v>
+        <v>0.05839180946350098</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9885883726830831</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9998310810810811</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1742,30 +2162,30 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08343935012817383</v>
+        <v>0.1200497150421143</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9918380364236208</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9998310810810811</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1777,443 +2197,863 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1888899803161621</v>
+        <v>0.1213326454162598</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9918326672831579</v>
+        <v>0.9829335526451433</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9936655405405406</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2196180820465088</v>
+        <v>0.1164255142211914</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.909534101018917</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9133644072758389</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.800391268359031</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9998310810810811</v>
+        <v>4.193312097150674</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4867086410522461</v>
+        <v>0.07103991508483887</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9087605182651902</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9133644072815305</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.8003912681685</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4.193312096705474</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>1.127304553985596</v>
+        <v>0.1252851486206055</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9967124678275436</v>
+        <v>0.909045741479711</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9128511910101398</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.817546224259836</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>4.201707106444708</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.7, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03718662261962891</v>
+        <v>0.04096603393554688</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9804397703729418</v>
+        <v>0.9095314697018355</v>
       </c>
       <c r="F17" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9133925467063826</v>
       </c>
       <c r="G17" t="n">
-        <v>0.986977845425334</v>
+        <v>5.799449201953228</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9863175675675676</v>
+        <v>4.192818052928173</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.06055116653442383</v>
+        <v>0.05547475814819336</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9804280526546304</v>
+        <v>0.9087547686315594</v>
       </c>
       <c r="F18" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9133935968581072</v>
       </c>
       <c r="G18" t="n">
-        <v>0.986977845425334</v>
+        <v>5.799414041468699</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9863175675675676</v>
+        <v>4.192899764404125</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06001806259155273</v>
+        <v>0.08036041259765625</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9804441893856517</v>
+        <v>0.9090587832930842</v>
       </c>
       <c r="F19" t="n">
-        <v>0.987012987012987</v>
+        <v>0.913146287430656</v>
       </c>
       <c r="G19" t="n">
-        <v>0.986977845425334</v>
+        <v>5.807688414253744</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9863175675675676</v>
+        <v>4.197174702000158</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8900933265686035</v>
+        <v>0.0965423583984375</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.909533215133945</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.469369411468506</v>
+        <v>0.1260969638824463</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9087632939524625</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9133122243111836</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.802137871795419</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>4.193872563312008</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>2.90601921081543</v>
+        <v>0.2260673046112061</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9983535762483131</v>
+        <v>0.9090849528753845</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9131240810741543</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9934996412139632</v>
+        <v>5.808430808292843</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>4.197240504719623</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>1.073341608047485</v>
+        <v>0.7079942226409912</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9950995611895129</v>
+        <v>0.9962821294270688</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9978246390639918</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9191254197681974</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.6382677938619158</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.492615699768066</v>
+        <v>1.160781383514404</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.9974229884587255</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>1.971936702728271</v>
+        <v>2.040958404541016</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9967368878519636</v>
+        <v>0.9978558588089712</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9971987634537949</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9934996412139632</v>
+        <v>1.042999274810321</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9998310810810811</v>
+        <v>0.634718037848133</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.5017249584198</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9965485258873344</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.4978578090667725</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9974346204770498</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.7781908512115479</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9977164520836048</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5.712222814559937</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9959430744288776</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.613202571868896</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9967680026539419</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4.955340147018433</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9969284949233164</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.25133228302002</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9914238516975447</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9920354917748463</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.758687177428648</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.129233766233765</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.473863124847412</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9918212871921988</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.109712337662338</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4.299732208251953</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9918118579963269</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.109712337662338</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.444255590438843</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9911019302061744</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.9923490394853252</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.723721485354504</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.110294250898904</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>{'cv': 3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.722037076950073</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9916725619279564</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.068923415563526</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.804654598236084</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.991650272801923</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.068923415563526</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,29 +458,44 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Test_Accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test_F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test_AUC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Params</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Test_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Test_RMSE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Test_MAE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Best_Params</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,30 +507,33 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.596037626266479</v>
+        <v>10.47228741645813</v>
       </c>
       <c r="E2" t="n">
-        <v>0.991165133416164</v>
+        <v>0.9259372549984396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G2" t="n">
-        <v>1.786976524979942</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H2" t="n">
-        <v>1.198261096007184</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
-        </is>
-      </c>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,65 +545,71 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.166927576065063</v>
+        <v>12.85234880447388</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9915514893368013</v>
+        <v>0.9296254451309558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G3" t="n">
-        <v>1.786976524979942</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H3" t="n">
-        <v>1.198261096007184</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
-        </is>
-      </c>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.238911151885986</v>
+        <v>0.3354244232177734</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9918184774008527</v>
+        <v>0.8998419434690367</v>
       </c>
       <c r="F4" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9254890678941312</v>
       </c>
       <c r="G4" t="n">
-        <v>1.786976524979942</v>
+        <v>0.8991261138706356</v>
       </c>
       <c r="H4" t="n">
-        <v>1.198261096007184</v>
+        <v>0.9601233380302046</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
-        </is>
-      </c>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,448 +618,487 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0916285514831543</v>
+        <v>0.3668956756591797</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9884016004359877</v>
+        <v>0.9008461098105501</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.9306674338319908</v>
       </c>
       <c r="G5" t="n">
-        <v>1.908331770496365</v>
+        <v>0.9049920684579351</v>
       </c>
       <c r="H5" t="n">
-        <v>1.312303784373733</v>
+        <v>0.9450958342365778</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
-        </is>
-      </c>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09849262237548828</v>
+        <v>220.4221472740173</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9891276364518466</v>
+        <v>0.8329028339735882</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G6" t="n">
-        <v>1.908331770496365</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H6" t="n">
-        <v>1.312303784373733</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
-        </is>
-      </c>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1757726669311523</v>
+        <v>404.337406873703</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9888184370756603</v>
+        <v>0.8406821430035827</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9879219094649494</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G7" t="n">
-        <v>2.165749660258334</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H7" t="n">
-        <v>1.344318181818182</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
-        </is>
-      </c>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3363256454467773</v>
+        <v>1.94414758682251</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9493173645748553</v>
+        <v>0.8013286401307914</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G8" t="n">
-        <v>2.945175805228017</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H8" t="n">
-        <v>1.933262226803274</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6418373584747314</v>
+        <v>2.169837713241577</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9593934708973952</v>
+        <v>0.81032050938439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G9" t="n">
-        <v>2.945175805228017</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H9" t="n">
-        <v>1.933262226803274</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.121366262435913</v>
+        <v>14.07042956352234</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9663252049059585</v>
+        <v>0.7318158655754914</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G10" t="n">
-        <v>2.945175805228017</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H10" t="n">
-        <v>1.933262226803274</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05839180946350098</v>
+        <v>29.15627408027649</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.7328819229288671</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9004199798826</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H11" t="n">
-        <v>1.388601264472551</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1200497150421143</v>
+        <v>0.1501247882843018</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.758522079737817</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9004199798826</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H12" t="n">
-        <v>1.388601264472551</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1213326454162598</v>
+        <v>0.2186179161071777</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9829335526451433</v>
+        <v>0.7588098200722057</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9004199798826</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H13" t="n">
-        <v>1.388601264472551</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1164255142211914</v>
+        <v>4.598600149154663</v>
       </c>
       <c r="E14" t="n">
-        <v>0.909534101018917</v>
+        <v>0.9280699341723085</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9133644072758389</v>
+        <v>0.950517836593786</v>
       </c>
       <c r="G14" t="n">
-        <v>5.800391268359031</v>
+        <v>0.932054070173397</v>
       </c>
       <c r="H14" t="n">
-        <v>4.193312097150674</v>
+        <v>0.9845430034684587</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
-        </is>
-      </c>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07103991508483887</v>
+        <v>8.56904125213623</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9087605182651902</v>
+        <v>0.928876610929035</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9133644072815305</v>
+        <v>0.9485040276179517</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8003912681685</v>
+        <v>0.9296640638468039</v>
       </c>
       <c r="H15" t="n">
-        <v>4.193312096705474</v>
+        <v>0.9831533618758581</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
-        </is>
-      </c>
+          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1252851486206055</v>
+        <v>42.96212124824524</v>
       </c>
       <c r="E16" t="n">
-        <v>0.909045741479711</v>
+        <v>0.9131605579577853</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9128511910101398</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G16" t="n">
-        <v>5.817546224259836</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H16" t="n">
-        <v>4.201707106444708</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
-        </is>
-      </c>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04096603393554688</v>
+        <v>56.19120001792908</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9095314697018355</v>
+        <v>0.9193219807675821</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9133925467063826</v>
+        <v>0.9413118527042578</v>
       </c>
       <c r="G17" t="n">
-        <v>5.799449201953228</v>
+        <v>0.9190787698855583</v>
       </c>
       <c r="H17" t="n">
-        <v>4.192818052928173</v>
+        <v>0.9801950104776356</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
-        </is>
-      </c>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1044,31 +1108,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05547475814819336</v>
+        <v>20.91527438163757</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9087547686315594</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.9133935968581072</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5.799414041468699</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.192899764404125</v>
-      </c>
+        <v>0.9401693017556561</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
-        </is>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9464218459082774</v>
+      </c>
+      <c r="K18" t="n">
+        <v>41.18949244604086</v>
+      </c>
+      <c r="L18" t="n">
+        <v>24.65244606562803</v>
       </c>
     </row>
     <row r="19">
@@ -1079,31 +1146,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08036041259765625</v>
+        <v>29.4542236328125</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9090587832930842</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.913146287430656</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5.807688414253744</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.197174702000158</v>
-      </c>
+        <v>0.9427502089343068</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
-        </is>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9464218459082774</v>
+      </c>
+      <c r="K19" t="n">
+        <v>41.18949244604086</v>
+      </c>
+      <c r="L19" t="n">
+        <v>24.65244606562803</v>
       </c>
     </row>
     <row r="20">
@@ -1114,31 +1184,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0965423583984375</v>
+        <v>8.565767526626587</v>
       </c>
       <c r="E20" t="n">
-        <v>0.909533215133945</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.9133122243111836</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5.802137871795419</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.193872563312008</v>
-      </c>
+        <v>0.7655546082141634</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
-        </is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7674557752723191</v>
+      </c>
+      <c r="K20" t="n">
+        <v>85.81147085279127</v>
+      </c>
+      <c r="L20" t="n">
+        <v>53.21821058688148</v>
       </c>
     </row>
     <row r="21">
@@ -1149,31 +1222,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1260969638824463</v>
+        <v>13.60066533088684</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9087632939524625</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9133122243111836</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5.802137871795419</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4.193872563312008</v>
-      </c>
+        <v>0.7743430854514228</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
-        </is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.7674557752723191</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.81147085279127</v>
+      </c>
+      <c r="L21" t="n">
+        <v>53.21821058688148</v>
       </c>
     </row>
     <row r="22">
@@ -1184,31 +1260,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2260673046112061</v>
+        <v>35.55732083320618</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9090849528753845</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.9131240810741543</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5.808430808292843</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.197240504719623</v>
-      </c>
+        <v>0.5811946043919515</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
-        </is>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.6046477401790427</v>
+      </c>
+      <c r="K22" t="n">
+        <v>111.88830113121</v>
+      </c>
+      <c r="L22" t="n">
+        <v>68.50656765299343</v>
       </c>
     </row>
     <row r="23">
@@ -1219,31 +1298,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7079942226409912</v>
+        <v>63.2348096370697</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9962821294270688</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9978246390639918</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.9191254197681974</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.6382677938619158</v>
-      </c>
+        <v>0.591339866408126</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.6046477401790427</v>
+      </c>
+      <c r="K23" t="n">
+        <v>111.88830113121</v>
+      </c>
+      <c r="L23" t="n">
+        <v>68.50656765299343</v>
       </c>
     </row>
     <row r="24">
@@ -1254,31 +1336,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>1.160781383514404</v>
+        <v>2.125401735305786</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9974229884587255</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.9971987634537949</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.042999274810321</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.634718037848133</v>
-      </c>
+        <v>0.5765101226696233</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
-        </is>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.6188887513166017</v>
+      </c>
+      <c r="K24" t="n">
+        <v>109.8546514923718</v>
+      </c>
+      <c r="L24" t="n">
+        <v>77.9838465335159</v>
       </c>
     </row>
     <row r="25">
@@ -1289,31 +1374,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.040958404541016</v>
+        <v>2.494043350219727</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9978558588089712</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.9971987634537949</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.042999274810321</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.634718037848133</v>
-      </c>
+        <v>0.5896721788986901</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
-        </is>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.6188887513166017</v>
+      </c>
+      <c r="K25" t="n">
+        <v>109.8546514923718</v>
+      </c>
+      <c r="L25" t="n">
+        <v>77.9838465335159</v>
       </c>
     </row>
     <row r="26">
@@ -1324,31 +1412,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>3.5017249584198</v>
+        <v>3.862469911575317</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9965485258873344</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.5851734726150313</v>
-      </c>
+        <v>0.3877192325497514</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3883092387008059</v>
+      </c>
+      <c r="K26" t="n">
+        <v>139.1741339734124</v>
+      </c>
+      <c r="L26" t="n">
+        <v>104.7576252565122</v>
       </c>
     </row>
     <row r="27">
@@ -1359,31 +1450,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4978578090667725</v>
+        <v>8.251466751098633</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9974346204770498</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.5851734726150313</v>
-      </c>
+        <v>0.3876193930187798</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3883092387008058</v>
+      </c>
+      <c r="K27" t="n">
+        <v>139.1741339734124</v>
+      </c>
+      <c r="L27" t="n">
+        <v>104.7576252565122</v>
       </c>
     </row>
     <row r="28">
@@ -1394,31 +1488,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7781908512115479</v>
+        <v>35.90342903137207</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9977164520836048</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.5851734726150313</v>
-      </c>
+        <v>0.387644777846075</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.3881966456514309</v>
+      </c>
+      <c r="K28" t="n">
+        <v>139.1869421765973</v>
+      </c>
+      <c r="L28" t="n">
+        <v>104.7894206132718</v>
       </c>
     </row>
     <row r="29">
@@ -1429,31 +1526,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>5.712222814559937</v>
+        <v>37.20738410949707</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9959430744288776</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.7230709546390158</v>
-      </c>
+        <v>0.3875372233114082</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3881966456514309</v>
+      </c>
+      <c r="K29" t="n">
+        <v>139.1869421765973</v>
+      </c>
+      <c r="L29" t="n">
+        <v>104.7894206132718</v>
       </c>
     </row>
     <row r="30">
@@ -1464,31 +1564,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>2.613202571868896</v>
+        <v>7.145894289016724</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9967680026539419</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.7230709546390158</v>
-      </c>
+        <v>0.387611695296131</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.3880771257287021</v>
+      </c>
+      <c r="K30" t="n">
+        <v>139.2005370678847</v>
+      </c>
+      <c r="L30" t="n">
+        <v>104.7953480310862</v>
       </c>
     </row>
     <row r="31">
@@ -1499,31 +1602,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>4.955340147018433</v>
+        <v>9.151961088180542</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9969284949233164</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.7230709546390158</v>
-      </c>
+        <v>0.3875075500335963</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.3880771257287021</v>
+      </c>
+      <c r="K31" t="n">
+        <v>139.2005370678847</v>
+      </c>
+      <c r="L31" t="n">
+        <v>104.7953480310862</v>
       </c>
     </row>
     <row r="32">
@@ -1534,31 +1640,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>1.25133228302002</v>
+        <v>14.13356161117554</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9914238516975447</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.9920354917748463</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.758687177428648</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.129233766233765</v>
-      </c>
+        <v>0.9516741927489486</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9579448551240813</v>
+      </c>
+      <c r="K32" t="n">
+        <v>36.49237538596583</v>
+      </c>
+      <c r="L32" t="n">
+        <v>22.45833191275022</v>
       </c>
     </row>
     <row r="33">
@@ -1569,31 +1678,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.473863124847412</v>
+        <v>27.21209073066711</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9918212871921988</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.9923259444363434</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.726321122047857</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.109712337662338</v>
-      </c>
+        <v>0.9555987839182706</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9572399750110738</v>
+      </c>
+      <c r="K33" t="n">
+        <v>36.79692623075351</v>
+      </c>
+      <c r="L33" t="n">
+        <v>22.72192192440616</v>
       </c>
     </row>
     <row r="34">
@@ -1604,31 +1716,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>4.299732208251953</v>
+        <v>3.663124322891235</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9918118579963269</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.9923259444363434</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.726321122047857</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.109712337662338</v>
-      </c>
+        <v>0.9536898136138916</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.9616894721984863</v>
+      </c>
+      <c r="K34" t="n">
+        <v>34.82984924316406</v>
+      </c>
+      <c r="L34" t="n">
+        <v>21.44558906555176</v>
       </c>
     </row>
     <row r="35">
@@ -1639,31 +1754,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1.444255590438843</v>
+        <v>2.157824516296387</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9911019302061744</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.9923490394853252</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.723721485354504</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.110294250898904</v>
-      </c>
+        <v>0.9580495715141296</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
-        </is>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.9616894721984863</v>
+      </c>
+      <c r="K35" t="n">
+        <v>34.82984924316406</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.44558906555176</v>
       </c>
     </row>
     <row r="36">
@@ -1674,31 +1792,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>1.722037076950073</v>
+        <v>5.985766887664795</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9916725619279564</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.9927500166340855</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.677944607223844</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.068923415563526</v>
-      </c>
+        <v>0.9528316417478734</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
-        </is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.960381630171073</v>
+      </c>
+      <c r="K36" t="n">
+        <v>35.41937290682655</v>
+      </c>
+      <c r="L36" t="n">
+        <v>22.46264210836679</v>
       </c>
     </row>
     <row r="37">
@@ -1709,31 +1830,186 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.750111818313599</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9563572448117584</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.960381630171073</v>
+      </c>
+      <c r="K37" t="n">
+        <v>35.41937290682655</v>
+      </c>
+      <c r="L37" t="n">
+        <v>22.46264210836679</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>14.99010396003723</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.944227051557548</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9498091161774663</v>
+      </c>
+      <c r="K38" t="n">
+        <v>39.86621353453122</v>
+      </c>
+      <c r="L38" t="n">
+        <v>23.61910385500575</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>27.69755601882935</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9471150885859518</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.9502406638435245</v>
+      </c>
+      <c r="K39" t="n">
+        <v>39.69445612706919</v>
+      </c>
+      <c r="L39" t="n">
+        <v>23.63055235903337</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Stacking</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>10</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2.804654598236084</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.991650272801923</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.9927500166340855</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.677944607223844</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.068923415563526</v>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>35.37915015220642</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9451094020818683</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9503855355387685</v>
+      </c>
+      <c r="K40" t="n">
+        <v>39.63662984415944</v>
+      </c>
+      <c r="L40" t="n">
+        <v>23.90459760874549</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>50.37099456787109</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9477025989384391</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.9503855355387685</v>
+      </c>
+      <c r="K41" t="n">
+        <v>39.63662984415944</v>
+      </c>
+      <c r="L41" t="n">
+        <v>23.90459760874549</v>
       </c>
     </row>
   </sheetData>
@@ -1747,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1778,29 +2054,44 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Test_Accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test_F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test_AUC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Params</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Test_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Test_RMSE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Test_MAE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Best_Params</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1812,30 +2103,33 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.596037626266479</v>
+        <v>10.47228741645813</v>
       </c>
       <c r="E2" t="n">
-        <v>0.991165133416164</v>
+        <v>0.9259372549984396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G2" t="n">
-        <v>1.786976524979942</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H2" t="n">
-        <v>1.198261096007184</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
-        </is>
-      </c>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1847,65 +2141,71 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.166927576065063</v>
+        <v>12.85234880447388</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9915514893368013</v>
+        <v>0.9296254451309558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G3" t="n">
-        <v>1.786976524979942</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H3" t="n">
-        <v>1.198261096007184</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
-        </is>
-      </c>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.238911151885986</v>
+        <v>0.3354244232177734</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9918184774008527</v>
+        <v>0.8998419434690367</v>
       </c>
       <c r="F4" t="n">
-        <v>0.991777204955937</v>
+        <v>0.9254890678941312</v>
       </c>
       <c r="G4" t="n">
-        <v>1.786976524979942</v>
+        <v>0.8991261138706356</v>
       </c>
       <c r="H4" t="n">
-        <v>1.198261096007184</v>
+        <v>0.9601233380302046</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
-        </is>
-      </c>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1914,447 +2214,1170 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0916285514831543</v>
+        <v>0.3668956756591797</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9884016004359877</v>
+        <v>0.9008461098105501</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.9306674338319908</v>
       </c>
       <c r="G5" t="n">
-        <v>1.908331770496365</v>
+        <v>0.9049920684579351</v>
       </c>
       <c r="H5" t="n">
-        <v>1.312303784373733</v>
+        <v>0.9450958342365778</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
-        </is>
-      </c>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09849262237548828</v>
+        <v>220.4221472740173</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9891276364518466</v>
+        <v>0.8329028339735882</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G6" t="n">
-        <v>1.908331770496365</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H6" t="n">
-        <v>1.312303784373733</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
-        </is>
-      </c>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1757726669311523</v>
+        <v>404.337406873703</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9888184370756603</v>
+        <v>0.8406821430035827</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9879219094649494</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G7" t="n">
-        <v>2.165749660258334</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H7" t="n">
-        <v>1.344318181818182</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
-        </is>
-      </c>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3363256454467773</v>
+        <v>1.94414758682251</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9493173645748553</v>
+        <v>0.8013286401307914</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G8" t="n">
-        <v>2.945175805228017</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H8" t="n">
-        <v>1.933262226803274</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6418373584747314</v>
+        <v>2.169837713241577</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9593934708973952</v>
+        <v>0.81032050938439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.8765822784810127</v>
       </c>
       <c r="G9" t="n">
-        <v>2.945175805228017</v>
+        <v>0.8213289652983488</v>
       </c>
       <c r="H9" t="n">
-        <v>1.933262226803274</v>
+        <v>0.91744187621938</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.121366262435913</v>
+        <v>14.07042956352234</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9663252049059585</v>
+        <v>0.7318158655754914</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9776640607919219</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G10" t="n">
-        <v>2.945175805228017</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H10" t="n">
-        <v>1.933262226803274</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
-        </is>
-      </c>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05839180946350098</v>
+        <v>29.15627408027649</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.7328819229288671</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.8285385500575374</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9004199798826</v>
+        <v>0.7381846049166845</v>
       </c>
       <c r="H11" t="n">
-        <v>1.388601264472551</v>
+        <v>0.8583667533781343</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
+          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1200497150421143</v>
+        <v>0.1501247882843018</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.758522079737817</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9004199798826</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H12" t="n">
-        <v>1.388601264472551</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1213326454162598</v>
+        <v>0.2186179161071777</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9829335526451433</v>
+        <v>0.7588098200722057</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.8201956271576525</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9004199798826</v>
+        <v>0.7654782974318119</v>
       </c>
       <c r="H13" t="n">
-        <v>1.388601264472551</v>
+        <v>0.8779147698533132</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1164255142211914</v>
+        <v>4.598600149154663</v>
       </c>
       <c r="E14" t="n">
-        <v>0.909534101018917</v>
+        <v>0.9280699341723085</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9133644072758389</v>
+        <v>0.950517836593786</v>
       </c>
       <c r="G14" t="n">
-        <v>5.800391268359031</v>
+        <v>0.932054070173397</v>
       </c>
       <c r="H14" t="n">
-        <v>4.193312097150674</v>
+        <v>0.9845430034684587</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
-        </is>
-      </c>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07103991508483887</v>
+        <v>8.56904125213623</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9087605182651902</v>
+        <v>0.928876610929035</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9133644072815305</v>
+        <v>0.9485040276179517</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8003912681685</v>
+        <v>0.9296640638468039</v>
       </c>
       <c r="H15" t="n">
-        <v>4.193312096705474</v>
+        <v>0.9831533618758581</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
-        </is>
-      </c>
+          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1252851486206055</v>
+        <v>42.96212124824524</v>
       </c>
       <c r="E16" t="n">
-        <v>0.909045741479711</v>
+        <v>0.9131605579577853</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9128511910101398</v>
+        <v>0.939873417721519</v>
       </c>
       <c r="G16" t="n">
-        <v>5.817546224259836</v>
+        <v>0.9169917656074629</v>
       </c>
       <c r="H16" t="n">
-        <v>4.201707106444708</v>
+        <v>0.9807870872172846</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
-        </is>
-      </c>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>56.19120001792908</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9193219807675821</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9413118527042578</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9190787698855583</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9801950104776356</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CV_Folds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tuning_Time_sec</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Best_CV_Score</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Test_Accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test_F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test_AUC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Params</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Test_R2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Test_RMSE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Test_MAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.91527438163757</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9401693017556561</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9464218459082774</v>
+      </c>
+      <c r="K2" t="n">
+        <v>41.18949244604086</v>
+      </c>
+      <c r="L2" t="n">
+        <v>24.65244606562803</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>29.4542236328125</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9427502089343068</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9464218459082774</v>
+      </c>
+      <c r="K3" t="n">
+        <v>41.18949244604086</v>
+      </c>
+      <c r="L3" t="n">
+        <v>24.65244606562803</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.565767526626587</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7655546082141634</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7674557752723191</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.81147085279127</v>
+      </c>
+      <c r="L4" t="n">
+        <v>53.21821058688148</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13.60066533088684</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7743430854514228</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7674557752723191</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.81147085279127</v>
+      </c>
+      <c r="L5" t="n">
+        <v>53.21821058688148</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>35.55732083320618</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5811946043919515</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6046477401790427</v>
+      </c>
+      <c r="K6" t="n">
+        <v>111.88830113121</v>
+      </c>
+      <c r="L6" t="n">
+        <v>68.50656765299343</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>63.2348096370697</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.591339866408126</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6046477401790427</v>
+      </c>
+      <c r="K7" t="n">
+        <v>111.88830113121</v>
+      </c>
+      <c r="L7" t="n">
+        <v>68.50656765299343</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.125401735305786</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5765101226696233</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6188887513166017</v>
+      </c>
+      <c r="K8" t="n">
+        <v>109.8546514923718</v>
+      </c>
+      <c r="L8" t="n">
+        <v>77.9838465335159</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.494043350219727</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5896721788986901</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6188887513166017</v>
+      </c>
+      <c r="K9" t="n">
+        <v>109.8546514923718</v>
+      </c>
+      <c r="L9" t="n">
+        <v>77.9838465335159</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.862469911575317</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3877192325497514</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3883092387008059</v>
+      </c>
+      <c r="K10" t="n">
+        <v>139.1741339734124</v>
+      </c>
+      <c r="L10" t="n">
+        <v>104.7576252565122</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.251466751098633</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3876193930187798</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3883092387008058</v>
+      </c>
+      <c r="K11" t="n">
+        <v>139.1741339734124</v>
+      </c>
+      <c r="L11" t="n">
+        <v>104.7576252565122</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Lasso</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>35.90342903137207</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.387644777846075</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3881966456514309</v>
+      </c>
+      <c r="K12" t="n">
+        <v>139.1869421765973</v>
+      </c>
+      <c r="L12" t="n">
+        <v>104.7894206132718</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>37.20738410949707</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3875372233114082</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3881966456514309</v>
+      </c>
+      <c r="K13" t="n">
+        <v>139.1869421765973</v>
+      </c>
+      <c r="L13" t="n">
+        <v>104.7894206132718</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.145894289016724</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.387611695296131</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.3880771257287021</v>
+      </c>
+      <c r="K14" t="n">
+        <v>139.2005370678847</v>
+      </c>
+      <c r="L14" t="n">
+        <v>104.7953480310862</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9.151961088180542</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3875075500335963</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3880771257287021</v>
+      </c>
+      <c r="K15" t="n">
+        <v>139.2005370678847</v>
+      </c>
+      <c r="L15" t="n">
+        <v>104.7953480310862</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>14.13356161117554</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9516741927489486</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9579448551240813</v>
+      </c>
+      <c r="K16" t="n">
+        <v>36.49237538596583</v>
+      </c>
+      <c r="L16" t="n">
+        <v>22.45833191275022</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04096603393554688</v>
+        <v>27.21209073066711</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9095314697018355</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9133925467063826</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5.799449201953228</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.192818052928173</v>
-      </c>
+        <v>0.9555987839182706</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
-        </is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9572399750110738</v>
+      </c>
+      <c r="K17" t="n">
+        <v>36.79692623075351</v>
+      </c>
+      <c r="L17" t="n">
+        <v>22.72192192440616</v>
       </c>
     </row>
     <row r="18">
@@ -2365,31 +3388,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05547475814819336</v>
+        <v>3.663124322891235</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9087547686315594</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.9133935968581072</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5.799414041468699</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.192899764404125</v>
-      </c>
+        <v>0.9536898136138916</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
-        </is>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9616894721984863</v>
+      </c>
+      <c r="K18" t="n">
+        <v>34.82984924316406</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.44558906555176</v>
       </c>
     </row>
     <row r="19">
@@ -2400,31 +3426,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08036041259765625</v>
+        <v>2.157824516296387</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9090587832930842</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.913146287430656</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5.807688414253744</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.197174702000158</v>
-      </c>
+        <v>0.9580495715141296</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
-        </is>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9616894721984863</v>
+      </c>
+      <c r="K19" t="n">
+        <v>34.82984924316406</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21.44558906555176</v>
       </c>
     </row>
     <row r="20">
@@ -2435,31 +3464,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0965423583984375</v>
+        <v>5.985766887664795</v>
       </c>
       <c r="E20" t="n">
-        <v>0.909533215133945</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.9133122243111836</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5.802137871795419</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.193872563312008</v>
-      </c>
+        <v>0.9528316417478734</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
-        </is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.960381630171073</v>
+      </c>
+      <c r="K20" t="n">
+        <v>35.41937290682655</v>
+      </c>
+      <c r="L20" t="n">
+        <v>22.46264210836679</v>
       </c>
     </row>
     <row r="21">
@@ -2470,31 +3502,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1260969638824463</v>
+        <v>5.750111818313599</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9087632939524625</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9133122243111836</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5.802137871795419</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4.193872563312008</v>
-      </c>
+        <v>0.9563572448117584</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
-        </is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.960381630171073</v>
+      </c>
+      <c r="K21" t="n">
+        <v>35.41937290682655</v>
+      </c>
+      <c r="L21" t="n">
+        <v>22.46264210836679</v>
       </c>
     </row>
     <row r="22">
@@ -2505,31 +3540,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2260673046112061</v>
+        <v>14.99010396003723</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9090849528753845</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.9131240810741543</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5.808430808292843</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.197240504719623</v>
-      </c>
+        <v>0.944227051557548</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
-        </is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9498091161774663</v>
+      </c>
+      <c r="K22" t="n">
+        <v>39.86621353453122</v>
+      </c>
+      <c r="L22" t="n">
+        <v>23.61910385500575</v>
       </c>
     </row>
     <row r="23">
@@ -2540,31 +3578,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7079942226409912</v>
+        <v>27.69755601882935</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9962821294270688</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9978246390639918</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.9191254197681974</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.6382677938619158</v>
-      </c>
+        <v>0.9471150885859518</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
+          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9502406638435245</v>
+      </c>
+      <c r="K23" t="n">
+        <v>39.69445612706919</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.63055235903337</v>
       </c>
     </row>
     <row r="24">
@@ -2575,31 +3616,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>1.160781383514404</v>
+        <v>35.37915015220642</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9974229884587255</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.9971987634537949</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.042999274810321</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.634718037848133</v>
-      </c>
+        <v>0.9451094020818683</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
-        </is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9503855355387685</v>
+      </c>
+      <c r="K24" t="n">
+        <v>39.63662984415944</v>
+      </c>
+      <c r="L24" t="n">
+        <v>23.90459760874549</v>
       </c>
     </row>
     <row r="25">
@@ -2610,451 +3654,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.040958404541016</v>
+        <v>50.37099456787109</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9978558588089712</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.9971987634537949</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.042999274810321</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.634718037848133</v>
-      </c>
+        <v>0.9477025989384391</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3.5017249584198</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.9965485258873344</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.5851734726150313</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.4978578090667725</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.9974346204770498</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.5851734726150313</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>10</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.7781908512115479</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.9977164520836048</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.9979915184339837</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.883167420157519</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.5851734726150313</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>5.712222814559937</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.9959430744288776</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.7230709546390158</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2.613202571868896</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.9967680026539419</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.7230709546390158</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4.955340147018433</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.9969284949233164</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.9971905430163311</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.044528533262776</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.7230709546390158</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1.25133228302002</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.9914238516975447</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.9920354917748463</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.758687177428648</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.129233766233765</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>5</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.473863124847412</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.9918212871921988</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.9923259444363434</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.726321122047857</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.109712337662338</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>10</v>
-      </c>
-      <c r="D34" t="n">
-        <v>4.299732208251953</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.9918118579963269</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.9923259444363434</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.726321122047857</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.109712337662338</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1.444255590438843</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.9911019302061744</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.9923490394853252</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.723721485354504</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.110294250898904</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>{'cv': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1.722037076950073</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.9916725619279564</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.9927500166340855</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.677944607223844</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.068923415563526</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
           <t>{'cv': 5}</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>10</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2.804654598236084</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.991650272801923</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.9927500166340855</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.677944607223844</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.068923415563526</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
+      <c r="J25" t="n">
+        <v>0.9503855355387685</v>
+      </c>
+      <c r="K25" t="n">
+        <v>39.63662984415944</v>
+      </c>
+      <c r="L25" t="n">
+        <v>23.90459760874549</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,23 +507,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.47228741645813</v>
+        <v>20.4457700252533</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9259372549984396</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9490794016110472</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9303364774002756</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9854205054555963</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -545,23 +545,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>12.85234880447388</v>
+        <v>29.11326050758362</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9296254451309558</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9490794016110472</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9303364774002756</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854205054555963</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -583,23 +583,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3354244232177734</v>
+        <v>0.5122740268707275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8998419434690367</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9254890678941312</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8991261138706356</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9601233380302046</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -621,23 +621,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3668956756591797</v>
+        <v>0.6788384914398193</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9008461098105501</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9306674338319908</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9049920684579351</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9450958342365778</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 6, 'max_features': None, 'max_depth': 6, 'criterion': 'entropy'}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -659,23 +659,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>220.4221472740173</v>
+        <v>167.733238697052</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8329028339735882</v>
+        <v>0.9996759964597205</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.9998444870665077</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.9998444843919962</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.9999999892512356</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -697,23 +697,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>404.337406873703</v>
+        <v>331.5528485774994</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8406821430035827</v>
+        <v>0.9996759945997233</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.9998444870665077</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.9998444843919962</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.9999999892512355</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -735,19 +735,19 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1.94414758682251</v>
+        <v>23.69982695579529</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.9825917846771556</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9843450313617749</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9843447819418814</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9992675254413582</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -773,19 +773,19 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.169837713241577</v>
+        <v>23.63667631149292</v>
       </c>
       <c r="E9" t="n">
-        <v>0.81032050938439</v>
+        <v>0.9837584121796732</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9843450313617749</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9843447819418814</v>
       </c>
       <c r="H9" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9992675254413582</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -811,23 +811,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>14.07042956352234</v>
+        <v>44.24955129623413</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7318158655754914</v>
+        <v>0.9998055964130637</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.9997926494220103</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.9997926459445896</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9999999785024709</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -849,23 +849,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>29.15627408027649</v>
+        <v>103.1700747013092</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7328819229288671</v>
+        <v>0.9997407969867332</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.9997926494220103</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.9997926459445896</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9999999785024709</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -880,30 +880,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1501247882843018</v>
+        <v>14.96656465530396</v>
       </c>
       <c r="E12" t="n">
-        <v>0.758522079737817</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8201956271576525</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7654782974318119</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8779147698533132</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -918,30 +918,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2186179161071777</v>
+        <v>38.96033000946045</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7588098200722057</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8201956271576525</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7654782974318119</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8779147698533132</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -956,30 +956,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>4.598600149154663</v>
+        <v>275.1872861385345</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9280699341723085</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.950517836593786</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.932054070173397</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9845430034684587</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -994,30 +994,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>8.56904125213623</v>
+        <v>328.0026791095734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.928876610929035</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9485040276179517</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9296640638468039</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9831533618758581</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1027,78 +1027,78 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>42.96212124824524</v>
+        <v>108.487827539444</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9131605579577853</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.939873417721519</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.9169917656074629</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.9807870872172846</v>
-      </c>
+        <v>0.9999515226287238</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9999752515704077</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.04775769396566595</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.01317099116795414</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>56.19120001792908</v>
+        <v>151.3269882202148</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9193219807675821</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9413118527042578</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9190787698855583</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.9801950104776356</v>
-      </c>
+        <v>0.9999602042730554</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9999752515704077</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.04775769396566595</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.01317099116795414</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1108,34 +1108,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>20.91527438163757</v>
+        <v>95.99473476409912</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9401693017556561</v>
+        <v>0.997705064162585</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="K18" t="n">
-        <v>41.18949244604086</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="L18" t="n">
-        <v>24.65244606562803</v>
+        <v>0.2439390274105945</v>
       </c>
     </row>
     <row r="19">
@@ -1146,34 +1146,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>29.4542236328125</v>
+        <v>161.5357649326324</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9427502089343068</v>
+        <v>0.9976930312457801</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="K19" t="n">
-        <v>41.18949244604086</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="L19" t="n">
-        <v>24.65244606562803</v>
+        <v>0.2439390274105945</v>
       </c>
     </row>
     <row r="20">
@@ -1184,34 +1184,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>8.565767526626587</v>
+        <v>22.92759561538696</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7655546082141634</v>
+        <v>0.9940702304082292</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="K20" t="n">
-        <v>85.81147085279127</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="L20" t="n">
-        <v>53.21821058688148</v>
+        <v>0.4629059086032067</v>
       </c>
     </row>
     <row r="21">
@@ -1222,34 +1222,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>13.60066533088684</v>
+        <v>22.38435125350952</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7743430854514228</v>
+        <v>0.9947256554325836</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="K21" t="n">
-        <v>85.81147085279127</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="L21" t="n">
-        <v>53.21821058688148</v>
+        <v>0.4629059086032067</v>
       </c>
     </row>
     <row r="22">
@@ -1260,34 +1260,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>35.55732083320618</v>
+        <v>0.4583749771118164</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5811946043919515</v>
+        <v>0.990098309686355</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.6046477401790427</v>
+        <v>0.990254957444855</v>
       </c>
       <c r="K22" t="n">
-        <v>111.88830113121</v>
+        <v>0.9476793014611543</v>
       </c>
       <c r="L22" t="n">
-        <v>68.50656765299343</v>
+        <v>0.7418452222906518</v>
       </c>
     </row>
     <row r="23">
@@ -1298,34 +1298,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>63.2348096370697</v>
+        <v>0.8081331253051758</v>
       </c>
       <c r="E23" t="n">
-        <v>0.591339866408126</v>
+        <v>0.9900987126467754</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.6046477401790427</v>
+        <v>0.9902550153826634</v>
       </c>
       <c r="K23" t="n">
-        <v>111.88830113121</v>
+        <v>0.9476764843085843</v>
       </c>
       <c r="L23" t="n">
-        <v>68.50656765299343</v>
+        <v>0.7418426994071522</v>
       </c>
     </row>
     <row r="24">
@@ -1336,34 +1336,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>2.125401735305786</v>
+        <v>0.2415382862091064</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5765101226696233</v>
+        <v>0.9900982229669099</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.9902541220814914</v>
       </c>
       <c r="K24" t="n">
-        <v>109.8546514923718</v>
+        <v>0.9477199190161582</v>
       </c>
       <c r="L24" t="n">
-        <v>77.9838465335159</v>
+        <v>0.7418471020336928</v>
       </c>
     </row>
     <row r="25">
@@ -1374,34 +1374,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.494043350219727</v>
+        <v>0.3280642032623291</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5896721788986901</v>
+        <v>0.9900985706256581</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.9902541076781655</v>
       </c>
       <c r="K25" t="n">
-        <v>109.8546514923718</v>
+        <v>0.9477206193283345</v>
       </c>
       <c r="L25" t="n">
-        <v>77.9838465335159</v>
+        <v>0.7418330359163595</v>
       </c>
     </row>
     <row r="26">
@@ -1412,34 +1412,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>3.862469911575317</v>
+        <v>0.3807992935180664</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3877192325497514</v>
+        <v>0.9900979108184975</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.3883092387008059</v>
+        <v>0.9902535164372656</v>
       </c>
       <c r="K26" t="n">
-        <v>139.1741339734124</v>
+        <v>0.9477493659364102</v>
       </c>
       <c r="L26" t="n">
-        <v>104.7576252565122</v>
+        <v>0.7417520659136477</v>
       </c>
     </row>
     <row r="27">
@@ -1450,34 +1450,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>8.251466751098633</v>
+        <v>0.5139460563659668</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3876193930187798</v>
+        <v>0.9900982946063565</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.3883092387008058</v>
+        <v>0.9902535127382041</v>
       </c>
       <c r="K27" t="n">
-        <v>139.1741339734124</v>
+        <v>0.9477495457850106</v>
       </c>
       <c r="L27" t="n">
-        <v>104.7576252565122</v>
+        <v>0.7417454198951648</v>
       </c>
     </row>
     <row r="28">
@@ -1488,34 +1488,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>35.90342903137207</v>
+        <v>68.56809163093567</v>
       </c>
       <c r="E28" t="n">
-        <v>0.387644777846075</v>
+        <v>0.9999509803336641</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.9999639062073347</v>
       </c>
       <c r="K28" t="n">
-        <v>139.1869421765973</v>
+        <v>0.05767475851971326</v>
       </c>
       <c r="L28" t="n">
-        <v>104.7894206132718</v>
+        <v>0.02854199958467986</v>
       </c>
     </row>
     <row r="29">
@@ -1526,34 +1526,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>37.20738410949707</v>
+        <v>131.5601994991302</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3875372233114082</v>
+        <v>0.9999587994980429</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.9999686703599214</v>
       </c>
       <c r="K29" t="n">
-        <v>139.1869421765973</v>
+        <v>0.05373375960316539</v>
       </c>
       <c r="L29" t="n">
-        <v>104.7894206132718</v>
+        <v>0.02588015723046504</v>
       </c>
     </row>
     <row r="30">
@@ -1564,34 +1564,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>7.145894289016724</v>
+        <v>5.649735450744629</v>
       </c>
       <c r="E30" t="n">
-        <v>0.387611695296131</v>
+        <v>0.9997890436781206</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.9998042027416953</v>
       </c>
       <c r="K30" t="n">
-        <v>139.2005370678847</v>
+        <v>0.134329942329803</v>
       </c>
       <c r="L30" t="n">
-        <v>104.7953480310862</v>
+        <v>0.05678066230454196</v>
       </c>
     </row>
     <row r="31">
@@ -1602,34 +1602,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>9.151961088180542</v>
+        <v>5.960345983505249</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3875075500335963</v>
+        <v>0.9998118365660742</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.9998042027416953</v>
       </c>
       <c r="K31" t="n">
-        <v>139.2005370678847</v>
+        <v>0.134329942329803</v>
       </c>
       <c r="L31" t="n">
-        <v>104.7953480310862</v>
+        <v>0.05678066230454196</v>
       </c>
     </row>
     <row r="32">
@@ -1640,34 +1640,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>14.13356161117554</v>
+        <v>13.53331780433655</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9516741927489486</v>
+        <v>0.9997793016116973</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.9579448551240813</v>
+        <v>0.9997917906890258</v>
       </c>
       <c r="K32" t="n">
-        <v>36.49237538596583</v>
+        <v>0.1385222696312019</v>
       </c>
       <c r="L32" t="n">
-        <v>22.45833191275022</v>
+        <v>0.06345873321224887</v>
       </c>
     </row>
     <row r="33">
@@ -1678,34 +1678,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>27.21209073066711</v>
+        <v>19.93512225151062</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9555987839182706</v>
+        <v>0.9997948876301346</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.9572399750110738</v>
+        <v>0.9997917906890258</v>
       </c>
       <c r="K33" t="n">
-        <v>36.79692623075351</v>
+        <v>0.1385222696312019</v>
       </c>
       <c r="L33" t="n">
-        <v>22.72192192440616</v>
+        <v>0.06345873321224887</v>
       </c>
     </row>
     <row r="34">
@@ -1716,34 +1716,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>3.663124322891235</v>
+        <v>62.09245896339417</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9536898136138916</v>
+        <v>0.999963921679574</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.9999797479530173</v>
       </c>
       <c r="K34" t="n">
-        <v>34.82984924316406</v>
+        <v>0.04320201350295112</v>
       </c>
       <c r="L34" t="n">
-        <v>21.44558906555176</v>
+        <v>0.01169699744843755</v>
       </c>
     </row>
     <row r="35">
@@ -1754,34 +1754,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>2.157824516296387</v>
+        <v>115.0258991718292</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9580495715141296</v>
+        <v>0.9999709085349604</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.9999797479530173</v>
       </c>
       <c r="K35" t="n">
-        <v>34.82984924316406</v>
+        <v>0.04320201350295112</v>
       </c>
       <c r="L35" t="n">
-        <v>21.44558906555176</v>
+        <v>0.01169699744843755</v>
       </c>
     </row>
     <row r="36">
@@ -1792,34 +1792,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>5.985766887664795</v>
+        <v>407.0889031887054</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9528316417478734</v>
+        <v>0.999963839089749</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.960381630171073</v>
+        <v>0.9999787651075426</v>
       </c>
       <c r="K36" t="n">
-        <v>35.41937290682655</v>
+        <v>0.04423790566095208</v>
       </c>
       <c r="L36" t="n">
-        <v>22.46264210836679</v>
+        <v>0.01322032863127662</v>
       </c>
     </row>
     <row r="37">
@@ -1830,186 +1830,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>5.750111818313599</v>
+        <v>669.6786866188049</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9563572448117584</v>
+        <v>0.999970790667121</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.960381630171073</v>
+        <v>0.9999787193001012</v>
       </c>
       <c r="K37" t="n">
-        <v>35.41937290682655</v>
+        <v>0.04428559447337719</v>
       </c>
       <c r="L37" t="n">
-        <v>22.46264210836679</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>3</v>
-      </c>
-      <c r="D38" t="n">
-        <v>14.99010396003723</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.944227051557548</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>0.9498091161774663</v>
-      </c>
-      <c r="K38" t="n">
-        <v>39.86621353453122</v>
-      </c>
-      <c r="L38" t="n">
-        <v>23.61910385500575</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Bagging</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D39" t="n">
-        <v>27.69755601882935</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.9471150885859518</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>0.9502406638435245</v>
-      </c>
-      <c r="K39" t="n">
-        <v>39.69445612706919</v>
-      </c>
-      <c r="L39" t="n">
-        <v>23.63055235903337</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" t="n">
-        <v>35.37915015220642</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.9451094020818683</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>0.9503855355387685</v>
-      </c>
-      <c r="K40" t="n">
-        <v>39.63662984415944</v>
-      </c>
-      <c r="L40" t="n">
-        <v>23.90459760874549</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" t="n">
-        <v>50.37099456787109</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.9477025989384391</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>0.9503855355387685</v>
-      </c>
-      <c r="K41" t="n">
-        <v>39.63662984415944</v>
-      </c>
-      <c r="L41" t="n">
-        <v>23.90459760874549</v>
+        <v>0.01312509334958275</v>
       </c>
     </row>
   </sheetData>
@@ -2023,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2103,23 +1951,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.47228741645813</v>
+        <v>20.4457700252533</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9259372549984396</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9490794016110472</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9303364774002756</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9854205054555963</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -2141,23 +1989,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>12.85234880447388</v>
+        <v>29.11326050758362</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9296254451309558</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9490794016110472</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9303364774002756</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854205054555963</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -2179,23 +2027,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3354244232177734</v>
+        <v>0.5122740268707275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8998419434690367</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9254890678941312</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8991261138706356</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9601233380302046</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': 10, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -2217,23 +2065,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3668956756591797</v>
+        <v>0.6788384914398193</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9008461098105501</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9306674338319908</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9049920684579351</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9450958342365778</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 6, 'max_features': None, 'max_depth': 6, 'criterion': 'entropy'}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2255,23 +2103,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>220.4221472740173</v>
+        <v>167.733238697052</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8329028339735882</v>
+        <v>0.9996759964597205</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.9998444870665077</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.9998444843919962</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.9999999892512356</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2293,23 +2141,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>404.337406873703</v>
+        <v>331.5528485774994</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8406821430035827</v>
+        <v>0.9996759945997233</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.9998444870665077</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.9998444843919962</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.9999999892512355</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -2331,19 +2179,19 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1.94414758682251</v>
+        <v>23.69982695579529</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8013286401307914</v>
+        <v>0.9825917846771556</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9843450313617749</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9843447819418814</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9992675254413582</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2369,19 +2217,19 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.169837713241577</v>
+        <v>23.63667631149292</v>
       </c>
       <c r="E9" t="n">
-        <v>0.81032050938439</v>
+        <v>0.9837584121796732</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8765822784810127</v>
+        <v>0.9843450313617749</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8213289652983488</v>
+        <v>0.9843447819418814</v>
       </c>
       <c r="H9" t="n">
-        <v>0.91744187621938</v>
+        <v>0.9992675254413582</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2407,23 +2255,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>14.07042956352234</v>
+        <v>44.24955129623413</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7318158655754914</v>
+        <v>0.9998055964130637</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.9997926494220103</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.9997926459445896</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9999999785024709</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -2445,23 +2293,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>29.15627408027649</v>
+        <v>103.1700747013092</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7328819229288671</v>
+        <v>0.9997407969867332</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8285385500575374</v>
+        <v>0.9997926494220103</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7381846049166845</v>
+        <v>0.9997926459445896</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8583667533781343</v>
+        <v>0.9999999785024709</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -2476,30 +2324,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1501247882843018</v>
+        <v>14.96656465530396</v>
       </c>
       <c r="E12" t="n">
-        <v>0.758522079737817</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8201956271576525</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7654782974318119</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8779147698533132</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2514,30 +2362,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2186179161071777</v>
+        <v>38.96033000946045</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7588098200722057</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8201956271576525</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7654782974318119</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8779147698533132</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -2552,30 +2400,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>4.598600149154663</v>
+        <v>275.1872861385345</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9280699341723085</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.950517836593786</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.932054070173397</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9845430034684587</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2590,111 +2438,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>8.56904125213623</v>
+        <v>328.0026791095734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.928876610929035</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9485040276179517</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9296640638468039</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9831533618758581</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 25, 'max_samples': 0.6, 'max_features': 1.0}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>42.96212124824524</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.9131605579577853</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.939873417721519</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.9169917656074629</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.9807870872172846</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>56.19120001792908</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9193219807675821</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9413118527042578</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9190787698855583</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.9801950104776356</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>{'cv': 3}</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2707,7 +2479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2787,10 +2559,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.91527438163757</v>
+        <v>108.487827539444</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9401693017556561</v>
+        <v>0.9999515226287238</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -2801,13 +2573,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.9999752515704077</v>
       </c>
       <c r="K2" t="n">
-        <v>41.18949244604086</v>
+        <v>0.04775769396566595</v>
       </c>
       <c r="L2" t="n">
-        <v>24.65244606562803</v>
+        <v>0.01317099116795414</v>
       </c>
     </row>
     <row r="3">
@@ -2825,10 +2597,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.4542236328125</v>
+        <v>151.3269882202148</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9427502089343068</v>
+        <v>0.9999602042730554</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -2839,13 +2611,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.9464218459082774</v>
+        <v>0.9999752515704077</v>
       </c>
       <c r="K3" t="n">
-        <v>41.18949244604086</v>
+        <v>0.04775769396566595</v>
       </c>
       <c r="L3" t="n">
-        <v>24.65244606562803</v>
+        <v>0.01317099116795414</v>
       </c>
     </row>
     <row r="4">
@@ -2863,10 +2635,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>8.565767526626587</v>
+        <v>95.99473476409912</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7655546082141634</v>
+        <v>0.997705064162585</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -2877,13 +2649,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="K4" t="n">
-        <v>85.81147085279127</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="L4" t="n">
-        <v>53.21821058688148</v>
+        <v>0.2439390274105945</v>
       </c>
     </row>
     <row r="5">
@@ -2901,10 +2673,10 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>13.60066533088684</v>
+        <v>161.5357649326324</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7743430854514228</v>
+        <v>0.9976930312457801</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -2915,13 +2687,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="K5" t="n">
-        <v>85.81147085279127</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="L5" t="n">
-        <v>53.21821058688148</v>
+        <v>0.2439390274105945</v>
       </c>
     </row>
     <row r="6">
@@ -2932,34 +2704,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>35.55732083320618</v>
+        <v>22.92759561538696</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5811946043919515</v>
+        <v>0.9940702304082292</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.6046477401790427</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="K6" t="n">
-        <v>111.88830113121</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="L6" t="n">
-        <v>68.50656765299343</v>
+        <v>0.4629059086032067</v>
       </c>
     </row>
     <row r="7">
@@ -2970,34 +2742,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>63.2348096370697</v>
+        <v>22.38435125350952</v>
       </c>
       <c r="E7" t="n">
-        <v>0.591339866408126</v>
+        <v>0.9947256554325836</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.6046477401790427</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="K7" t="n">
-        <v>111.88830113121</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="L7" t="n">
-        <v>68.50656765299343</v>
+        <v>0.4629059086032067</v>
       </c>
     </row>
     <row r="8">
@@ -3008,34 +2780,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2.125401735305786</v>
+        <v>0.4583749771118164</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5765101226696233</v>
+        <v>0.990098309686355</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.990254957444855</v>
       </c>
       <c r="K8" t="n">
-        <v>109.8546514923718</v>
+        <v>0.9476793014611543</v>
       </c>
       <c r="L8" t="n">
-        <v>77.9838465335159</v>
+        <v>0.7418452222906518</v>
       </c>
     </row>
     <row r="9">
@@ -3046,34 +2818,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.494043350219727</v>
+        <v>0.8081331253051758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5896721788986901</v>
+        <v>0.9900987126467754</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.9902550153826634</v>
       </c>
       <c r="K9" t="n">
-        <v>109.8546514923718</v>
+        <v>0.9476764843085843</v>
       </c>
       <c r="L9" t="n">
-        <v>77.9838465335159</v>
+        <v>0.7418426994071522</v>
       </c>
     </row>
     <row r="10">
@@ -3084,34 +2856,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3.862469911575317</v>
+        <v>0.2415382862091064</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3877192325497514</v>
+        <v>0.9900982229669099</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.3883092387008059</v>
+        <v>0.9902541220814914</v>
       </c>
       <c r="K10" t="n">
-        <v>139.1741339734124</v>
+        <v>0.9477199190161582</v>
       </c>
       <c r="L10" t="n">
-        <v>104.7576252565122</v>
+        <v>0.7418471020336928</v>
       </c>
     </row>
     <row r="11">
@@ -3122,34 +2894,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>8.251466751098633</v>
+        <v>0.3280642032623291</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3876193930187798</v>
+        <v>0.9900985706256581</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.3883092387008058</v>
+        <v>0.9902541076781655</v>
       </c>
       <c r="K11" t="n">
-        <v>139.1741339734124</v>
+        <v>0.9477206193283345</v>
       </c>
       <c r="L11" t="n">
-        <v>104.7576252565122</v>
+        <v>0.7418330359163595</v>
       </c>
     </row>
     <row r="12">
@@ -3160,34 +2932,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>35.90342903137207</v>
+        <v>0.3807992935180664</v>
       </c>
       <c r="E12" t="n">
-        <v>0.387644777846075</v>
+        <v>0.9900979108184975</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.9902535164372656</v>
       </c>
       <c r="K12" t="n">
-        <v>139.1869421765973</v>
+        <v>0.9477493659364102</v>
       </c>
       <c r="L12" t="n">
-        <v>104.7894206132718</v>
+        <v>0.7417520659136477</v>
       </c>
     </row>
     <row r="13">
@@ -3198,34 +2970,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>37.20738410949707</v>
+        <v>0.5139460563659668</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3875372233114082</v>
+        <v>0.9900982946063565</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.9902535127382041</v>
       </c>
       <c r="K13" t="n">
-        <v>139.1869421765973</v>
+        <v>0.9477495457850106</v>
       </c>
       <c r="L13" t="n">
-        <v>104.7894206132718</v>
+        <v>0.7417454198951648</v>
       </c>
     </row>
     <row r="14">
@@ -3236,34 +3008,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>7.145894289016724</v>
+        <v>68.56809163093567</v>
       </c>
       <c r="E14" t="n">
-        <v>0.387611695296131</v>
+        <v>0.9999509803336641</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.9999639062073347</v>
       </c>
       <c r="K14" t="n">
-        <v>139.2005370678847</v>
+        <v>0.05767475851971326</v>
       </c>
       <c r="L14" t="n">
-        <v>104.7953480310862</v>
+        <v>0.02854199958467986</v>
       </c>
     </row>
     <row r="15">
@@ -3274,34 +3046,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>9.151961088180542</v>
+        <v>131.5601994991302</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3875075500335963</v>
+        <v>0.9999587994980429</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.01}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.3880771257287021</v>
+        <v>0.9999686703599214</v>
       </c>
       <c r="K15" t="n">
-        <v>139.2005370678847</v>
+        <v>0.05373375960316539</v>
       </c>
       <c r="L15" t="n">
-        <v>104.7953480310862</v>
+        <v>0.02588015723046504</v>
       </c>
     </row>
     <row r="16">
@@ -3312,34 +3084,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>14.13356161117554</v>
+        <v>5.649735450744629</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9516741927489486</v>
+        <v>0.9997890436781206</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.9579448551240813</v>
+        <v>0.9998042027416953</v>
       </c>
       <c r="K16" t="n">
-        <v>36.49237538596583</v>
+        <v>0.134329942329803</v>
       </c>
       <c r="L16" t="n">
-        <v>22.45833191275022</v>
+        <v>0.05678066230454196</v>
       </c>
     </row>
     <row r="17">
@@ -3350,34 +3122,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>27.21209073066711</v>
+        <v>5.960345983505249</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9555987839182706</v>
+        <v>0.9998118365660742</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.9572399750110738</v>
+        <v>0.9998042027416953</v>
       </c>
       <c r="K17" t="n">
-        <v>36.79692623075351</v>
+        <v>0.134329942329803</v>
       </c>
       <c r="L17" t="n">
-        <v>22.72192192440616</v>
+        <v>0.05678066230454196</v>
       </c>
     </row>
     <row r="18">
@@ -3388,34 +3160,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>3.663124322891235</v>
+        <v>13.53331780433655</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9536898136138916</v>
+        <v>0.9997793016116973</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.9997917906890258</v>
       </c>
       <c r="K18" t="n">
-        <v>34.82984924316406</v>
+        <v>0.1385222696312019</v>
       </c>
       <c r="L18" t="n">
-        <v>21.44558906555176</v>
+        <v>0.06345873321224887</v>
       </c>
     </row>
     <row r="19">
@@ -3426,34 +3198,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>2.157824516296387</v>
+        <v>19.93512225151062</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9580495715141296</v>
+        <v>0.9997948876301346</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.9616894721984863</v>
+        <v>0.9997917906890258</v>
       </c>
       <c r="K19" t="n">
-        <v>34.82984924316406</v>
+        <v>0.1385222696312019</v>
       </c>
       <c r="L19" t="n">
-        <v>21.44558906555176</v>
+        <v>0.06345873321224887</v>
       </c>
     </row>
     <row r="20">
@@ -3464,34 +3236,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>5.985766887664795</v>
+        <v>62.09245896339417</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9528316417478734</v>
+        <v>0.999963921679574</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.960381630171073</v>
+        <v>0.9999797479530173</v>
       </c>
       <c r="K20" t="n">
-        <v>35.41937290682655</v>
+        <v>0.04320201350295112</v>
       </c>
       <c r="L20" t="n">
-        <v>22.46264210836679</v>
+        <v>0.01169699744843755</v>
       </c>
     </row>
     <row r="21">
@@ -3502,34 +3274,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>5.750111818313599</v>
+        <v>115.0258991718292</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9563572448117584</v>
+        <v>0.9999709085349604</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.960381630171073</v>
+        <v>0.9999797479530173</v>
       </c>
       <c r="K21" t="n">
-        <v>35.41937290682655</v>
+        <v>0.04320201350295112</v>
       </c>
       <c r="L21" t="n">
-        <v>22.46264210836679</v>
+        <v>0.01169699744843755</v>
       </c>
     </row>
     <row r="22">
@@ -3540,34 +3312,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>14.99010396003723</v>
+        <v>407.0889031887054</v>
       </c>
       <c r="E22" t="n">
-        <v>0.944227051557548</v>
+        <v>0.999963839089749</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.9498091161774663</v>
+        <v>0.9999787651075426</v>
       </c>
       <c r="K22" t="n">
-        <v>39.86621353453122</v>
+        <v>0.04423790566095208</v>
       </c>
       <c r="L22" t="n">
-        <v>23.61910385500575</v>
+        <v>0.01322032863127662</v>
       </c>
     </row>
     <row r="23">
@@ -3578,110 +3350,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>27.69755601882935</v>
+        <v>669.6786866188049</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9471150885859518</v>
+        <v>0.999970790667121</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.9502406638435245</v>
+        <v>0.9999787193001012</v>
       </c>
       <c r="K23" t="n">
-        <v>39.69445612706919</v>
+        <v>0.04428559447337719</v>
       </c>
       <c r="L23" t="n">
-        <v>23.63055235903337</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>35.37915015220642</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.9451094020818683</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>0.9503855355387685</v>
-      </c>
-      <c r="K24" t="n">
-        <v>39.63662984415944</v>
-      </c>
-      <c r="L24" t="n">
-        <v>23.90459760874549</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>50.37099456787109</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.9477025989384391</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{'cv': 5}</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>0.9503855355387685</v>
-      </c>
-      <c r="K25" t="n">
-        <v>39.63662984415944</v>
-      </c>
-      <c r="L25" t="n">
-        <v>23.90459760874549</v>
+        <v>0.01312509334958275</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,23 +507,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.4457700252533</v>
+        <v>34.96213316917419</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.7424679277285154</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -545,23 +545,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.11326050758362</v>
+        <v>49.15799784660339</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.7591605966879464</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -583,23 +583,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5122740268707275</v>
+        <v>0.5657615661621094</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.7178455340929982</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -621,23 +621,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6788384914398193</v>
+        <v>0.8688530921936035</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.7296280924933435</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 6, 'max_features': None, 'max_depth': 6, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -659,23 +659,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>167.733238697052</v>
+        <v>7582.797722101212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9996759964597205</v>
+        <v>0.7749083896227867</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9998444870665077</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9998444843919962</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9999999892512356</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': None, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -697,23 +697,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>331.5528485774994</v>
+        <v>13063.4157834053</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9996759945997233</v>
+        <v>0.7829275385741383</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9998444870665077</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9998444843919962</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9999999892512355</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -735,23 +735,23 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>23.69982695579529</v>
+        <v>3.388538360595703</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9825917846771556</v>
+        <v>0.7816443157726987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9843450313617749</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9843447819418814</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9992675254413582</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -773,23 +773,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>23.63667631149292</v>
+        <v>3.476355314254761</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9837584121796732</v>
+        <v>0.7887837510961361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9843450313617749</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9843447819418814</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9992675254413582</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -811,23 +811,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>44.24955129623413</v>
+        <v>1.879142999649048</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9998055964130637</v>
+        <v>0.5708386073605726</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9997926494220103</v>
+        <v>0.7322016721560679</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9997926459445896</v>
+        <v>0.5792004344384017</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9999999785024709</v>
+        <v>0.7940013503316254</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -849,23 +849,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>103.1700747013092</v>
+        <v>3.306220293045044</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9997407969867332</v>
+        <v>0.5714566683306512</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9997926494220103</v>
+        <v>0.7332151000760071</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9997926459445896</v>
+        <v>0.5799855750471964</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9999999785024709</v>
+        <v>0.7939449541284403</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -880,30 +880,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>14.96656465530396</v>
+        <v>0.1857089996337891</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.5534276352203948</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -918,30 +918,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>38.96033000946045</v>
+        <v>0.2213370800018311</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.5584974950698796</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -956,30 +956,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>275.1872861385345</v>
+        <v>30.05495476722717</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.7521014360203813</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.9450215353432987</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.7897204739826351</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.9349533341276461</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -994,30 +994,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>328.0026791095734</v>
+        <v>58.17849445343018</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.7677588908801928</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.9445148213833291</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.7926083122896885</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.9250530203741212</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1027,78 +1027,78 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>108.487827539444</v>
+        <v>58.71340918540955</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9999515226287238</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+        <v>0.7663753818038094</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9467950342031923</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8046094877089758</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9339814925136026</v>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0.9999752515704077</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.04775769396566595</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.01317099116795414</v>
-      </c>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>Stacking</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>151.3269882202148</v>
+        <v>85.50505352020264</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9999602042730554</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+        <v>0.7834056300532612</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9447681783633139</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7965198332895054</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9337503475118155</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0.9999752515704077</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.04775769396566595</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.01317099116795414</v>
-      </c>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1108,34 +1108,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>95.99473476409912</v>
+        <v>111.6458830833435</v>
       </c>
       <c r="E18" t="n">
-        <v>0.997705064162585</v>
+        <v>0.4357274358187564</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4545389345695044</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2439390274105945</v>
+        <v>34.12331542084517</v>
       </c>
     </row>
     <row r="19">
@@ -1146,34 +1146,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>161.5357649326324</v>
+        <v>150.6258206367493</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9976930312457801</v>
+        <v>0.4620163922841435</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4545389345695044</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2439390274105945</v>
+        <v>34.12331542084517</v>
       </c>
     </row>
     <row r="20">
@@ -1184,34 +1184,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>22.92759561538696</v>
+        <v>15.49662733078003</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9940702304082292</v>
+        <v>0.200405995010477</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.2605617127993397</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6399832259487974</v>
+        <v>86.02108054688992</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4629059086032067</v>
+        <v>38.02254877121864</v>
       </c>
     </row>
     <row r="21">
@@ -1222,34 +1222,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>22.38435125350952</v>
+        <v>30.89138531684875</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9947256554325836</v>
+        <v>0.2494303631632399</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.3362235571106167</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6399832259487974</v>
+        <v>81.50135784198201</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4629059086032067</v>
+        <v>37.53977704585761</v>
       </c>
     </row>
     <row r="22">
@@ -1260,34 +1260,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4583749771118164</v>
+        <v>106.9222595691681</v>
       </c>
       <c r="E22" t="n">
-        <v>0.990098309686355</v>
+        <v>0.3296251448796029</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.990254957444855</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9476793014611543</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7418452222906518</v>
+        <v>32.98778734697751</v>
       </c>
     </row>
     <row r="23">
@@ -1298,34 +1298,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8081331253051758</v>
+        <v>180.7806396484375</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9900987126467754</v>
+        <v>0.3439273431575175</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.9902550153826634</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9476764843085843</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7418426994071522</v>
+        <v>32.98778734697751</v>
       </c>
     </row>
     <row r="24">
@@ -1336,34 +1336,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2415382862091064</v>
+        <v>3.681244850158691</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9900982229669099</v>
+        <v>0.4935003325207741</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.9902541220814914</v>
+        <v>0.5873816881539017</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9477199190161582</v>
+        <v>64.25814371519127</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7418471020336928</v>
+        <v>29.24887821574554</v>
       </c>
     </row>
     <row r="25">
@@ -1374,34 +1374,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3280642032623291</v>
+        <v>4.550774812698364</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9900985706256581</v>
+        <v>0.5309137658627969</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.9902541076781655</v>
+        <v>0.6036051296434839</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9477206193283345</v>
+        <v>62.98221635411645</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7418330359163595</v>
+        <v>27.77407416552622</v>
       </c>
     </row>
     <row r="26">
@@ -1412,34 +1412,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3807992935180664</v>
+        <v>0.4936785697937012</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9900979108184975</v>
+        <v>0.1631081258955845</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.9902535164372656</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9477493659364102</v>
+        <v>91.204868609201</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7417520659136477</v>
+        <v>52.61355946207429</v>
       </c>
     </row>
     <row r="27">
@@ -1450,34 +1450,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5139460563659668</v>
+        <v>0.6994311809539795</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9900982946063565</v>
+        <v>0.1637077778427174</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.9902535127382041</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9477495457850106</v>
+        <v>91.204868609201</v>
       </c>
       <c r="L27" t="n">
-        <v>0.7417454198951648</v>
+        <v>52.61355946207429</v>
       </c>
     </row>
     <row r="28">
@@ -1488,34 +1488,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>68.56809163093567</v>
+        <v>5.73303747177124</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9999509803336641</v>
+        <v>0.1631297501254156</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.9999639062073347</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="K28" t="n">
-        <v>0.05767475851971326</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02854199958467986</v>
+        <v>52.59974169016452</v>
       </c>
     </row>
     <row r="29">
@@ -1526,34 +1526,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>131.5601994991302</v>
+        <v>6.808621406555176</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9999587994980429</v>
+        <v>0.1637257443267972</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.9999686703599214</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="K29" t="n">
-        <v>0.05373375960316539</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02588015723046504</v>
+        <v>52.59974169016452</v>
       </c>
     </row>
     <row r="30">
@@ -1564,34 +1564,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>5.649735450744629</v>
+        <v>7.956679582595825</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9997890436781206</v>
+        <v>0.1631195370408529</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.9998042027416953</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="K30" t="n">
-        <v>0.134329942329803</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="L30" t="n">
-        <v>0.05678066230454196</v>
+        <v>52.59133960916441</v>
       </c>
     </row>
     <row r="31">
@@ -1602,34 +1602,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>5.960345983505249</v>
+        <v>10.55267238616943</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9998118365660742</v>
+        <v>0.1637308957578318</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.9998042027416953</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="K31" t="n">
-        <v>0.134329942329803</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="L31" t="n">
-        <v>0.05678066230454196</v>
+        <v>52.59133960916441</v>
       </c>
     </row>
     <row r="32">
@@ -1640,34 +1640,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>13.53331780433655</v>
+        <v>67.05084180831909</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9997793016116973</v>
+        <v>0.4401797218112232</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.9997917906890258</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1385222696312019</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="L32" t="n">
-        <v>0.06345873321224887</v>
+        <v>35.09659729829767</v>
       </c>
     </row>
     <row r="33">
@@ -1678,34 +1678,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>19.93512225151062</v>
+        <v>104.0239977836609</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9997948876301346</v>
+        <v>0.4797057452240424</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.9997917906890258</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1385222696312019</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="L33" t="n">
-        <v>0.06345873321224887</v>
+        <v>35.09659729829767</v>
       </c>
     </row>
     <row r="34">
@@ -1716,34 +1716,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>62.09245896339417</v>
+        <v>5.446849346160889</v>
       </c>
       <c r="E34" t="n">
-        <v>0.999963921679574</v>
+        <v>0.4881770610809326</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.9999797479530173</v>
+        <v>0.5276503562927246</v>
       </c>
       <c r="K34" t="n">
-        <v>0.04320201350295112</v>
+        <v>68.75205993652344</v>
       </c>
       <c r="L34" t="n">
-        <v>0.01169699744843755</v>
+        <v>33.24764251708984</v>
       </c>
     </row>
     <row r="35">
@@ -1754,34 +1754,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>115.0258991718292</v>
+        <v>5.661454677581787</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9999709085349604</v>
+        <v>0.5191580176353454</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.9999797479530173</v>
+        <v>0.5484093427658081</v>
       </c>
       <c r="K35" t="n">
-        <v>0.04320201350295112</v>
+        <v>67.22431182861328</v>
       </c>
       <c r="L35" t="n">
-        <v>0.01169699744843755</v>
+        <v>33.18839645385742</v>
       </c>
     </row>
     <row r="36">
@@ -1792,34 +1792,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>407.0889031887054</v>
+        <v>8.076727867126465</v>
       </c>
       <c r="E36" t="n">
-        <v>0.999963839089749</v>
+        <v>0.4804153325581517</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.9999787651075426</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="K36" t="n">
-        <v>0.04423790566095208</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="L36" t="n">
-        <v>0.01322032863127662</v>
+        <v>34.62104164052829</v>
       </c>
     </row>
     <row r="37">
@@ -1830,34 +1830,186 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>669.6786866188049</v>
+        <v>9.786618232727051</v>
       </c>
       <c r="E37" t="n">
-        <v>0.999970790667121</v>
+        <v>0.5001636848295401</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.5435438726227794</v>
+      </c>
+      <c r="K37" t="n">
+        <v>67.58548695620104</v>
+      </c>
+      <c r="L37" t="n">
+        <v>34.62104164052829</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>60.35610222816467</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5059173107368674</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.589358628410138</v>
+      </c>
+      <c r="K38" t="n">
+        <v>64.1040218121336</v>
+      </c>
+      <c r="L38" t="n">
+        <v>30.19281732961743</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>118.0046970844269</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5359470634249959</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.589358628410138</v>
+      </c>
+      <c r="K39" t="n">
+        <v>64.1040218121336</v>
+      </c>
+      <c r="L39" t="n">
+        <v>30.19281732961743</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>138.0690364837646</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.4742039714755084</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>{'cv': 5}</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>0.9999787193001012</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.04428559447337719</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.01312509334958275</v>
+      <c r="J40" t="n">
+        <v>0.5480245530595298</v>
+      </c>
+      <c r="K40" t="n">
+        <v>67.25295138365956</v>
+      </c>
+      <c r="L40" t="n">
+        <v>31.38330002219408</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>175.5471067428589</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5006287526437336</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5478088376009014</v>
+      </c>
+      <c r="K41" t="n">
+        <v>67.26899846183061</v>
+      </c>
+      <c r="L41" t="n">
+        <v>31.30699612414678</v>
       </c>
     </row>
   </sheetData>
@@ -1871,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1951,23 +2103,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.4457700252533</v>
+        <v>34.96213316917419</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.7424679277285154</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -1989,23 +2141,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.11326050758362</v>
+        <v>49.15799784660339</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.7591605966879464</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -2027,23 +2179,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5122740268707275</v>
+        <v>0.5657615661621094</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.7178455340929982</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -2065,23 +2217,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6788384914398193</v>
+        <v>0.8688530921936035</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.7296280924933435</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9262731188244236</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.7355279473071596</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.7828472139481314</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 6, 'max_features': None, 'max_depth': 6, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2103,23 +2255,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>167.733238697052</v>
+        <v>7582.797722101212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9996759964597205</v>
+        <v>0.7749083896227867</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9998444870665077</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9998444843919962</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9999999892512356</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': None, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2141,23 +2293,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>331.5528485774994</v>
+        <v>13063.4157834053</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9996759945997233</v>
+        <v>0.7829275385741383</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9998444870665077</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9998444843919962</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9999999892512355</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -2179,23 +2331,23 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>23.69982695579529</v>
+        <v>3.388538360595703</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9825917846771556</v>
+        <v>0.7816443157726987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9843450313617749</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9843447819418814</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9992675254413582</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -2217,23 +2369,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>23.63667631149292</v>
+        <v>3.476355314254761</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9837584121796732</v>
+        <v>0.7887837510961361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9843450313617749</v>
+        <v>0.9414745376235115</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9843447819418814</v>
+        <v>0.7987217188801441</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9992675254413582</v>
+        <v>0.9096314388974939</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -2255,23 +2407,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>44.24955129623413</v>
+        <v>1.879142999649048</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9998055964130637</v>
+        <v>0.5708386073605726</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9997926494220103</v>
+        <v>0.7322016721560679</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9997926459445896</v>
+        <v>0.5792004344384017</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9999999785024709</v>
+        <v>0.7940013503316254</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -2293,23 +2445,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>103.1700747013092</v>
+        <v>3.306220293045044</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9997407969867332</v>
+        <v>0.5714566683306512</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9997926494220103</v>
+        <v>0.7332151000760071</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9997926459445896</v>
+        <v>0.5799855750471964</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9999999785024709</v>
+        <v>0.7939449541284403</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -2324,30 +2476,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>14.96656465530396</v>
+        <v>0.1857089996337891</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.5534276352203948</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2362,30 +2514,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>38.96033000946045</v>
+        <v>0.2213370800018311</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.5584974950698796</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.8697745122878136</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.5553941137590488</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.6969482505262322</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -2400,30 +2552,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>275.1872861385345</v>
+        <v>30.05495476722717</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.7521014360203813</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.9450215353432987</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.7897204739826351</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.9349533341276461</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2438,35 +2590,111 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>328.0026791095734</v>
+        <v>58.17849445343018</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.7677588908801928</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.9445148213833291</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.7926083122896885</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.9250530203741212</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>58.71340918540955</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7663753818038094</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9467950342031923</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8046094877089758</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9339814925136026</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>85.50505352020264</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7834056300532612</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9447681783633139</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7965198332895054</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9337503475118155</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2479,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2559,10 +2787,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>108.487827539444</v>
+        <v>111.6458830833435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999515226287238</v>
+        <v>0.4357274358187564</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -2573,13 +2801,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.9999752515704077</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04775769396566595</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01317099116795414</v>
+        <v>34.12331542084517</v>
       </c>
     </row>
     <row r="3">
@@ -2597,10 +2825,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>151.3269882202148</v>
+        <v>150.6258206367493</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999602042730554</v>
+        <v>0.4620163922841435</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -2611,13 +2839,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.9999752515704077</v>
+        <v>0.4894214179550179</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04775769396566595</v>
+        <v>71.48011178783491</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01317099116795414</v>
+        <v>34.12331542084517</v>
       </c>
     </row>
     <row r="4">
@@ -2635,27 +2863,27 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>95.99473476409912</v>
+        <v>15.49662733078003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.997705064162585</v>
+        <v>0.200405995010477</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.2605617127993397</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4545389345695044</v>
+        <v>86.02108054688992</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2439390274105945</v>
+        <v>38.02254877121864</v>
       </c>
     </row>
     <row r="5">
@@ -2673,27 +2901,27 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>161.5357649326324</v>
+        <v>30.89138531684875</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9976930312457801</v>
+        <v>0.2494303631632399</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.3362235571106167</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4545389345695044</v>
+        <v>81.50135784198201</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2439390274105945</v>
+        <v>37.53977704585761</v>
       </c>
     </row>
     <row r="6">
@@ -2704,34 +2932,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>22.92759561538696</v>
+        <v>106.9222595691681</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9940702304082292</v>
+        <v>0.3296251448796029</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6399832259487974</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4629059086032067</v>
+        <v>32.98778734697751</v>
       </c>
     </row>
     <row r="7">
@@ -2742,34 +2970,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>22.38435125350952</v>
+        <v>180.7806396484375</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9947256554325836</v>
+        <v>0.3439273431575175</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.3460882767829514</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6399832259487974</v>
+        <v>80.89347428382811</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4629059086032067</v>
+        <v>32.98778734697751</v>
       </c>
     </row>
     <row r="8">
@@ -2780,34 +3008,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4583749771118164</v>
+        <v>3.681244850158691</v>
       </c>
       <c r="E8" t="n">
-        <v>0.990098309686355</v>
+        <v>0.4935003325207741</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.990254957444855</v>
+        <v>0.5873816881539017</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9476793014611543</v>
+        <v>64.25814371519127</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7418452222906518</v>
+        <v>29.24887821574554</v>
       </c>
     </row>
     <row r="9">
@@ -2818,34 +3046,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8081331253051758</v>
+        <v>4.550774812698364</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9900987126467754</v>
+        <v>0.5309137658627969</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.9902550153826634</v>
+        <v>0.6036051296434839</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9476764843085843</v>
+        <v>62.98221635411645</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7418426994071522</v>
+        <v>27.77407416552622</v>
       </c>
     </row>
     <row r="10">
@@ -2856,34 +3084,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2415382862091064</v>
+        <v>0.4936785697937012</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9900982229669099</v>
+        <v>0.1631081258955845</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.9902541220814914</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9477199190161582</v>
+        <v>91.204868609201</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7418471020336928</v>
+        <v>52.61355946207429</v>
       </c>
     </row>
     <row r="11">
@@ -2894,34 +3122,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3280642032623291</v>
+        <v>0.6994311809539795</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9900985706256581</v>
+        <v>0.1637077778427174</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.9902541076781655</v>
+        <v>0.1687566366856434</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9477206193283345</v>
+        <v>91.204868609201</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7418330359163595</v>
+        <v>52.61355946207429</v>
       </c>
     </row>
     <row r="12">
@@ -2932,34 +3160,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3807992935180664</v>
+        <v>5.73303747177124</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9900979108184975</v>
+        <v>0.1631297501254156</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.9902535164372656</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9477493659364102</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7417520659136477</v>
+        <v>52.59974169016452</v>
       </c>
     </row>
     <row r="13">
@@ -2970,34 +3198,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5139460563659668</v>
+        <v>6.808621406555176</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9900982946063565</v>
+        <v>0.1637257443267972</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.9902535127382041</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9477495457850106</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7417454198951648</v>
+        <v>52.59974169016452</v>
       </c>
     </row>
     <row r="14">
@@ -3008,34 +3236,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>68.56809163093567</v>
+        <v>7.956679582595825</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9999509803336641</v>
+        <v>0.1631195370408529</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.9999639062073347</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05767475851971326</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02854199958467986</v>
+        <v>52.59133960916441</v>
       </c>
     </row>
     <row r="15">
@@ -3046,34 +3274,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>131.5601994991302</v>
+        <v>10.55267238616943</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9999587994980429</v>
+        <v>0.1637308957578318</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.9999686703599214</v>
+        <v>0.1688718910031372</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05373375960316539</v>
+        <v>91.1985454794509</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02588015723046504</v>
+        <v>52.59133960916441</v>
       </c>
     </row>
     <row r="16">
@@ -3084,34 +3312,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>5.649735450744629</v>
+        <v>67.05084180831909</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9997890436781206</v>
+        <v>0.4401797218112232</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.9998042027416953</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="K16" t="n">
-        <v>0.134329942329803</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05678066230454196</v>
+        <v>35.09659729829767</v>
       </c>
     </row>
     <row r="17">
@@ -3122,34 +3350,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>5.960345983505249</v>
+        <v>104.0239977836609</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9998118365660742</v>
+        <v>0.4797057452240424</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.9998042027416953</v>
+        <v>0.4974964768614818</v>
       </c>
       <c r="K17" t="n">
-        <v>0.134329942329803</v>
+        <v>70.91261193281821</v>
       </c>
       <c r="L17" t="n">
-        <v>0.05678066230454196</v>
+        <v>35.09659729829767</v>
       </c>
     </row>
     <row r="18">
@@ -3160,34 +3388,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>13.53331780433655</v>
+        <v>5.446849346160889</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9997793016116973</v>
+        <v>0.4881770610809326</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.9997917906890258</v>
+        <v>0.5276503562927246</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1385222696312019</v>
+        <v>68.75205993652344</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06345873321224887</v>
+        <v>33.24764251708984</v>
       </c>
     </row>
     <row r="19">
@@ -3198,34 +3426,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>19.93512225151062</v>
+        <v>5.661454677581787</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9997948876301346</v>
+        <v>0.5191580176353454</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'num_leaves': 31, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.9997917906890258</v>
+        <v>0.5484093427658081</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1385222696312019</v>
+        <v>67.22431182861328</v>
       </c>
       <c r="L19" t="n">
-        <v>0.06345873321224887</v>
+        <v>33.18839645385742</v>
       </c>
     </row>
     <row r="20">
@@ -3236,34 +3464,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>62.09245896339417</v>
+        <v>8.076727867126465</v>
       </c>
       <c r="E20" t="n">
-        <v>0.999963921679574</v>
+        <v>0.4804153325581517</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.9999797479530173</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04320201350295112</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01169699744843755</v>
+        <v>34.62104164052829</v>
       </c>
     </row>
     <row r="21">
@@ -3274,34 +3502,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>115.0258991718292</v>
+        <v>9.786618232727051</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9999709085349604</v>
+        <v>0.5001636848295401</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.9999797479530173</v>
+        <v>0.5435438726227794</v>
       </c>
       <c r="K21" t="n">
-        <v>0.04320201350295112</v>
+        <v>67.58548695620104</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01169699744843755</v>
+        <v>34.62104164052829</v>
       </c>
     </row>
     <row r="22">
@@ -3312,34 +3540,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>407.0889031887054</v>
+        <v>60.35610222816467</v>
       </c>
       <c r="E22" t="n">
-        <v>0.999963839089749</v>
+        <v>0.5059173107368674</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.9999787651075426</v>
+        <v>0.589358628410138</v>
       </c>
       <c r="K22" t="n">
-        <v>0.04423790566095208</v>
+        <v>64.1040218121336</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01322032863127662</v>
+        <v>30.19281732961743</v>
       </c>
     </row>
     <row r="23">
@@ -3350,34 +3578,110 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>669.6786866188049</v>
+        <v>118.0046970844269</v>
       </c>
       <c r="E23" t="n">
-        <v>0.999970790667121</v>
+        <v>0.5359470634249959</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.589358628410138</v>
+      </c>
+      <c r="K23" t="n">
+        <v>64.1040218121336</v>
+      </c>
+      <c r="L23" t="n">
+        <v>30.19281732961743</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>138.0690364837646</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4742039714755084</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>{'cv': 5}</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>0.9999787193001012</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.04428559447337719</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.01312509334958275</v>
+      <c r="J24" t="n">
+        <v>0.5480245530595298</v>
+      </c>
+      <c r="K24" t="n">
+        <v>67.25295138365956</v>
+      </c>
+      <c r="L24" t="n">
+        <v>31.38330002219408</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>175.5471067428589</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5006287526437336</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5478088376009014</v>
+      </c>
+      <c r="K25" t="n">
+        <v>67.26899846183061</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.30699612414678</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -507,23 +507,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>34.96213316917419</v>
+        <v>61.78164196014404</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7424679277285154</v>
+        <v>0.9427398491413124</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9546202680460851</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9468293212200711</v>
       </c>
       <c r="H2" t="n">
-        <v>0.90826124945391</v>
+        <v>0.9903869894713397</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -545,23 +545,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>49.15799784660339</v>
+        <v>102.1410129070282</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7591605966879464</v>
+        <v>0.9447134275511153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9557959087702798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9481739773427895</v>
       </c>
       <c r="H3" t="n">
-        <v>0.90826124945391</v>
+        <v>0.9901331238317979</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -583,23 +583,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5657615661621094</v>
+        <v>1.819243192672729</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7178455340929982</v>
+        <v>0.9207321669579768</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9440395015283329</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9333833423014269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9545206207717516</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -621,23 +621,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8688530921936035</v>
+        <v>2.692499399185181</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7296280924933435</v>
+        <v>0.9272708256612205</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9440395015283329</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9333833423014269</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9545206207717516</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -659,23 +659,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7582.797722101212</v>
+        <v>351.8641495704651</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7749083896227867</v>
+        <v>0.9284502465999035</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9419233482247825</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9324042859331567</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9788942174844476</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -697,19 +697,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>13063.4157834053</v>
+        <v>761.6525349617004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7829275385741383</v>
+        <v>0.9328469405523752</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9454502703973665</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9369826450254473</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9795603357067736</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -735,19 +735,19 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3.388538360595703</v>
+        <v>7.729877471923828</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7816443157726987</v>
+        <v>0.937197913778761</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9508582177286621</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9419507116201434</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9717784936272238</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -773,19 +773,19 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.476355314254761</v>
+        <v>8.527689933776855</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7887837510961361</v>
+        <v>0.9413842056504705</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9508582177286621</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9419507116201434</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9717784936272238</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -811,23 +811,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.879142999649048</v>
+        <v>129.834644317627</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5708386073605726</v>
+        <v>0.9053356399652978</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7322016721560679</v>
+        <v>0.9172348930166941</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5792004344384017</v>
+        <v>0.9054590941791756</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7940013503316254</v>
+        <v>0.9696373805793969</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -849,23 +849,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3.306220293045044</v>
+        <v>222.530154466629</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5714566683306512</v>
+        <v>0.9051087342385802</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7332151000760071</v>
+        <v>0.9172348930166941</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5799855750471964</v>
+        <v>0.9054590941791756</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7939449541284403</v>
+        <v>0.9696373805793969</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -887,23 +887,23 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1857089996337891</v>
+        <v>0.3268022537231445</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5534276352203948</v>
+        <v>0.79106389788666</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.8074300493769104</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.7975398631827457</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.8671062626670155</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -925,19 +925,19 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2213370800018311</v>
+        <v>0.4358818531036377</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5584974950698796</v>
+        <v>0.7912015650524316</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.8074300493769104</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.7975398631827457</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.8671067879968438</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -963,23 +963,23 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>30.05495476722717</v>
+        <v>74.81637406349182</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7521014360203813</v>
+        <v>0.9421905253471752</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9450215353432987</v>
+        <v>0.9555607806254409</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7897204739826351</v>
+        <v>0.9476193061066791</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9349533341276461</v>
+        <v>0.9891931774364535</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 0.6}</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1001,23 +1001,23 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>58.17849445343018</v>
+        <v>153.9736731052399</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7677588908801928</v>
+        <v>0.9459086431217779</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9445148213833291</v>
+        <v>0.9562661650599577</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7926083122896885</v>
+        <v>0.9485504116966064</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9250530203741212</v>
+        <v>0.9887731762387013</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.8}</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1039,19 +1039,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>58.71340918540955</v>
+        <v>101.9579718112946</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7663753818038094</v>
+        <v>0.9414777373848328</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9467950342031923</v>
+        <v>0.9529743710322126</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8046094877089758</v>
+        <v>0.9445826512034934</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9339814925136026</v>
+        <v>0.9902825801679586</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>85.50505352020264</v>
+        <v>208.2088785171509</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7834056300532612</v>
+        <v>0.9443251101310539</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9447681783633139</v>
+        <v>0.9539148836115683</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7965198332895054</v>
+        <v>0.945737748115375</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9337503475118155</v>
+        <v>0.9901785648619486</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>111.6458830833435</v>
+        <v>292.0688977241516</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4357274358187564</v>
+        <v>0.9102965857569525</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.9273325445472385</v>
       </c>
       <c r="K18" t="n">
-        <v>71.48011178783491</v>
+        <v>9.145823506301472</v>
       </c>
       <c r="L18" t="n">
-        <v>34.12331542084517</v>
+        <v>5.264394540992574</v>
       </c>
     </row>
     <row r="19">
@@ -1153,10 +1153,10 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>150.6258206367493</v>
+        <v>416.8807187080383</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4620163922841435</v>
+        <v>0.9158221695712907</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.9273325445472385</v>
       </c>
       <c r="K19" t="n">
-        <v>71.48011178783491</v>
+        <v>9.145823506301472</v>
       </c>
       <c r="L19" t="n">
-        <v>34.12331542084517</v>
+        <v>5.264394540992574</v>
       </c>
     </row>
     <row r="20">
@@ -1191,27 +1191,27 @@
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>15.49662733078003</v>
+        <v>31.36257743835449</v>
       </c>
       <c r="E20" t="n">
-        <v>0.200405995010477</v>
+        <v>0.8630177794140446</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'friedman_mse'}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.2605617127993397</v>
+        <v>0.8888639939395483</v>
       </c>
       <c r="K20" t="n">
-        <v>86.02108054688992</v>
+        <v>11.31045906689468</v>
       </c>
       <c r="L20" t="n">
-        <v>38.02254877121864</v>
+        <v>6.040182151688382</v>
       </c>
     </row>
     <row r="21">
@@ -1229,10 +1229,10 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>30.89138531684875</v>
+        <v>86.33157324790955</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2494303631632399</v>
+        <v>0.8730497345442128</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.3362235571106167</v>
+        <v>0.8855511189077954</v>
       </c>
       <c r="K21" t="n">
-        <v>81.50135784198201</v>
+        <v>11.47779900500352</v>
       </c>
       <c r="L21" t="n">
-        <v>37.53977704585761</v>
+        <v>6.316851478595777</v>
       </c>
     </row>
     <row r="22">
@@ -1267,10 +1267,10 @@
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>106.9222595691681</v>
+        <v>342.1860818862915</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3296251448796029</v>
+        <v>0.8782810451903668</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9002271579078316</v>
       </c>
       <c r="K22" t="n">
-        <v>80.89347428382811</v>
+        <v>10.71664912018776</v>
       </c>
       <c r="L22" t="n">
-        <v>32.98778734697751</v>
+        <v>6.050534389613801</v>
       </c>
     </row>
     <row r="23">
@@ -1305,10 +1305,10 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>180.7806396484375</v>
+        <v>794.1601617336273</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3439273431575175</v>
+        <v>0.882429566993066</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9002271579078316</v>
       </c>
       <c r="K23" t="n">
-        <v>80.89347428382811</v>
+        <v>10.71664912018776</v>
       </c>
       <c r="L23" t="n">
-        <v>32.98778734697751</v>
+        <v>6.050534389613801</v>
       </c>
     </row>
     <row r="24">
@@ -1343,10 +1343,10 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>3.681244850158691</v>
+        <v>9.408438682556152</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4935003325207741</v>
+        <v>0.9029883463751035</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.5873816881539017</v>
+        <v>0.9210421468734596</v>
       </c>
       <c r="K24" t="n">
-        <v>64.25814371519127</v>
+        <v>9.533459047908195</v>
       </c>
       <c r="L24" t="n">
-        <v>29.24887821574554</v>
+        <v>5.22191277459623</v>
       </c>
     </row>
     <row r="25">
@@ -1381,27 +1381,27 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>4.550774812698364</v>
+        <v>11.40788674354553</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5309137658627969</v>
+        <v>0.9080335763132791</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.6036051296434839</v>
+        <v>0.9210421468734596</v>
       </c>
       <c r="K25" t="n">
-        <v>62.98221635411645</v>
+        <v>9.533459047908195</v>
       </c>
       <c r="L25" t="n">
-        <v>27.77407416552622</v>
+        <v>5.22191277459623</v>
       </c>
     </row>
     <row r="26">
@@ -1419,27 +1419,27 @@
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4936785697937012</v>
+        <v>23.55539107322693</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1631081258955845</v>
+        <v>0.733920064339284</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.7375098266344251</v>
       </c>
       <c r="K26" t="n">
-        <v>91.204868609201</v>
+        <v>17.38238498910604</v>
       </c>
       <c r="L26" t="n">
-        <v>52.61355946207429</v>
+        <v>13.21099620560328</v>
       </c>
     </row>
     <row r="27">
@@ -1457,27 +1457,27 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6994311809539795</v>
+        <v>51.92563271522522</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1637077778427174</v>
+        <v>0.7339708525065632</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.7375098266344251</v>
       </c>
       <c r="K27" t="n">
-        <v>91.204868609201</v>
+        <v>17.38238498910604</v>
       </c>
       <c r="L27" t="n">
-        <v>52.61355946207429</v>
+        <v>13.21099620560328</v>
       </c>
     </row>
     <row r="28">
@@ -1495,27 +1495,27 @@
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>5.73303747177124</v>
+        <v>183.1296489238739</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1631297501254156</v>
+        <v>0.7337649931248545</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.168803458291798</v>
+        <v>0.7371529686246404</v>
       </c>
       <c r="K28" t="n">
-        <v>91.20229991586648</v>
+        <v>17.39419673883764</v>
       </c>
       <c r="L28" t="n">
-        <v>52.59974169016452</v>
+        <v>13.20418315547962</v>
       </c>
     </row>
     <row r="29">
@@ -1533,27 +1533,27 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>6.808621406555176</v>
+        <v>206.5332767963409</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1637257443267972</v>
+        <v>0.7338476286732339</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.168803458291798</v>
+        <v>0.7371529686246404</v>
       </c>
       <c r="K29" t="n">
-        <v>91.20229991586648</v>
+        <v>17.39419673883764</v>
       </c>
       <c r="L29" t="n">
-        <v>52.59974169016452</v>
+        <v>13.20418315547962</v>
       </c>
     </row>
     <row r="30">
@@ -1571,27 +1571,27 @@
         <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>7.956679582595825</v>
+        <v>199.4946460723877</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1631195370408529</v>
+        <v>0.7327682996256856</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.7359707138489484</v>
       </c>
       <c r="K30" t="n">
-        <v>91.1985454794509</v>
+        <v>17.43327136693664</v>
       </c>
       <c r="L30" t="n">
-        <v>52.59133960916441</v>
+        <v>13.23667225137099</v>
       </c>
     </row>
     <row r="31">
@@ -1609,27 +1609,27 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>10.55267238616943</v>
+        <v>247.0868356227875</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1637308957578318</v>
+        <v>0.7328899937014212</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.7359707138489484</v>
       </c>
       <c r="K31" t="n">
-        <v>91.1985454794509</v>
+        <v>17.43327136693664</v>
       </c>
       <c r="L31" t="n">
-        <v>52.59133960916441</v>
+        <v>13.23667225137099</v>
       </c>
     </row>
     <row r="32">
@@ -1647,27 +1647,27 @@
         <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>67.05084180831909</v>
+        <v>212.3113346099854</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4401797218112232</v>
+        <v>0.9086459277482887</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9234507192447867</v>
       </c>
       <c r="K32" t="n">
-        <v>70.91261193281821</v>
+        <v>9.386926059133257</v>
       </c>
       <c r="L32" t="n">
-        <v>35.09659729829767</v>
+        <v>5.775696783249589</v>
       </c>
     </row>
     <row r="33">
@@ -1685,27 +1685,27 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>104.0239977836609</v>
+        <v>366.6692905426025</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4797057452240424</v>
+        <v>0.9128931506703857</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9234507192447867</v>
       </c>
       <c r="K33" t="n">
-        <v>70.91261193281821</v>
+        <v>9.386926059133257</v>
       </c>
       <c r="L33" t="n">
-        <v>35.09659729829767</v>
+        <v>5.775696783249589</v>
       </c>
     </row>
     <row r="34">
@@ -1723,10 +1723,10 @@
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>5.446849346160889</v>
+        <v>15.64453220367432</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4881770610809326</v>
+        <v>0.9152503745433745</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.5276503562927246</v>
+        <v>0.9309440281122273</v>
       </c>
       <c r="K34" t="n">
-        <v>68.75205993652344</v>
+        <v>8.915659227845845</v>
       </c>
       <c r="L34" t="n">
-        <v>33.24764251708984</v>
+        <v>5.212121269458375</v>
       </c>
     </row>
     <row r="35">
@@ -1761,27 +1761,27 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>5.661454677581787</v>
+        <v>19.70489597320557</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5191580176353454</v>
+        <v>0.9202444657974951</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.5484093427658081</v>
+        <v>0.9309440281122273</v>
       </c>
       <c r="K35" t="n">
-        <v>67.22431182861328</v>
+        <v>8.915659227845845</v>
       </c>
       <c r="L35" t="n">
-        <v>33.18839645385742</v>
+        <v>5.212121269458375</v>
       </c>
     </row>
     <row r="36">
@@ -1799,10 +1799,10 @@
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>8.076727867126465</v>
+        <v>12.90986633300781</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4804153325581517</v>
+        <v>0.914363680035399</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1813,13 +1813,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9305517581909237</v>
       </c>
       <c r="K36" t="n">
-        <v>67.58548695620104</v>
+        <v>8.940945906678417</v>
       </c>
       <c r="L36" t="n">
-        <v>34.62104164052829</v>
+        <v>5.211787970198956</v>
       </c>
     </row>
     <row r="37">
@@ -1837,10 +1837,10 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>9.786618232727051</v>
+        <v>17.80681109428406</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5001636848295401</v>
+        <v>0.9189320204122685</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9305517581909237</v>
       </c>
       <c r="K37" t="n">
-        <v>67.58548695620104</v>
+        <v>8.940945906678417</v>
       </c>
       <c r="L37" t="n">
-        <v>34.62104164052829</v>
+        <v>5.211787970198956</v>
       </c>
     </row>
     <row r="38">
@@ -1875,10 +1875,10 @@
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>60.35610222816467</v>
+        <v>149.8692018985748</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5059173107368674</v>
+        <v>0.9161002400651177</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1889,13 +1889,13 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9306523814924526</v>
       </c>
       <c r="K38" t="n">
-        <v>64.1040218121336</v>
+        <v>8.93446630697939</v>
       </c>
       <c r="L38" t="n">
-        <v>30.19281732961743</v>
+        <v>5.068721809255267</v>
       </c>
     </row>
     <row r="39">
@@ -1913,10 +1913,10 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>118.0046970844269</v>
+        <v>291.6767017841339</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5359470634249959</v>
+        <v>0.9209918367104901</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9306523814924526</v>
       </c>
       <c r="K39" t="n">
-        <v>64.1040218121336</v>
+        <v>8.93446630697939</v>
       </c>
       <c r="L39" t="n">
-        <v>30.19281732961743</v>
+        <v>5.068721809255267</v>
       </c>
     </row>
     <row r="40">
@@ -1951,27 +1951,27 @@
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>138.0690364837646</v>
+        <v>359.0611598491669</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4742039714755084</v>
+        <v>0.9143654286374646</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0.5480245530595298</v>
+        <v>0.929790484223216</v>
       </c>
       <c r="K40" t="n">
-        <v>67.25295138365956</v>
+        <v>8.989816532636402</v>
       </c>
       <c r="L40" t="n">
-        <v>31.38330002219408</v>
+        <v>5.108558655758215</v>
       </c>
     </row>
     <row r="41">
@@ -1989,27 +1989,27 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>175.5471067428589</v>
+        <v>475.1110761165619</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5006287526437336</v>
+        <v>0.9195783641133068</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.5478088376009014</v>
+        <v>0.9298079132741046</v>
       </c>
       <c r="K41" t="n">
-        <v>67.26899846183061</v>
+        <v>8.988700631940874</v>
       </c>
       <c r="L41" t="n">
-        <v>31.30699612414678</v>
+        <v>5.102076726523771</v>
       </c>
     </row>
   </sheetData>
@@ -2103,23 +2103,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>34.96213316917419</v>
+        <v>61.78164196014404</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7424679277285154</v>
+        <v>0.9427398491413124</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9546202680460851</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9468293212200711</v>
       </c>
       <c r="H2" t="n">
-        <v>0.90826124945391</v>
+        <v>0.9903869894713397</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -2141,23 +2141,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>49.15799784660339</v>
+        <v>102.1410129070282</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7591605966879464</v>
+        <v>0.9447134275511153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9557959087702798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9481739773427895</v>
       </c>
       <c r="H3" t="n">
-        <v>0.90826124945391</v>
+        <v>0.9901331238317979</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -2179,23 +2179,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5657615661621094</v>
+        <v>1.819243192672729</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7178455340929982</v>
+        <v>0.9207321669579768</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9440395015283329</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9333833423014269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9545206207717516</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -2217,23 +2217,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8688530921936035</v>
+        <v>2.692499399185181</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7296280924933435</v>
+        <v>0.9272708256612205</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9262731188244236</v>
+        <v>0.9440395015283329</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7355279473071596</v>
+        <v>0.9333833423014269</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7828472139481314</v>
+        <v>0.9545206207717516</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'gini'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2255,23 +2255,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7582.797722101212</v>
+        <v>351.8641495704651</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7749083896227867</v>
+        <v>0.9284502465999035</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9419233482247825</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9324042859331567</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9788942174844476</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2293,19 +2293,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>13063.4157834053</v>
+        <v>761.6525349617004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7829275385741383</v>
+        <v>0.9328469405523752</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9454502703973665</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9369826450254473</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9795603357067736</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2331,19 +2331,19 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3.388538360595703</v>
+        <v>7.729877471923828</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7816443157726987</v>
+        <v>0.937197913778761</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9508582177286621</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9419507116201434</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9717784936272238</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2369,19 +2369,19 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.476355314254761</v>
+        <v>8.527689933776855</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7887837510961361</v>
+        <v>0.9413842056504705</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9414745376235115</v>
+        <v>0.9508582177286621</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7987217188801441</v>
+        <v>0.9419507116201434</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9096314388974939</v>
+        <v>0.9717784936272238</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2407,23 +2407,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.879142999649048</v>
+        <v>129.834644317627</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5708386073605726</v>
+        <v>0.9053356399652978</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7322016721560679</v>
+        <v>0.9172348930166941</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5792004344384017</v>
+        <v>0.9054590941791756</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7940013503316254</v>
+        <v>0.9696373805793969</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -2445,23 +2445,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3.306220293045044</v>
+        <v>222.530154466629</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5714566683306512</v>
+        <v>0.9051087342385802</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7332151000760071</v>
+        <v>0.9172348930166941</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5799855750471964</v>
+        <v>0.9054590941791756</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7939449541284403</v>
+        <v>0.9696373805793969</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -2483,23 +2483,23 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1857089996337891</v>
+        <v>0.3268022537231445</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5534276352203948</v>
+        <v>0.79106389788666</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.8074300493769104</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.7975398631827457</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.8671062626670155</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2521,19 +2521,19 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2213370800018311</v>
+        <v>0.4358818531036377</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5584974950698796</v>
+        <v>0.7912015650524316</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8697745122878136</v>
+        <v>0.8074300493769104</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5553941137590488</v>
+        <v>0.7975398631827457</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6969482505262322</v>
+        <v>0.8671067879968438</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2559,23 +2559,23 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>30.05495476722717</v>
+        <v>74.81637406349182</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7521014360203813</v>
+        <v>0.9421905253471752</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9450215353432987</v>
+        <v>0.9555607806254409</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7897204739826351</v>
+        <v>0.9476193061066791</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9349533341276461</v>
+        <v>0.9891931774364535</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 0.6}</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2597,23 +2597,23 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>58.17849445343018</v>
+        <v>153.9736731052399</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7677588908801928</v>
+        <v>0.9459086431217779</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9445148213833291</v>
+        <v>0.9562661650599577</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7926083122896885</v>
+        <v>0.9485504116966064</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9250530203741212</v>
+        <v>0.9887731762387013</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.8}</t>
+          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.8}</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2635,19 +2635,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>58.71340918540955</v>
+        <v>101.9579718112946</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7663753818038094</v>
+        <v>0.9414777373848328</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9467950342031923</v>
+        <v>0.9529743710322126</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8046094877089758</v>
+        <v>0.9445826512034934</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9339814925136026</v>
+        <v>0.9902825801679586</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2673,19 +2673,19 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>85.50505352020264</v>
+        <v>208.2088785171509</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7834056300532612</v>
+        <v>0.9443251101310539</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9447681783633139</v>
+        <v>0.9539148836115683</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7965198332895054</v>
+        <v>0.945737748115375</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9337503475118155</v>
+        <v>0.9901785648619486</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>111.6458830833435</v>
+        <v>292.0688977241516</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4357274358187564</v>
+        <v>0.9102965857569525</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.9273325445472385</v>
       </c>
       <c r="K2" t="n">
-        <v>71.48011178783491</v>
+        <v>9.145823506301472</v>
       </c>
       <c r="L2" t="n">
-        <v>34.12331542084517</v>
+        <v>5.264394540992574</v>
       </c>
     </row>
     <row r="3">
@@ -2825,10 +2825,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>150.6258206367493</v>
+        <v>416.8807187080383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4620163922841435</v>
+        <v>0.9158221695712907</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.4894214179550179</v>
+        <v>0.9273325445472385</v>
       </c>
       <c r="K3" t="n">
-        <v>71.48011178783491</v>
+        <v>9.145823506301472</v>
       </c>
       <c r="L3" t="n">
-        <v>34.12331542084517</v>
+        <v>5.264394540992574</v>
       </c>
     </row>
     <row r="4">
@@ -2863,27 +2863,27 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>15.49662733078003</v>
+        <v>31.36257743835449</v>
       </c>
       <c r="E4" t="n">
-        <v>0.200405995010477</v>
+        <v>0.8630177794140446</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'friedman_mse'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.2605617127993397</v>
+        <v>0.8888639939395483</v>
       </c>
       <c r="K4" t="n">
-        <v>86.02108054688992</v>
+        <v>11.31045906689468</v>
       </c>
       <c r="L4" t="n">
-        <v>38.02254877121864</v>
+        <v>6.040182151688382</v>
       </c>
     </row>
     <row r="5">
@@ -2901,10 +2901,10 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>30.89138531684875</v>
+        <v>86.33157324790955</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2494303631632399</v>
+        <v>0.8730497345442128</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -2915,13 +2915,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.3362235571106167</v>
+        <v>0.8855511189077954</v>
       </c>
       <c r="K5" t="n">
-        <v>81.50135784198201</v>
+        <v>11.47779900500352</v>
       </c>
       <c r="L5" t="n">
-        <v>37.53977704585761</v>
+        <v>6.316851478595777</v>
       </c>
     </row>
     <row r="6">
@@ -2939,10 +2939,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>106.9222595691681</v>
+        <v>342.1860818862915</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3296251448796029</v>
+        <v>0.8782810451903668</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -2953,13 +2953,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9002271579078316</v>
       </c>
       <c r="K6" t="n">
-        <v>80.89347428382811</v>
+        <v>10.71664912018776</v>
       </c>
       <c r="L6" t="n">
-        <v>32.98778734697751</v>
+        <v>6.050534389613801</v>
       </c>
     </row>
     <row r="7">
@@ -2977,10 +2977,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>180.7806396484375</v>
+        <v>794.1601617336273</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3439273431575175</v>
+        <v>0.882429566993066</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.3460882767829514</v>
+        <v>0.9002271579078316</v>
       </c>
       <c r="K7" t="n">
-        <v>80.89347428382811</v>
+        <v>10.71664912018776</v>
       </c>
       <c r="L7" t="n">
-        <v>32.98778734697751</v>
+        <v>6.050534389613801</v>
       </c>
     </row>
     <row r="8">
@@ -3015,10 +3015,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3.681244850158691</v>
+        <v>9.408438682556152</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4935003325207741</v>
+        <v>0.9029883463751035</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.5873816881539017</v>
+        <v>0.9210421468734596</v>
       </c>
       <c r="K8" t="n">
-        <v>64.25814371519127</v>
+        <v>9.533459047908195</v>
       </c>
       <c r="L8" t="n">
-        <v>29.24887821574554</v>
+        <v>5.22191277459623</v>
       </c>
     </row>
     <row r="9">
@@ -3053,27 +3053,27 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>4.550774812698364</v>
+        <v>11.40788674354553</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5309137658627969</v>
+        <v>0.9080335763132791</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.6036051296434839</v>
+        <v>0.9210421468734596</v>
       </c>
       <c r="K9" t="n">
-        <v>62.98221635411645</v>
+        <v>9.533459047908195</v>
       </c>
       <c r="L9" t="n">
-        <v>27.77407416552622</v>
+        <v>5.22191277459623</v>
       </c>
     </row>
     <row r="10">
@@ -3091,27 +3091,27 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4936785697937012</v>
+        <v>23.55539107322693</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1631081258955845</v>
+        <v>0.733920064339284</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.7375098266344251</v>
       </c>
       <c r="K10" t="n">
-        <v>91.204868609201</v>
+        <v>17.38238498910604</v>
       </c>
       <c r="L10" t="n">
-        <v>52.61355946207429</v>
+        <v>13.21099620560328</v>
       </c>
     </row>
     <row r="11">
@@ -3129,27 +3129,27 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6994311809539795</v>
+        <v>51.92563271522522</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1637077778427174</v>
+        <v>0.7339708525065632</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
+          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.1687566366856434</v>
+        <v>0.7375098266344251</v>
       </c>
       <c r="K11" t="n">
-        <v>91.204868609201</v>
+        <v>17.38238498910604</v>
       </c>
       <c r="L11" t="n">
-        <v>52.61355946207429</v>
+        <v>13.21099620560328</v>
       </c>
     </row>
     <row r="12">
@@ -3167,27 +3167,27 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>5.73303747177124</v>
+        <v>183.1296489238739</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1631297501254156</v>
+        <v>0.7337649931248545</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.168803458291798</v>
+        <v>0.7371529686246404</v>
       </c>
       <c r="K12" t="n">
-        <v>91.20229991586648</v>
+        <v>17.39419673883764</v>
       </c>
       <c r="L12" t="n">
-        <v>52.59974169016452</v>
+        <v>13.20418315547962</v>
       </c>
     </row>
     <row r="13">
@@ -3205,27 +3205,27 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>6.808621406555176</v>
+        <v>206.5332767963409</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1637257443267972</v>
+        <v>0.7338476286732339</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.168803458291798</v>
+        <v>0.7371529686246404</v>
       </c>
       <c r="K13" t="n">
-        <v>91.20229991586648</v>
+        <v>17.39419673883764</v>
       </c>
       <c r="L13" t="n">
-        <v>52.59974169016452</v>
+        <v>13.20418315547962</v>
       </c>
     </row>
     <row r="14">
@@ -3243,27 +3243,27 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>7.956679582595825</v>
+        <v>199.4946460723877</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1631195370408529</v>
+        <v>0.7327682996256856</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.7359707138489484</v>
       </c>
       <c r="K14" t="n">
-        <v>91.1985454794509</v>
+        <v>17.43327136693664</v>
       </c>
       <c r="L14" t="n">
-        <v>52.59133960916441</v>
+        <v>13.23667225137099</v>
       </c>
     </row>
     <row r="15">
@@ -3281,27 +3281,27 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>10.55267238616943</v>
+        <v>247.0868356227875</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1637308957578318</v>
+        <v>0.7328899937014212</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.5, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.1688718910031372</v>
+        <v>0.7359707138489484</v>
       </c>
       <c r="K15" t="n">
-        <v>91.1985454794509</v>
+        <v>17.43327136693664</v>
       </c>
       <c r="L15" t="n">
-        <v>52.59133960916441</v>
+        <v>13.23667225137099</v>
       </c>
     </row>
     <row r="16">
@@ -3319,27 +3319,27 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>67.05084180831909</v>
+        <v>212.3113346099854</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4401797218112232</v>
+        <v>0.9086459277482887</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9234507192447867</v>
       </c>
       <c r="K16" t="n">
-        <v>70.91261193281821</v>
+        <v>9.386926059133257</v>
       </c>
       <c r="L16" t="n">
-        <v>35.09659729829767</v>
+        <v>5.775696783249589</v>
       </c>
     </row>
     <row r="17">
@@ -3357,27 +3357,27 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>104.0239977836609</v>
+        <v>366.6692905426025</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4797057452240424</v>
+        <v>0.9128931506703857</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.4974964768614818</v>
+        <v>0.9234507192447867</v>
       </c>
       <c r="K17" t="n">
-        <v>70.91261193281821</v>
+        <v>9.386926059133257</v>
       </c>
       <c r="L17" t="n">
-        <v>35.09659729829767</v>
+        <v>5.775696783249589</v>
       </c>
     </row>
     <row r="18">
@@ -3395,10 +3395,10 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>5.446849346160889</v>
+        <v>15.64453220367432</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4881770610809326</v>
+        <v>0.9152503745433745</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -3409,13 +3409,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.5276503562927246</v>
+        <v>0.9309440281122273</v>
       </c>
       <c r="K18" t="n">
-        <v>68.75205993652344</v>
+        <v>8.915659227845845</v>
       </c>
       <c r="L18" t="n">
-        <v>33.24764251708984</v>
+        <v>5.212121269458375</v>
       </c>
     </row>
     <row r="19">
@@ -3433,27 +3433,27 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>5.661454677581787</v>
+        <v>19.70489597320557</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5191580176353454</v>
+        <v>0.9202444657974951</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 5, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.5484093427658081</v>
+        <v>0.9309440281122273</v>
       </c>
       <c r="K19" t="n">
-        <v>67.22431182861328</v>
+        <v>8.915659227845845</v>
       </c>
       <c r="L19" t="n">
-        <v>33.18839645385742</v>
+        <v>5.212121269458375</v>
       </c>
     </row>
     <row r="20">
@@ -3471,10 +3471,10 @@
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>8.076727867126465</v>
+        <v>12.90986633300781</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4804153325581517</v>
+        <v>0.914363680035399</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -3485,13 +3485,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9305517581909237</v>
       </c>
       <c r="K20" t="n">
-        <v>67.58548695620104</v>
+        <v>8.940945906678417</v>
       </c>
       <c r="L20" t="n">
-        <v>34.62104164052829</v>
+        <v>5.211787970198956</v>
       </c>
     </row>
     <row r="21">
@@ -3509,10 +3509,10 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>9.786618232727051</v>
+        <v>17.80681109428406</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5001636848295401</v>
+        <v>0.9189320204122685</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -3523,13 +3523,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.5435438726227794</v>
+        <v>0.9305517581909237</v>
       </c>
       <c r="K21" t="n">
-        <v>67.58548695620104</v>
+        <v>8.940945906678417</v>
       </c>
       <c r="L21" t="n">
-        <v>34.62104164052829</v>
+        <v>5.211787970198956</v>
       </c>
     </row>
     <row r="22">
@@ -3547,10 +3547,10 @@
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>60.35610222816467</v>
+        <v>149.8692018985748</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5059173107368674</v>
+        <v>0.9161002400651177</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -3561,13 +3561,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9306523814924526</v>
       </c>
       <c r="K22" t="n">
-        <v>64.1040218121336</v>
+        <v>8.93446630697939</v>
       </c>
       <c r="L22" t="n">
-        <v>30.19281732961743</v>
+        <v>5.068721809255267</v>
       </c>
     </row>
     <row r="23">
@@ -3585,10 +3585,10 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>118.0046970844269</v>
+        <v>291.6767017841339</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5359470634249959</v>
+        <v>0.9209918367104901</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -3599,13 +3599,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.589358628410138</v>
+        <v>0.9306523814924526</v>
       </c>
       <c r="K23" t="n">
-        <v>64.1040218121336</v>
+        <v>8.93446630697939</v>
       </c>
       <c r="L23" t="n">
-        <v>30.19281732961743</v>
+        <v>5.068721809255267</v>
       </c>
     </row>
     <row r="24">
@@ -3623,27 +3623,27 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>138.0690364837646</v>
+        <v>359.0611598491669</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4742039714755084</v>
+        <v>0.9143654286374646</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.5480245530595298</v>
+        <v>0.929790484223216</v>
       </c>
       <c r="K24" t="n">
-        <v>67.25295138365956</v>
+        <v>8.989816532636402</v>
       </c>
       <c r="L24" t="n">
-        <v>31.38330002219408</v>
+        <v>5.108558655758215</v>
       </c>
     </row>
     <row r="25">
@@ -3661,27 +3661,27 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>175.5471067428589</v>
+        <v>475.1110761165619</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5006287526437336</v>
+        <v>0.9195783641133068</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'cv': 5}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.5478088376009014</v>
+        <v>0.9298079132741046</v>
       </c>
       <c r="K25" t="n">
-        <v>67.26899846183061</v>
+        <v>8.988700631940874</v>
       </c>
       <c r="L25" t="n">
-        <v>31.30699612414678</v>
+        <v>5.102076726523771</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -507,23 +507,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>61.78164196014404</v>
+        <v>113.2630970478058</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9427398491413124</v>
+        <v>0.3720115955028341</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9546202680460851</v>
+        <v>0.7020408163265306</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9468293212200711</v>
+        <v>0.5078676263535075</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9903869894713397</v>
+        <v>0.9497494099680689</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -545,23 +545,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>102.1410129070282</v>
+        <v>207.853880405426</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9447134275511153</v>
+        <v>0.3973386578538888</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9557959087702798</v>
+        <v>0.6836734693877551</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9481739773427895</v>
+        <v>0.4908803299777239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9901331238317979</v>
+        <v>0.9468468867138693</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -583,23 +583,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.819243192672729</v>
+        <v>0.9261305332183838</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9207321669579768</v>
+        <v>0.3391992867247582</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9440395015283329</v>
+        <v>0.613265306122449</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9333833423014269</v>
+        <v>0.4332895651444917</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9545206207717516</v>
+        <v>0.7744047619047619</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -621,23 +621,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.692499399185181</v>
+        <v>1.807075500488281</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9272708256612205</v>
+        <v>0.3503912807052719</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9440395015283329</v>
+        <v>0.613265306122449</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9333833423014269</v>
+        <v>0.4332895651444917</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9545206207717516</v>
+        <v>0.7744047619047619</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -659,23 +659,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>351.8641495704651</v>
+        <v>636.6349778175354</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9284502465999035</v>
+        <v>0.339159554098232</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9419233482247825</v>
+        <v>0.6244897959183674</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9324042859331567</v>
+        <v>0.3801460934017369</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9788942174844476</v>
+        <v>0.9203715465778147</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'C': 100, 'class_weight': None, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -697,23 +697,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>761.6525349617004</v>
+        <v>1314.020700931549</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9328469405523752</v>
+        <v>0.3495388752192812</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9454502703973665</v>
+        <v>0.6163265306122448</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9369826450254473</v>
+        <v>0.3868945733264785</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9795603357067736</v>
+        <v>0.9204642162987644</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -735,23 +735,23 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>7.729877471923828</v>
+        <v>0.5380501747131348</v>
       </c>
       <c r="E8" t="n">
-        <v>0.937197913778761</v>
+        <v>0.3731252769552402</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9508582177286621</v>
+        <v>0.6775510204081633</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9419507116201434</v>
+        <v>0.4912773562421409</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9717784936272238</v>
+        <v>0.941466576426489</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -773,23 +773,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>8.527689933776855</v>
+        <v>0.6125397682189941</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9413842056504705</v>
+        <v>0.3930298749540874</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9508582177286621</v>
+        <v>0.6775510204081633</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9419507116201434</v>
+        <v>0.4948636883981792</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9717784936272238</v>
+        <v>0.9371775649035123</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -811,23 +811,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>129.834644317627</v>
+        <v>70.75936245918274</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9053356399652978</v>
+        <v>0.2961390255365762</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9172348930166941</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9054590941791756</v>
+        <v>0.2721936515775019</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9696373805793969</v>
+        <v>0.8458810565042343</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -849,23 +849,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>222.530154466629</v>
+        <v>139.754597902298</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9051087342385802</v>
+        <v>0.2921261617486491</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9172348930166941</v>
+        <v>0.4581632653061224</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9054590941791756</v>
+        <v>0.2728290119081531</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9696373805793969</v>
+        <v>0.8460117312231015</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -887,23 +887,23 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3268022537231445</v>
+        <v>0.0595390796661377</v>
       </c>
       <c r="E12" t="n">
-        <v>0.79106389788666</v>
+        <v>0.2583424476388876</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8074300493769104</v>
+        <v>0.4326530612244898</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7975398631827457</v>
+        <v>0.2576611820510127</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8671062626670155</v>
+        <v>0.8504772317090102</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-05}</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -925,23 +925,23 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4358818531036377</v>
+        <v>0.04764246940612793</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7912015650524316</v>
+        <v>0.2529756910104267</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8074300493769104</v>
+        <v>0.4326530612244898</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7975398631827457</v>
+        <v>0.2576611820510127</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8671067879968438</v>
+        <v>0.850476537553797</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -963,23 +963,23 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>74.81637406349182</v>
+        <v>3.838783740997314</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9421905253471752</v>
+        <v>0.3702938726305914</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9555607806254409</v>
+        <v>0.6795918367346939</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9476193061066791</v>
+        <v>0.4957490656219858</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9891931774364535</v>
+        <v>0.9393980806608357</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 0.6}</t>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 25}</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1001,23 +1001,23 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>153.9736731052399</v>
+        <v>7.496529817581177</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9459086431217779</v>
+        <v>0.3947567302277579</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9562661650599577</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9485504116966064</v>
+        <v>0.5166914607998288</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9887731762387013</v>
+        <v>0.9459208836595863</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.8}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1039,19 +1039,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>101.9579718112946</v>
+        <v>10.09751319885254</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9414777373848328</v>
+        <v>0.3856052350539436</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9529743710322126</v>
+        <v>0.686734693877551</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9445826512034934</v>
+        <v>0.5042296191044431</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9902825801679586</v>
+        <v>0.9515792031098153</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>208.2088785171509</v>
+        <v>13.40703725814819</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9443251101310539</v>
+        <v>0.408905626066224</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9539148836115683</v>
+        <v>0.6908163265306122</v>
       </c>
       <c r="G17" t="n">
-        <v>0.945737748115375</v>
+        <v>0.4947434728497458</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9901785648619486</v>
+        <v>0.950504130223518</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1115,27 +1115,27 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>292.0688977241516</v>
+        <v>88.95418930053711</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9102965857569525</v>
+        <v>0.4632401988762054</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.9273325445472385</v>
+        <v>0.5541589867760863</v>
       </c>
       <c r="K18" t="n">
-        <v>9.145823506301472</v>
+        <v>0.5876154250486469</v>
       </c>
       <c r="L18" t="n">
-        <v>5.264394540992574</v>
+        <v>0.4176122448979592</v>
       </c>
     </row>
     <row r="19">
@@ -1153,27 +1153,27 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>416.8807187080383</v>
+        <v>175.4782721996307</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9158221695712907</v>
+        <v>0.4938420438668326</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.9273325445472385</v>
+        <v>0.5543425190507176</v>
       </c>
       <c r="K19" t="n">
-        <v>9.145823506301472</v>
+        <v>0.5874944654537398</v>
       </c>
       <c r="L19" t="n">
-        <v>5.264394540992574</v>
+        <v>0.4179591836734693</v>
       </c>
     </row>
     <row r="20">
@@ -1191,27 +1191,27 @@
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>31.36257743835449</v>
+        <v>19.01388764381409</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8630177794140446</v>
+        <v>0.2750714284478929</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'friedman_mse'}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.8888639939395483</v>
+        <v>0.3023159180823696</v>
       </c>
       <c r="K20" t="n">
-        <v>11.31045906689468</v>
+        <v>0.7350765803607523</v>
       </c>
       <c r="L20" t="n">
-        <v>6.040182151688382</v>
+        <v>0.5692981466247743</v>
       </c>
     </row>
     <row r="21">
@@ -1229,27 +1229,27 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>86.33157324790955</v>
+        <v>32.88626933097839</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8730497345442128</v>
+        <v>0.2931724278316331</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.8855511189077954</v>
+        <v>0.3119320545342128</v>
       </c>
       <c r="K21" t="n">
-        <v>11.47779900500352</v>
+        <v>0.7299932462967971</v>
       </c>
       <c r="L21" t="n">
-        <v>6.316851478595777</v>
+        <v>0.5644500073791107</v>
       </c>
     </row>
     <row r="22">
@@ -1267,27 +1267,27 @@
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>342.1860818862915</v>
+        <v>80.29093623161316</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8782810451903668</v>
+        <v>0.3812621241616503</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.9002271579078316</v>
+        <v>0.4035728160022128</v>
       </c>
       <c r="K22" t="n">
-        <v>10.71664912018776</v>
+        <v>0.6796446363370173</v>
       </c>
       <c r="L22" t="n">
-        <v>6.050534389613801</v>
+        <v>0.5177601079262396</v>
       </c>
     </row>
     <row r="23">
@@ -1305,27 +1305,27 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>794.1601617336273</v>
+        <v>184.3960673809052</v>
       </c>
       <c r="E23" t="n">
-        <v>0.882429566993066</v>
+        <v>0.3962985813470993</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.9002271579078316</v>
+        <v>0.4035728160022128</v>
       </c>
       <c r="K23" t="n">
-        <v>10.71664912018776</v>
+        <v>0.6796446363370173</v>
       </c>
       <c r="L23" t="n">
-        <v>6.050534389613801</v>
+        <v>0.5177601079262396</v>
       </c>
     </row>
     <row r="24">
@@ -1343,27 +1343,27 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>9.408438682556152</v>
+        <v>0.4648361206054688</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9029883463751035</v>
+        <v>0.4611791357184896</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.9210421468734596</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="K24" t="n">
-        <v>9.533459047908195</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="L24" t="n">
-        <v>5.22191277459623</v>
+        <v>0.3799547808937107</v>
       </c>
     </row>
     <row r="25">
@@ -1381,27 +1381,27 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>11.40788674354553</v>
+        <v>0.5001530647277832</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9080335763132791</v>
+        <v>0.4869014791301536</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.9210421468734596</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="K25" t="n">
-        <v>9.533459047908195</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="L25" t="n">
-        <v>5.22191277459623</v>
+        <v>0.3799547808937107</v>
       </c>
     </row>
     <row r="26">
@@ -1419,27 +1419,27 @@
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>23.55539107322693</v>
+        <v>0.103060245513916</v>
       </c>
       <c r="E26" t="n">
-        <v>0.733920064339284</v>
+        <v>0.2756427052041309</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.7375098266344251</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="K26" t="n">
-        <v>17.38238498910604</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="L26" t="n">
-        <v>13.21099620560328</v>
+        <v>0.5863230154211657</v>
       </c>
     </row>
     <row r="27">
@@ -1457,27 +1457,27 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>51.92563271522522</v>
+        <v>0.1919951438903809</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7339708525065632</v>
+        <v>0.2772285011706008</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.7375098266344251</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="K27" t="n">
-        <v>17.38238498910604</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="L27" t="n">
-        <v>13.21099620560328</v>
+        <v>0.5863230154211657</v>
       </c>
     </row>
     <row r="28">
@@ -1495,27 +1495,27 @@
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>183.1296489238739</v>
+        <v>0.03827381134033203</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7337649931248545</v>
+        <v>0.2762198267065196</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.7371529686246404</v>
+        <v>0.2642087227138233</v>
       </c>
       <c r="K28" t="n">
-        <v>17.39419673883764</v>
+        <v>0.7548844799725748</v>
       </c>
       <c r="L28" t="n">
-        <v>13.20418315547962</v>
+        <v>0.5870174989191963</v>
       </c>
     </row>
     <row r="29">
@@ -1533,27 +1533,27 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>206.5332767963409</v>
+        <v>0.1115138530731201</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7338476286732339</v>
+        <v>0.2776218701339047</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'random', 'tol': 0.0001}</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.7371529686246404</v>
+        <v>0.2642022548184634</v>
       </c>
       <c r="K29" t="n">
-        <v>17.39419673883764</v>
+        <v>0.7548877978313523</v>
       </c>
       <c r="L29" t="n">
-        <v>13.20418315547962</v>
+        <v>0.5870198778151539</v>
       </c>
     </row>
     <row r="30">
@@ -1571,27 +1571,27 @@
         <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>199.4946460723877</v>
+        <v>0.08172798156738281</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7327682996256856</v>
+        <v>0.2766903121172088</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.7359707138489484</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="K30" t="n">
-        <v>17.43327136693664</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="L30" t="n">
-        <v>13.23667225137099</v>
+        <v>0.5882492388088877</v>
       </c>
     </row>
     <row r="31">
@@ -1609,27 +1609,27 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>247.0868356227875</v>
+        <v>0.1224496364593506</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7328899937014212</v>
+        <v>0.2779434303402907</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0.7359707138489484</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="K31" t="n">
-        <v>17.43327136693664</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="L31" t="n">
-        <v>13.23667225137099</v>
+        <v>0.5882492388088877</v>
       </c>
     </row>
     <row r="32">
@@ -1647,27 +1647,27 @@
         <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>212.3113346099854</v>
+        <v>37.40417456626892</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9086459277482887</v>
+        <v>0.440750682226018</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.9234507192447867</v>
+        <v>0.5417900273946938</v>
       </c>
       <c r="K32" t="n">
-        <v>9.386926059133257</v>
+        <v>0.5957107641453661</v>
       </c>
       <c r="L32" t="n">
-        <v>5.775696783249589</v>
+        <v>0.4244218364523328</v>
       </c>
     </row>
     <row r="33">
@@ -1685,27 +1685,27 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>366.6692905426025</v>
+        <v>70.7239203453064</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9128931506703857</v>
+        <v>0.4777373636797072</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.9234507192447867</v>
+        <v>0.5291968951379508</v>
       </c>
       <c r="K33" t="n">
-        <v>9.386926059133257</v>
+        <v>0.603841334418266</v>
       </c>
       <c r="L33" t="n">
-        <v>5.775696783249589</v>
+        <v>0.4316743421594985</v>
       </c>
     </row>
     <row r="34">
@@ -1723,27 +1723,27 @@
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>15.64453220367432</v>
+        <v>6.800420999526978</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9152503745433745</v>
+        <v>0.4397318959236145</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 250}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.9309440281122273</v>
+        <v>0.5523912906646729</v>
       </c>
       <c r="K34" t="n">
-        <v>8.915659227845845</v>
+        <v>0.5887791514396667</v>
       </c>
       <c r="L34" t="n">
-        <v>5.212121269458375</v>
+        <v>0.4128801226615906</v>
       </c>
     </row>
     <row r="35">
@@ -1761,27 +1761,27 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>19.70489597320557</v>
+        <v>7.363279819488525</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9202444657974951</v>
+        <v>0.4839082956314087</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 5, 'n_estimators': 250}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.9309440281122273</v>
+        <v>0.5292840003967285</v>
       </c>
       <c r="K35" t="n">
-        <v>8.915659227845845</v>
+        <v>0.6037854552268982</v>
       </c>
       <c r="L35" t="n">
-        <v>5.212121269458375</v>
+        <v>0.4324872493743896</v>
       </c>
     </row>
     <row r="36">
@@ -1799,27 +1799,27 @@
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>12.90986633300781</v>
+        <v>31.34100079536438</v>
       </c>
       <c r="E36" t="n">
-        <v>0.914363680035399</v>
+        <v>0.4221265380535599</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 100}</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.9305517581909237</v>
+        <v>0.5242101900276488</v>
       </c>
       <c r="K36" t="n">
-        <v>8.940945906678417</v>
+        <v>0.607030828128258</v>
       </c>
       <c r="L36" t="n">
-        <v>5.211787970198956</v>
+        <v>0.4489069112717186</v>
       </c>
     </row>
     <row r="37">
@@ -1837,27 +1837,27 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>17.80681109428406</v>
+        <v>33.56432199478149</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9189320204122685</v>
+        <v>0.4569217333243272</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 50}</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.9305517581909237</v>
+        <v>0.5110951993178363</v>
       </c>
       <c r="K37" t="n">
-        <v>8.940945906678417</v>
+        <v>0.6153402589496745</v>
       </c>
       <c r="L37" t="n">
-        <v>5.211787970198956</v>
+        <v>0.4525967415825661</v>
       </c>
     </row>
     <row r="38">
@@ -1875,27 +1875,27 @@
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>149.8692018985748</v>
+        <v>7.273386716842651</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9161002400651177</v>
+        <v>0.4742876429367182</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.9306523814924526</v>
+        <v>0.5669789924496238</v>
       </c>
       <c r="K38" t="n">
-        <v>8.93446630697939</v>
+        <v>0.5791054634132733</v>
       </c>
       <c r="L38" t="n">
-        <v>5.068721809255267</v>
+        <v>0.4152397959183673</v>
       </c>
     </row>
     <row r="39">
@@ -1913,27 +1913,27 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>291.6767017841339</v>
+        <v>13.36617517471313</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9209918367104901</v>
+        <v>0.5047939318645751</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.9306523814924526</v>
+        <v>0.5669789924496238</v>
       </c>
       <c r="K39" t="n">
-        <v>8.93446630697939</v>
+        <v>0.5791054634132733</v>
       </c>
       <c r="L39" t="n">
-        <v>5.068721809255267</v>
+        <v>0.4152397959183673</v>
       </c>
     </row>
     <row r="40">
@@ -1951,10 +1951,10 @@
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>359.0611598491669</v>
+        <v>11.00290584564209</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9143654286374646</v>
+        <v>0.4623585754058815</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -1965,13 +1965,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0.929790484223216</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="K40" t="n">
-        <v>8.989816532636402</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="L40" t="n">
-        <v>5.108558655758215</v>
+        <v>0.4270981493479949</v>
       </c>
     </row>
     <row r="41">
@@ -1989,27 +1989,27 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>475.1110761165619</v>
+        <v>13.14061999320984</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9195783641133068</v>
+        <v>0.48977812589358</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.9298079132741046</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="K41" t="n">
-        <v>8.988700631940874</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="L41" t="n">
-        <v>5.102076726523771</v>
+        <v>0.4270981493479949</v>
       </c>
     </row>
   </sheetData>
@@ -2103,23 +2103,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>61.78164196014404</v>
+        <v>113.2630970478058</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9427398491413124</v>
+        <v>0.3720115955028341</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9546202680460851</v>
+        <v>0.7020408163265306</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9468293212200711</v>
+        <v>0.5078676263535075</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9903869894713397</v>
+        <v>0.9497494099680689</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -2141,23 +2141,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>102.1410129070282</v>
+        <v>207.853880405426</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9447134275511153</v>
+        <v>0.3973386578538888</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9557959087702798</v>
+        <v>0.6836734693877551</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9481739773427895</v>
+        <v>0.4908803299777239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9901331238317979</v>
+        <v>0.9468468867138693</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -2179,23 +2179,23 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.819243192672729</v>
+        <v>0.9261305332183838</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9207321669579768</v>
+        <v>0.3391992867247582</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9440395015283329</v>
+        <v>0.613265306122449</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9333833423014269</v>
+        <v>0.4332895651444917</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9545206207717516</v>
+        <v>0.7744047619047619</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -2217,23 +2217,23 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.692499399185181</v>
+        <v>1.807075500488281</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9272708256612205</v>
+        <v>0.3503912807052719</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9440395015283329</v>
+        <v>0.613265306122449</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9333833423014269</v>
+        <v>0.4332895651444917</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9545206207717516</v>
+        <v>0.7744047619047619</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2255,23 +2255,23 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>351.8641495704651</v>
+        <v>636.6349778175354</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9284502465999035</v>
+        <v>0.339159554098232</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9419233482247825</v>
+        <v>0.6244897959183674</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9324042859331567</v>
+        <v>0.3801460934017369</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9788942174844476</v>
+        <v>0.9203715465778147</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'C': 100, 'class_weight': None, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2293,23 +2293,23 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>761.6525349617004</v>
+        <v>1314.020700931549</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9328469405523752</v>
+        <v>0.3495388752192812</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9454502703973665</v>
+        <v>0.6163265306122448</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9369826450254473</v>
+        <v>0.3868945733264785</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9795603357067736</v>
+        <v>0.9204642162987644</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -2331,23 +2331,23 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>7.729877471923828</v>
+        <v>0.5380501747131348</v>
       </c>
       <c r="E8" t="n">
-        <v>0.937197913778761</v>
+        <v>0.3731252769552402</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9508582177286621</v>
+        <v>0.6775510204081633</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9419507116201434</v>
+        <v>0.4912773562421409</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9717784936272238</v>
+        <v>0.941466576426489</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -2369,23 +2369,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>8.527689933776855</v>
+        <v>0.6125397682189941</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9413842056504705</v>
+        <v>0.3930298749540874</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9508582177286621</v>
+        <v>0.6775510204081633</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9419507116201434</v>
+        <v>0.4948636883981792</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9717784936272238</v>
+        <v>0.9371775649035123</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -2407,23 +2407,23 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>129.834644317627</v>
+        <v>70.75936245918274</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9053356399652978</v>
+        <v>0.2961390255365762</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9172348930166941</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9054590941791756</v>
+        <v>0.2721936515775019</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9696373805793969</v>
+        <v>0.8458810565042343</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -2445,23 +2445,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>222.530154466629</v>
+        <v>139.754597902298</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9051087342385802</v>
+        <v>0.2921261617486491</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9172348930166941</v>
+        <v>0.4581632653061224</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9054590941791756</v>
+        <v>0.2728290119081531</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9696373805793969</v>
+        <v>0.8460117312231015</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': None, 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'max_iter': 5000, 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -2483,23 +2483,23 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3268022537231445</v>
+        <v>0.0595390796661377</v>
       </c>
       <c r="E12" t="n">
-        <v>0.79106389788666</v>
+        <v>0.2583424476388876</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8074300493769104</v>
+        <v>0.4326530612244898</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7975398631827457</v>
+        <v>0.2576611820510127</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8671062626670155</v>
+        <v>0.8504772317090102</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-05}</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -2521,23 +2521,23 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4358818531036377</v>
+        <v>0.04764246940612793</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7912015650524316</v>
+        <v>0.2529756910104267</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8074300493769104</v>
+        <v>0.4326530612244898</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7975398631827457</v>
+        <v>0.2576611820510127</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8671067879968438</v>
+        <v>0.850476537553797</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'priors': None, 'var_smoothing': 1e-11}</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -2559,23 +2559,23 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>74.81637406349182</v>
+        <v>3.838783740997314</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9421905253471752</v>
+        <v>0.3702938726305914</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9555607806254409</v>
+        <v>0.6795918367346939</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9476193061066791</v>
+        <v>0.4957490656219858</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9891931774364535</v>
+        <v>0.9393980806608357</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 0.6}</t>
+          <t>{'max_features': 1.0, 'max_samples': 1.0, 'n_estimators': 25}</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2597,23 +2597,23 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>153.9736731052399</v>
+        <v>7.496529817581177</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9459086431217779</v>
+        <v>0.3947567302277579</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9562661650599577</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9485504116966064</v>
+        <v>0.5166914607998288</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9887731762387013</v>
+        <v>0.9459208836595863</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.6, 'max_features': 0.8}</t>
+          <t>{'max_features': 1.0, 'max_samples': 0.8, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2635,19 +2635,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>101.9579718112946</v>
+        <v>10.09751319885254</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9414777373848328</v>
+        <v>0.3856052350539436</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9529743710322126</v>
+        <v>0.686734693877551</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9445826512034934</v>
+        <v>0.5042296191044431</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9902825801679586</v>
+        <v>0.9515792031098153</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2673,19 +2673,19 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>208.2088785171509</v>
+        <v>13.40703725814819</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9443251101310539</v>
+        <v>0.408905626066224</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9539148836115683</v>
+        <v>0.6908163265306122</v>
       </c>
       <c r="G17" t="n">
-        <v>0.945737748115375</v>
+        <v>0.4947434728497458</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9901785648619486</v>
+        <v>0.950504130223518</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2787,27 +2787,27 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>292.0688977241516</v>
+        <v>88.95418930053711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9102965857569525</v>
+        <v>0.4632401988762054</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.9273325445472385</v>
+        <v>0.5541589867760863</v>
       </c>
       <c r="K2" t="n">
-        <v>9.145823506301472</v>
+        <v>0.5876154250486469</v>
       </c>
       <c r="L2" t="n">
-        <v>5.264394540992574</v>
+        <v>0.4176122448979592</v>
       </c>
     </row>
     <row r="3">
@@ -2825,27 +2825,27 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>416.8807187080383</v>
+        <v>175.4782721996307</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9158221695712907</v>
+        <v>0.4938420438668326</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 250}</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.9273325445472385</v>
+        <v>0.5543425190507176</v>
       </c>
       <c r="K3" t="n">
-        <v>9.145823506301472</v>
+        <v>0.5874944654537398</v>
       </c>
       <c r="L3" t="n">
-        <v>5.264394540992574</v>
+        <v>0.4179591836734693</v>
       </c>
     </row>
     <row r="4">
@@ -2863,27 +2863,27 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>31.36257743835449</v>
+        <v>19.01388764381409</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8630177794140446</v>
+        <v>0.2750714284478929</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'friedman_mse'}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.8888639939395483</v>
+        <v>0.3023159180823696</v>
       </c>
       <c r="K4" t="n">
-        <v>11.31045906689468</v>
+        <v>0.7350765803607523</v>
       </c>
       <c r="L4" t="n">
-        <v>6.040182151688382</v>
+        <v>0.5692981466247743</v>
       </c>
     </row>
     <row r="5">
@@ -2901,27 +2901,27 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>86.33157324790955</v>
+        <v>32.88626933097839</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8730497345442128</v>
+        <v>0.2931724278316331</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.8855511189077954</v>
+        <v>0.3119320545342128</v>
       </c>
       <c r="K5" t="n">
-        <v>11.47779900500352</v>
+        <v>0.7299932462967971</v>
       </c>
       <c r="L5" t="n">
-        <v>6.316851478595777</v>
+        <v>0.5644500073791107</v>
       </c>
     </row>
     <row r="6">
@@ -2939,27 +2939,27 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>342.1860818862915</v>
+        <v>80.29093623161316</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8782810451903668</v>
+        <v>0.3812621241616503</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.9002271579078316</v>
+        <v>0.4035728160022128</v>
       </c>
       <c r="K6" t="n">
-        <v>10.71664912018776</v>
+        <v>0.6796446363370173</v>
       </c>
       <c r="L6" t="n">
-        <v>6.050534389613801</v>
+        <v>0.5177601079262396</v>
       </c>
     </row>
     <row r="7">
@@ -2977,27 +2977,27 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>794.1601617336273</v>
+        <v>184.3960673809052</v>
       </c>
       <c r="E7" t="n">
-        <v>0.882429566993066</v>
+        <v>0.3962985813470993</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
+          <t>{'C': 1, 'epsilon': 0.2, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.9002271579078316</v>
+        <v>0.4035728160022128</v>
       </c>
       <c r="K7" t="n">
-        <v>10.71664912018776</v>
+        <v>0.6796446363370173</v>
       </c>
       <c r="L7" t="n">
-        <v>6.050534389613801</v>
+        <v>0.5177601079262396</v>
       </c>
     </row>
     <row r="8">
@@ -3015,27 +3015,27 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>9.408438682556152</v>
+        <v>0.4648361206054688</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9029883463751035</v>
+        <v>0.4611791357184896</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.9210421468734596</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="K8" t="n">
-        <v>9.533459047908195</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="L8" t="n">
-        <v>5.22191277459623</v>
+        <v>0.3799547808937107</v>
       </c>
     </row>
     <row r="9">
@@ -3053,27 +3053,27 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>11.40788674354553</v>
+        <v>0.5001530647277832</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9080335763132791</v>
+        <v>0.4869014791301536</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.9210421468734596</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="K9" t="n">
-        <v>9.533459047908195</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="L9" t="n">
-        <v>5.22191277459623</v>
+        <v>0.3799547808937107</v>
       </c>
     </row>
     <row r="10">
@@ -3091,27 +3091,27 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>23.55539107322693</v>
+        <v>0.103060245513916</v>
       </c>
       <c r="E10" t="n">
-        <v>0.733920064339284</v>
+        <v>0.2756427052041309</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.7375098266344251</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="K10" t="n">
-        <v>17.38238498910604</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="L10" t="n">
-        <v>13.21099620560328</v>
+        <v>0.5863230154211657</v>
       </c>
     </row>
     <row r="11">
@@ -3129,27 +3129,27 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>51.92563271522522</v>
+        <v>0.1919951438903809</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7339708525065632</v>
+        <v>0.2772285011706008</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'svd', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'alpha': 1.0, 'max_iter': 10000, 'solver': 'saga'}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.7375098266344251</v>
+        <v>0.2651571125229343</v>
       </c>
       <c r="K11" t="n">
-        <v>17.38238498910604</v>
+        <v>0.7543978232164172</v>
       </c>
       <c r="L11" t="n">
-        <v>13.21099620560328</v>
+        <v>0.5863230154211657</v>
       </c>
     </row>
     <row r="12">
@@ -3167,27 +3167,27 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>183.1296489238739</v>
+        <v>0.03827381134033203</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7337649931248545</v>
+        <v>0.2762198267065196</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.7371529686246404</v>
+        <v>0.2642087227138233</v>
       </c>
       <c r="K12" t="n">
-        <v>17.39419673883764</v>
+        <v>0.7548844799725748</v>
       </c>
       <c r="L12" t="n">
-        <v>13.20418315547962</v>
+        <v>0.5870174989191963</v>
       </c>
     </row>
     <row r="13">
@@ -3205,27 +3205,27 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>206.5332767963409</v>
+        <v>0.1115138530731201</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7338476286732339</v>
+        <v>0.2776218701339047</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'random', 'tol': 0.0001}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.7371529686246404</v>
+        <v>0.2642022548184634</v>
       </c>
       <c r="K13" t="n">
-        <v>17.39419673883764</v>
+        <v>0.7548877978313523</v>
       </c>
       <c r="L13" t="n">
-        <v>13.20418315547962</v>
+        <v>0.5870198778151539</v>
       </c>
     </row>
     <row r="14">
@@ -3243,27 +3243,27 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>199.4946460723877</v>
+        <v>0.08172798156738281</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7327682996256856</v>
+        <v>0.2766903121172088</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.7359707138489484</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="K14" t="n">
-        <v>17.43327136693664</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="L14" t="n">
-        <v>13.23667225137099</v>
+        <v>0.5882492388088877</v>
       </c>
     </row>
     <row r="15">
@@ -3281,27 +3281,27 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>247.0868356227875</v>
+        <v>0.1224496364593506</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7328899937014212</v>
+        <v>0.2779434303402907</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.01, 'l1_ratio': 0.1, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.7359707138489484</v>
+        <v>0.2616875221828251</v>
       </c>
       <c r="K15" t="n">
-        <v>17.43327136693664</v>
+        <v>0.7561766858252632</v>
       </c>
       <c r="L15" t="n">
-        <v>13.23667225137099</v>
+        <v>0.5882492388088877</v>
       </c>
     </row>
     <row r="16">
@@ -3319,27 +3319,27 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>212.3113346099854</v>
+        <v>37.40417456626892</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9086459277482887</v>
+        <v>0.440750682226018</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.9234507192447867</v>
+        <v>0.5417900273946938</v>
       </c>
       <c r="K16" t="n">
-        <v>9.386926059133257</v>
+        <v>0.5957107641453661</v>
       </c>
       <c r="L16" t="n">
-        <v>5.775696783249589</v>
+        <v>0.4244218364523328</v>
       </c>
     </row>
     <row r="17">
@@ -3357,27 +3357,27 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>366.6692905426025</v>
+        <v>70.7239203453064</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9128931506703857</v>
+        <v>0.4777373636797072</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.9234507192447867</v>
+        <v>0.5291968951379508</v>
       </c>
       <c r="K17" t="n">
-        <v>9.386926059133257</v>
+        <v>0.603841334418266</v>
       </c>
       <c r="L17" t="n">
-        <v>5.775696783249589</v>
+        <v>0.4316743421594985</v>
       </c>
     </row>
     <row r="18">
@@ -3395,27 +3395,27 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>15.64453220367432</v>
+        <v>6.800420999526978</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9152503745433745</v>
+        <v>0.4397318959236145</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 3, 'n_estimators': 250}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.9309440281122273</v>
+        <v>0.5523912906646729</v>
       </c>
       <c r="K18" t="n">
-        <v>8.915659227845845</v>
+        <v>0.5887791514396667</v>
       </c>
       <c r="L18" t="n">
-        <v>5.212121269458375</v>
+        <v>0.4128801226615906</v>
       </c>
     </row>
     <row r="19">
@@ -3433,27 +3433,27 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>19.70489597320557</v>
+        <v>7.363279819488525</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9202444657974951</v>
+        <v>0.4839082956314087</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'min_child_weight': 5, 'n_estimators': 250}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0.9309440281122273</v>
+        <v>0.5292840003967285</v>
       </c>
       <c r="K19" t="n">
-        <v>8.915659227845845</v>
+        <v>0.6037854552268982</v>
       </c>
       <c r="L19" t="n">
-        <v>5.212121269458375</v>
+        <v>0.4324872493743896</v>
       </c>
     </row>
     <row r="20">
@@ -3471,27 +3471,27 @@
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>12.90986633300781</v>
+        <v>31.34100079536438</v>
       </c>
       <c r="E20" t="n">
-        <v>0.914363680035399</v>
+        <v>0.4221265380535599</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 100}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.9305517581909237</v>
+        <v>0.5242101900276488</v>
       </c>
       <c r="K20" t="n">
-        <v>8.940945906678417</v>
+        <v>0.607030828128258</v>
       </c>
       <c r="L20" t="n">
-        <v>5.211787970198956</v>
+        <v>0.4489069112717186</v>
       </c>
     </row>
     <row r="21">
@@ -3509,27 +3509,27 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>17.80681109428406</v>
+        <v>33.56432199478149</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9189320204122685</v>
+        <v>0.4569217333243272</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 7, 'n_estimators': 250, 'num_leaves': 50}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.9305517581909237</v>
+        <v>0.5110951993178363</v>
       </c>
       <c r="K21" t="n">
-        <v>8.940945906678417</v>
+        <v>0.6153402589496745</v>
       </c>
       <c r="L21" t="n">
-        <v>5.211787970198956</v>
+        <v>0.4525967415825661</v>
       </c>
     </row>
     <row r="22">
@@ -3547,27 +3547,27 @@
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>149.8692018985748</v>
+        <v>7.273386716842651</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9161002400651177</v>
+        <v>0.4742876429367182</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.9306523814924526</v>
+        <v>0.5669789924496238</v>
       </c>
       <c r="K22" t="n">
-        <v>8.93446630697939</v>
+        <v>0.5791054634132733</v>
       </c>
       <c r="L22" t="n">
-        <v>5.068721809255267</v>
+        <v>0.4152397959183673</v>
       </c>
     </row>
     <row r="23">
@@ -3585,27 +3585,27 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>291.6767017841339</v>
+        <v>13.36617517471313</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9209918367104901</v>
+        <v>0.5047939318645751</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 0.6}</t>
+          <t>{'max_features': 0.8, 'max_samples': 1.0, 'n_estimators': 200}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.9306523814924526</v>
+        <v>0.5669789924496238</v>
       </c>
       <c r="K23" t="n">
-        <v>8.93446630697939</v>
+        <v>0.5791054634132733</v>
       </c>
       <c r="L23" t="n">
-        <v>5.068721809255267</v>
+        <v>0.4152397959183673</v>
       </c>
     </row>
     <row r="24">
@@ -3623,10 +3623,10 @@
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>359.0611598491669</v>
+        <v>11.00290584564209</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9143654286374646</v>
+        <v>0.4623585754058815</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.929790484223216</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="K24" t="n">
-        <v>8.989816532636402</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="L24" t="n">
-        <v>5.108558655758215</v>
+        <v>0.4270981493479949</v>
       </c>
     </row>
     <row r="25">
@@ -3661,27 +3661,27 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>475.1110761165619</v>
+        <v>13.14061999320984</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9195783641133068</v>
+        <v>0.48977812589358</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'cv': 3}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.9298079132741046</v>
+        <v>0.5476623229282194</v>
       </c>
       <c r="K25" t="n">
-        <v>8.988700631940874</v>
+        <v>0.5918812206686007</v>
       </c>
       <c r="L25" t="n">
-        <v>5.102076726523771</v>
+        <v>0.4270981493479949</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,17 +457,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_Accuracy</t>
+          <t>Test_R2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_F1</t>
+          <t>Test_RMSE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_AUC</t>
+          <t>Test_MAE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,30 +491,30 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>18.47461676597595</v>
+        <v>27.10186529159546</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9130844517233803</v>
+        <v>0.9270418266698393</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9266891891891892</v>
+        <v>0.924444145078114</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9193123612301874</v>
+        <v>36.66002480664519</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9787282333085371</v>
+        <v>22.35330437575353</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,30 +526,30 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>34.06773924827576</v>
+        <v>57.25639843940735</v>
       </c>
       <c r="E3" t="n">
-        <v>0.913262433288194</v>
+        <v>0.9276906110886332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9263513513513514</v>
+        <v>0.924444145078114</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9191034179457824</v>
+        <v>36.66002480664519</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9772424591462098</v>
+        <v>22.35330437575353</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,30 +561,30 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4917073249816895</v>
+        <v>10.18944954872131</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8877861070208095</v>
+        <v>0.7359940809611855</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9097972972972973</v>
+        <v>0.745665528057754</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9003132051325229</v>
+        <v>67.26068813890413</v>
       </c>
       <c r="H4" t="n">
-        <v>0.938653824618658</v>
+        <v>43.04966216216216</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,100 +596,100 @@
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9211866855621338</v>
+        <v>18.64355683326721</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8862895625445848</v>
+        <v>0.7328720963192651</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9097972972972973</v>
+        <v>0.745665528057754</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9003132051325229</v>
+        <v>67.26068813890413</v>
       </c>
       <c r="H5" t="n">
-        <v>0.938653824618658</v>
+        <v>43.04966216216216</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>778.4893350601196</v>
+        <v>89.69519591331482</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8729324256296929</v>
+        <v>0.5849552540587489</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8793918918918919</v>
+        <v>0.572752040575516</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8707109028397426</v>
+        <v>87.17635191701446</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9522532575048592</v>
+        <v>54.04575955422463</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>1741.498635292053</v>
+        <v>183.6354990005493</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8727232928382499</v>
+        <v>0.5863769503374059</v>
       </c>
       <c r="F7" t="n">
-        <v>0.879054054054054</v>
+        <v>0.572752040575516</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8701280874728412</v>
+        <v>87.17635191701446</v>
       </c>
       <c r="H7" t="n">
-        <v>0.952378988393764</v>
+        <v>54.04575955422463</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,19 +701,19 @@
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>2.732681512832642</v>
+        <v>1.562232732772827</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8396187077676405</v>
+        <v>0.6182642045857853</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8540540540540541</v>
+        <v>0.610371309728729</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8366571952229587</v>
+        <v>83.24998363278404</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9265321671105993</v>
+        <v>58.25620790008099</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,19 +736,19 @@
         <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>3.780983209609985</v>
+        <v>2.088099718093872</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8401864108199846</v>
+        <v>0.6218922072306379</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8540540540540541</v>
+        <v>0.610371309728729</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8366571952229587</v>
+        <v>83.24998363278404</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9265321671105993</v>
+        <v>58.25620790008099</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -759,278 +759,558 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>1.472885608673096</v>
+        <v>0.4543380737304688</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7659440168113942</v>
+        <v>0.3879676979818973</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7800675675675676</v>
+        <v>0.3785530597229144</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7661955415100101</v>
+        <v>105.1382440718104</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8462693670562074</v>
+        <v>79.46521830767777</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>2.926017999649048</v>
+        <v>0.677628755569458</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7666973234670946</v>
+        <v>0.3876142441170848</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7800675675675676</v>
+        <v>0.3785530597229144</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7661955415100101</v>
+        <v>105.1382440718104</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8462693670562074</v>
+        <v>79.46521830767777</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3184258937835693</v>
+        <v>0.6050491333007812</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7865159669517574</v>
+        <v>0.3879948745862398</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8054054054054054</v>
+        <v>0.3786827871069254</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7834761366055069</v>
+        <v>105.1272696664699</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8639571785088667</v>
+        <v>79.44687800082798</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4198737144470215</v>
+        <v>0.7991194725036621</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7869286649232033</v>
+        <v>0.3876229557024191</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8054054054054054</v>
+        <v>0.3786827871069254</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7834761366055069</v>
+        <v>105.1272696664699</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8639571785088667</v>
+        <v>79.44687800082798</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>22.2285475730896</v>
+        <v>0.8618404865264893</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9122105898905353</v>
+        <v>0.3880221697468028</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9280405405405405</v>
+        <v>0.378311815589937</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9210462943865704</v>
+        <v>105.158649292119</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9785067669714204</v>
+        <v>79.46228555504133</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>47.55513858795166</v>
+        <v>1.384314060211182</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9125947712270616</v>
+        <v>0.3876606679499853</v>
       </c>
       <c r="F15" t="n">
-        <v>0.925</v>
+        <v>0.378311815589937</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9176556212519473</v>
+        <v>105.158649292119</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9791446700101585</v>
+        <v>79.46228555504133</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>186.2187540531158</v>
+        <v>23.98345422744751</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9033234438824053</v>
+        <v>0.9358564357913293</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9172297297297297</v>
+        <v>0.9335005210846987</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9089010530018247</v>
+        <v>34.39282212503215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9752632599844824</v>
+        <v>20.89310493392084</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" t="n">
+        <v>47.19415616989136</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9371377236464621</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9335005210846987</v>
+      </c>
+      <c r="G17" t="n">
+        <v>34.39282212503215</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20.89310493392084</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.200452327728271</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.939555150270462</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9362788796424866</v>
+      </c>
+      <c r="G18" t="n">
+        <v>33.66668319702148</v>
+      </c>
+      <c r="H18" t="n">
+        <v>20.24748420715332</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.034294128417969</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9401066422462463</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.935413122177124</v>
+      </c>
+      <c r="G19" t="n">
+        <v>33.89462280273438</v>
+      </c>
+      <c r="H19" t="n">
+        <v>20.38737678527832</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26.07546329498291</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9384792118700446</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9365992887514033</v>
+      </c>
+      <c r="G20" t="n">
+        <v>33.58193815324221</v>
+      </c>
+      <c r="H20" t="n">
+        <v>20.61395626552133</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="n">
+        <v>34.9989058971405</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9387975117365815</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.938452982378154</v>
+      </c>
+      <c r="G21" t="n">
+        <v>33.0873662758359</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20.64294981605578</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>32.65823650360107</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9315370185332427</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9284488897472609</v>
+      </c>
+      <c r="G22" t="n">
+        <v>35.67523815721992</v>
+      </c>
+      <c r="H22" t="n">
+        <v>21.55962423986486</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" t="n">
+        <v>65.31638360023499</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9320700644384793</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.928334448890752</v>
+      </c>
+      <c r="G23" t="n">
+        <v>35.70375674765465</v>
+      </c>
+      <c r="H23" t="n">
+        <v>21.68945104166667</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Stacking</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D17" t="n">
-        <v>169.5387573242188</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9060012070323756</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9172297297297297</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9089010530018247</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.9752632599844824</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>67.2276451587677</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9317507467241954</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9288018973917292</v>
+      </c>
+      <c r="G24" t="n">
+        <v>35.58712489594088</v>
+      </c>
+      <c r="H24" t="n">
+        <v>21.54101354188551</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" t="n">
+        <v>121.8825795650482</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9319565654152878</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9288018973917292</v>
+      </c>
+      <c r="G25" t="n">
+        <v>35.58712489594088</v>
+      </c>
+      <c r="H25" t="n">
+        <v>21.54101354188551</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>
@@ -1047,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1078,17 +1358,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_Accuracy</t>
+          <t>Test_R2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_F1</t>
+          <t>Test_RMSE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_AUC</t>
+          <t>Test_MAE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1100,7 +1380,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1112,30 +1392,30 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>18.47461676597595</v>
+        <v>27.10186529159546</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9130844517233803</v>
+        <v>0.9270418266698393</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9266891891891892</v>
+        <v>0.924444145078114</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9193123612301874</v>
+        <v>36.66002480664519</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9787282333085371</v>
+        <v>22.35330437575353</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1147,30 +1427,30 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>34.06773924827576</v>
+        <v>57.25639843940735</v>
       </c>
       <c r="E3" t="n">
-        <v>0.913262433288194</v>
+        <v>0.9276906110886332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9263513513513514</v>
+        <v>0.924444145078114</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9191034179457824</v>
+        <v>36.66002480664519</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9772424591462098</v>
+        <v>22.35330437575353</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1182,30 +1462,30 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4917073249816895</v>
+        <v>10.18944954872131</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8877861070208095</v>
+        <v>0.7359940809611855</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9097972972972973</v>
+        <v>0.745665528057754</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9003132051325229</v>
+        <v>67.26068813890413</v>
       </c>
       <c r="H4" t="n">
-        <v>0.938653824618658</v>
+        <v>43.04966216216216</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1217,100 +1497,100 @@
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9211866855621338</v>
+        <v>18.64355683326721</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8862895625445848</v>
+        <v>0.7328720963192651</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9097972972972973</v>
+        <v>0.745665528057754</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9003132051325229</v>
+        <v>67.26068813890413</v>
       </c>
       <c r="H5" t="n">
-        <v>0.938653824618658</v>
+        <v>43.04966216216216</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>778.4893350601196</v>
+        <v>89.69519591331482</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8729324256296929</v>
+        <v>0.5849552540587489</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8793918918918919</v>
+        <v>0.572752040575516</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8707109028397426</v>
+        <v>87.17635191701446</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9522532575048592</v>
+        <v>54.04575955422463</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>1741.498635292053</v>
+        <v>183.6354990005493</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8727232928382499</v>
+        <v>0.5863769503374059</v>
       </c>
       <c r="F7" t="n">
-        <v>0.879054054054054</v>
+        <v>0.572752040575516</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8701280874728412</v>
+        <v>87.17635191701446</v>
       </c>
       <c r="H7" t="n">
-        <v>0.952378988393764</v>
+        <v>54.04575955422463</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'epsilon': 0.5, 'C': 100}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1322,19 +1602,19 @@
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>2.732681512832642</v>
+        <v>1.562232732772827</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8396187077676405</v>
+        <v>0.6182642045857853</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8540540540540541</v>
+        <v>0.610371309728729</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8366571952229587</v>
+        <v>83.24998363278404</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9265321671105993</v>
+        <v>58.25620790008099</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1345,7 +1625,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1357,19 +1637,19 @@
         <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>3.780983209609985</v>
+        <v>2.088099718093872</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8401864108199846</v>
+        <v>0.6218922072306379</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8540540540540541</v>
+        <v>0.610371309728729</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8366571952229587</v>
+        <v>83.24998363278404</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9265321671105993</v>
+        <v>58.25620790008099</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1380,278 +1660,558 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>1.472885608673096</v>
+        <v>0.4543380737304688</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7659440168113942</v>
+        <v>0.3879676979818973</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7800675675675676</v>
+        <v>0.3785530597229144</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7661955415100101</v>
+        <v>105.1382440718104</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8462693670562074</v>
+        <v>79.46521830767777</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>2.926017999649048</v>
+        <v>0.677628755569458</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7666973234670946</v>
+        <v>0.3876142441170848</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7800675675675676</v>
+        <v>0.3785530597229144</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7661955415100101</v>
+        <v>105.1382440718104</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8462693670562074</v>
+        <v>79.46521830767777</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'saga', 'max_iter': 10000, 'alpha': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3184258937835693</v>
+        <v>0.6050491333007812</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7865159669517574</v>
+        <v>0.3879948745862398</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8054054054054054</v>
+        <v>0.3786827871069254</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7834761366055069</v>
+        <v>105.1272696664699</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8639571785088667</v>
+        <v>79.44687800082798</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4198737144470215</v>
+        <v>0.7991194725036621</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7869286649232033</v>
+        <v>0.3876229557024191</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8054054054054054</v>
+        <v>0.3786827871069254</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7834761366055069</v>
+        <v>105.1272696664699</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8639571785088667</v>
+        <v>79.44687800082798</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>22.2285475730896</v>
+        <v>0.8618404865264893</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9122105898905353</v>
+        <v>0.3880221697468028</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9280405405405405</v>
+        <v>0.378311815589937</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9210462943865704</v>
+        <v>105.158649292119</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9785067669714204</v>
+        <v>79.46228555504133</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>47.55513858795166</v>
+        <v>1.384314060211182</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9125947712270616</v>
+        <v>0.3876606679499853</v>
       </c>
       <c r="F15" t="n">
-        <v>0.925</v>
+        <v>0.378311815589937</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9176556212519473</v>
+        <v>105.158649292119</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9791446700101585</v>
+        <v>79.46228555504133</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.9, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>186.2187540531158</v>
+        <v>23.98345422744751</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9033234438824053</v>
+        <v>0.9358564357913293</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9172297297297297</v>
+        <v>0.9335005210846987</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9089010530018247</v>
+        <v>34.39282212503215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9752632599844824</v>
+        <v>20.89310493392084</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 5}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" t="n">
+        <v>47.19415616989136</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9371377236464621</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9335005210846987</v>
+      </c>
+      <c r="G17" t="n">
+        <v>34.39282212503215</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20.89310493392084</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.200452327728271</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.939555150270462</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9362788796424866</v>
+      </c>
+      <c r="G18" t="n">
+        <v>33.66668319702148</v>
+      </c>
+      <c r="H18" t="n">
+        <v>20.24748420715332</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.034294128417969</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9401066422462463</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.935413122177124</v>
+      </c>
+      <c r="G19" t="n">
+        <v>33.89462280273438</v>
+      </c>
+      <c r="H19" t="n">
+        <v>20.38737678527832</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26.07546329498291</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9384792118700446</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9365992887514033</v>
+      </c>
+      <c r="G20" t="n">
+        <v>33.58193815324221</v>
+      </c>
+      <c r="H20" t="n">
+        <v>20.61395626552133</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="n">
+        <v>34.9989058971405</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9387975117365815</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.938452982378154</v>
+      </c>
+      <c r="G21" t="n">
+        <v>33.0873662758359</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20.64294981605578</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>32.65823650360107</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9315370185332427</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9284488897472609</v>
+      </c>
+      <c r="G22" t="n">
+        <v>35.67523815721992</v>
+      </c>
+      <c r="H22" t="n">
+        <v>21.55962423986486</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" t="n">
+        <v>65.31638360023499</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9320700644384793</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.928334448890752</v>
+      </c>
+      <c r="G23" t="n">
+        <v>35.70375674765465</v>
+      </c>
+      <c r="H23" t="n">
+        <v>21.68945104166667</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Stacking</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D17" t="n">
-        <v>169.5387573242188</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9060012070323756</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9172297297297297</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9089010530018247</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.9752632599844824</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>67.2276451587677</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9317507467241954</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9288018973917292</v>
+      </c>
+      <c r="G24" t="n">
+        <v>35.58712489594088</v>
+      </c>
+      <c r="H24" t="n">
+        <v>21.54101354188551</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" t="n">
+        <v>121.8825795650482</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9319565654152878</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9288018973917292</v>
+      </c>
+      <c r="G25" t="n">
+        <v>35.58712489594088</v>
+      </c>
+      <c r="H25" t="n">
+        <v>21.54101354188551</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>{'cv': 5}</t>
         </is>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,58 +458,2318 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Test_Accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test_F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test_AUC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Params</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Test_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Test_RMSE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Test_MAE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Best_Params</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.529591083526611</v>
+        <v>4.141305446624756</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9338110486666361</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.935413122177124</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>33.89462280273438</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>20.38737678527832</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.670144319534302</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.750752210617065</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1057054996490479</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9983593504958139</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.09599804878234863</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.174518346786499</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1679651737213135</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9967294558426634</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9888513513513514</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1711742877960205</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9967253463310086</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9888513513513514</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3445255756378174</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9967071524966261</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1213340759277344</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9885883726830831</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.095428466796875</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9918380364236208</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1554012298583984</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9918326672831579</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9936655405405406</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3569977283477783</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9967294558426634</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6214008331298828</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.419265270233154</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'solver': 'saga', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 10}</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.09097671508789062</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9804397703729418</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.04074692726135254</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9804280526546304</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.06908965110778809</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9804441893856517</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9232625961303711</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9983593504958139</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.43821907043457</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.016119718551636</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.293261289596558</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9950995611895129</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.739360809326172</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9967253463310086</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.597257137298584</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9967368878519636</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.704530954360962</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.991165133416164</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.991777204955937</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.786976524979942</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.198261096007184</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.037497520446777</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9915514893368013</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.991777204955937</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.786976524979942</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.198261096007184</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6.253591299057007</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9918184774008527</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.991777204955937</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.786976524979942</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.198261096007184</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.08736729621887207</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9884016004359877</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.9906224468993026</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.908331770496365</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.312303784373733</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.1213846206665039</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9891276364518466</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9906224468993026</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.908331770496365</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.312303784373733</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.2279641628265381</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9888184370756603</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.9879219094649494</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.165749660258334</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.344318181818182</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.4465219974517822</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9493173645748553</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.933262226803274</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.043767213821411</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9593934708973952</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.933262226803274</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.757725715637207</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9663252049059585</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.933262226803274</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08384418487548828</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9753267773098955</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.388601264472551</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.1074974536895752</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9809646707133171</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.388601264472551</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.1651961803436279</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9829335526451433</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.388601264472551</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08175039291381836</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.909534101018917</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9133644072758389</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5.800391268359031</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4.193312097150674</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.1122102737426758</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9087605182651902</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.9133644072815305</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5.8003912681685</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4.193312096705474</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.2052247524261475</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.909045741479711</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9128511910101398</v>
+      </c>
+      <c r="K40" t="n">
+        <v>5.817546224259836</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4.201707106444708</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.1089096069335938</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9095314697018355</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.9133925467063826</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5.799449201953228</v>
+      </c>
+      <c r="L41" t="n">
+        <v>4.192818052928173</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.0565636157989502</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9087547686315594</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.9133935968581072</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5.799414041468699</v>
+      </c>
+      <c r="L42" t="n">
+        <v>4.192899764404125</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.09963870048522949</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9090587832930842</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.913146287430656</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.807688414253744</v>
+      </c>
+      <c r="L43" t="n">
+        <v>4.197174702000158</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.1181185245513916</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.909533215133945</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.9133122243111836</v>
+      </c>
+      <c r="K44" t="n">
+        <v>5.802137871795419</v>
+      </c>
+      <c r="L44" t="n">
+        <v>4.193872563312008</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.09784483909606934</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9087632939524625</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.9133122243111836</v>
+      </c>
+      <c r="K45" t="n">
+        <v>5.802137871795419</v>
+      </c>
+      <c r="L45" t="n">
+        <v>4.193872563312008</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.2399892807006836</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9090849528753845</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9131240810741543</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5.808430808292843</v>
+      </c>
+      <c r="L46" t="n">
+        <v>4.197240504719623</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.208387851715088</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9962821294270688</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.9978246390639918</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.9191254197681974</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.6382677938619158</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.340327739715576</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9974229884587255</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.9971987634537949</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.042999274810321</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.634718037848133</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4.603539228439331</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9978558588089712</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.9971987634537949</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.042999274810321</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.634718037848133</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3.02683162689209</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9965485258873344</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.3923439979553223</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9974346204770498</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>10</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.7825050354003906</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9977164520836048</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>30.5763635635376</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9959430744288776</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.43288707733154</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9967680026539419</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>10</v>
+      </c>
+      <c r="D55" t="n">
+        <v>49.61752033233643</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9969284949233164</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.6965103149414062</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9914238516975447</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.9920354917748463</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1.758687177428648</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.129233766233765</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.195473909378052</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9918212871921988</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.109712337662338</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2.187191247940063</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9918118579963269</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.109712337662338</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.215555906295776</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9911019302061744</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0.9923490394853252</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1.723721485354504</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.110294250898904</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.493859052658081</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.9916725619279564</v>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.068923415563526</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>10</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2.197186708450317</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.991650272801923</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.068923415563526</v>
       </c>
     </row>
   </sheetData>
@@ -522,7 +2783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,58 +2814,2394 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Test_Accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test_F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test_AUC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Params</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Test_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Test_RMSE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Test_MAE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Best_Params</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.529591083526611</v>
+        <v>4.141305446624756</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9338110486666361</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.935413122177124</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>33.89462280273438</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>20.38737678527832</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
-        </is>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.670144319534302</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.750752210617065</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1057054996490479</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9983593504958139</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.09599804878234863</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.174518346786499</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9999155405405405</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1679651737213135</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9967294558426634</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9888513513513514</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1711742877960205</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9967253463310086</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9888513513513514</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3445255756378174</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9967071524966261</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1213340759277344</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9885883726830831</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.095428466796875</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9918380364236208</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1554012298583984</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9918326672831579</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9936655405405406</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'euclidean'}</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3569977283477783</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9967294558426634</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6214008331298828</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.419265270233154</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'solver': 'saga', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 10}</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.09097671508789062</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9804397703729418</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.04074692726135254</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9804280526546304</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.06908965110778809</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9804441893856517</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.987012987012987</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.986977845425334</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9863175675675676</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'var_smoothing': 1e-11, 'priors': None}</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9232625961303711</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9983593504958139</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.43821907043457</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9983552409841592</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.016119718551636</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 1.0, 'max_features': 0.6}</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.293261289596558</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9950995611895129</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.739360809326172</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9967253463310086</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.597257137298584</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9967368878519636</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.9998310810810811</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CV_Folds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tuning_Time_sec</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Best_CV_Score</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Test_Accuracy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Test_F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Test_AUC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Params</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Test_R2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Test_RMSE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Test_MAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.704530954360962</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.991165133416164</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.991777204955937</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.786976524979942</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.198261096007184</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.037497520446777</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9915514893368013</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.991777204955937</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.786976524979942</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.198261096007184</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.253591299057007</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9918184774008527</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': 7}</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.991777204955937</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.786976524979942</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.198261096007184</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08736729621887207</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9884016004359877</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9906224468993026</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.908331770496365</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.312303784373733</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1213846206665039</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9891276364518466</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9906224468993026</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.908331770496365</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.312303784373733</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2279641628265381</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9888184370756603</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9879219094649494</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.165749660258334</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.344318181818182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4465219974517822</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9493173645748553</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.933262226803274</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.043767213821411</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9593934708973952</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.933262226803274</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.757725715637207</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9663252049059585</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.2, 'C': 100}</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9776640607919219</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.945175805228017</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.933262226803274</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.08384418487548828</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9753267773098955</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.388601264472551</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1074974536895752</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9809646707133171</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.388601264472551</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1651961803436279</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9829335526451433</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.388601264472551</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.08175039291381836</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.909534101018917</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'solver': 'cholesky', 'max_iter': 10000, 'alpha': 0.1}</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9133644072758389</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.800391268359031</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.193312097150674</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1122102737426758</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9087605182651902</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 0.1}</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9133644072815305</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.8003912681685</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.193312096705474</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.2052247524261475</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.909045741479711</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'solver': 'lsqr', 'max_iter': 10000, 'alpha': 1.0}</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9128511910101398</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.817546224259836</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4.201707106444708</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1089096069335938</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9095314697018355</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9133925467063826</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.799449201953228</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.192818052928173</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0565636157989502</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9087547686315594</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9133935968581072</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.799414041468699</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4.192899764404125</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.09963870048522949</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9090587832930842</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.913146287430656</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.807688414253744</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4.197174702000158</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1181185245513916</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.909533215133945</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.9133122243111836</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.802137871795419</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4.193872563312008</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.09784483909606934</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9087632939524625</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9133122243111836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.802137871795419</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4.193872563312008</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.2399892807006836</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9090849528753845</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'l1_ratio': 0.1, 'alpha': 0.001}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9131240810741543</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.808430808292843</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4.197240504719623</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.208387851715088</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9962821294270688</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9978246390639918</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.9191254197681974</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.6382677938619158</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.340327739715576</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9974229884587255</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9971987634537949</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.042999274810321</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.634718037848133</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.603539228439331</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9978558588089712</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_samples_split': 2, 'max_depth': 5, 'learning_rate': 0.5}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9971987634537949</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.042999274810321</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.634718037848133</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.02683162689209</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9965485258873344</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.3923439979553223</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9974346204770498</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.7825050354003906</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9977164520836048</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 250, 'min_child_weight': 5, 'max_depth': 5, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9979915184339837</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.883167420157519</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.5851734726150313</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>30.5763635635376</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9959430744288776</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.43288707733154</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9967680026539419</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>49.61752033233643</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9969284949233164</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'num_leaves': 50, 'n_estimators': 250, 'max_depth': 7, 'learning_rate': 0.2}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.9971905430163311</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.044528533262776</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.7230709546390158</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.6965103149414062</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9914238516975447</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9920354917748463</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.758687177428648</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.129233766233765</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.195473909378052</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9918212871921988</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.109712337662338</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bagging</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.187191247940063</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9918118579963269</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_samples': 0.8, 'max_features': 1.0}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.9923259444363434</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.726321122047857</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.109712337662338</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.215555906295776</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9911019302061744</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'cv': 3}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.9923490394853252</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.723721485354504</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.110294250898904</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.493859052658081</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9916725619279564</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.068923415563526</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.197186708450317</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.991650272801923</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'cv': 5}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9927500166340855</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.677944607223844</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.068923415563526</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cv_experiment_all_models_kmeans.xlsx
+++ b/output/reports/cv_experiment_all_models_kmeans.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,17 +457,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_Accuracy</t>
+          <t>Test_R2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_F1</t>
+          <t>Test_RMSE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_AUC</t>
+          <t>Test_MAE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,30 +491,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>21.03134727478027</v>
+        <v>142.4573543071747</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9999678077497777</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9999805234233666</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.04185051084179357</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.01120138434431437</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,30 +526,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>35.0576798915863</v>
+        <v>209.7782816886902</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.9999725193608008</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9999805234233666</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.04185051084179357</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.01120138434431437</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,30 +561,30 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5360722541809082</v>
+        <v>89.27391028404236</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.9981248275564775</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.9974305173225426</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.4806924474102501</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.1766567471493122</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,443 +596,443 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6800587177276611</v>
+        <v>155.4993200302124</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.9980554539914183</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9979896144261586</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.4251910664182704</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.2249787215400599</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>158.3006844520569</v>
+        <v>11.81552910804749</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9996620109119062</v>
+        <v>0.989567395589308</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9999436746648642</v>
+        <v>0.9913454450269565</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9999436745145818</v>
+        <v>0.8821995297482219</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9999999365489514</v>
+        <v>0.6634157895241657</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>335.9704122543335</v>
+        <v>15.45020747184753</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9997183417435679</v>
+        <v>0.9904880707374442</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999436746648642</v>
+        <v>0.9913454450269565</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9999436745145818</v>
+        <v>0.8821995297482219</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9999999365489514</v>
+        <v>0.6634157895241657</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>11.76212882995605</v>
+        <v>0.371823787689209</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9724697886854861</v>
+        <v>0.9913128938769532</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9744846231835079</v>
+        <v>0.9911884119642234</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9744832339482654</v>
+        <v>0.8901671098299406</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9975799262404401</v>
+        <v>0.7027435502511595</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>13.78122329711914</v>
+        <v>0.4821679592132568</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9734836673129882</v>
+        <v>0.9913120707267371</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9740340205024219</v>
+        <v>0.9911884119642234</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9740320919679999</v>
+        <v>0.8901671098299406</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9978872640851937</v>
+        <v>0.7027435502511595</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>40.58893442153931</v>
+        <v>108.4727911949158</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9999436686941007</v>
+        <v>0.9999596685562091</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9998873493297286</v>
+        <v>0.9999751355245586</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9998873490080773</v>
+        <v>0.04728616597242019</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9999999619293707</v>
+        <v>0.0236837833684335</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>88.34208679199219</v>
+        <v>178.9059579372406</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9999155034749145</v>
+        <v>0.9999660970286026</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9998873493297286</v>
+        <v>0.9999751355245586</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9998873490080773</v>
+        <v>0.04728616597242019</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9999999619293707</v>
+        <v>0.0236837833684335</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3330526351928711</v>
+        <v>6.135040760040283</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7986222110648104</v>
+        <v>0.99982357862805</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8060155457924975</v>
+        <v>0.9998209317977906</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7984304915439394</v>
+        <v>0.1268976817616241</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9849637004164317</v>
+        <v>0.05364276771399302</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3865957260131836</v>
+        <v>7.205111026763916</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7986221448254553</v>
+        <v>0.9998247893839546</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8060155457924975</v>
+        <v>0.9998267509010639</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7984304915439394</v>
+        <v>0.1248187829825181</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9849637004164317</v>
+        <v>0.05288277202897447</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>11.07282543182373</v>
+        <v>11.67587733268738</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.9998235129695029</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.9997970644558954</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.1350900964123299</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.0563297772888775</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>21.25451612472534</v>
+        <v>14.30642175674438</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.9998204407468496</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.9997970644558954</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.1350900964123299</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.0563297772888775</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>248.3944759368896</v>
+        <v>37.30611491203308</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.9999687479736658</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.9999810355680122</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0.0412966070481332</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0.0109924492759083</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>461.5363669395447</v>
+        <v>69.11179947853088</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.9999736474855199</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.9999810355680122</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.0412966070481332</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0.0109924492759083</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
@@ -1078,17 +1078,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Test_Accuracy</t>
+          <t>Test_R2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Test_F1</t>
+          <t>Test_RMSE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Test_AUC</t>
+          <t>Test_MAE</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1112,30 +1112,30 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>21.03134727478027</v>
+        <v>142.4573543071747</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9999678077497777</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9999805234233666</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.04185051084179357</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.01120138434431437</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1147,30 +1147,30 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>35.0576798915863</v>
+        <v>209.7782816886902</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.9999725193608008</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9999805234233666</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.04185051084179357</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.01120138434431437</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_depth': None}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1182,30 +1182,30 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5360722541809082</v>
+        <v>89.27391028404236</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.9981248275564775</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.9974305173225426</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.4806924474102501</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.1766567471493122</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1217,443 +1217,443 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6800587177276611</v>
+        <v>155.4993200302124</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.9980554539914183</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9979896144261586</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.4251910664182704</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.2249787215400599</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 5, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>158.3006844520569</v>
+        <v>11.81552910804749</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9996620109119062</v>
+        <v>0.989567395589308</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9999436746648642</v>
+        <v>0.9913454450269565</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9999436745145818</v>
+        <v>0.8821995297482219</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9999999365489514</v>
+        <v>0.6634157895241657</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>335.9704122543335</v>
+        <v>15.45020747184753</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9997183417435679</v>
+        <v>0.9904880707374442</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999436746648642</v>
+        <v>0.9913454450269565</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9999436745145818</v>
+        <v>0.8821995297482219</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9999999365489514</v>
+        <v>0.6634157895241657</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>11.76212882995605</v>
+        <v>0.371823787689209</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9724697886854861</v>
+        <v>0.9913128938769532</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9744846231835079</v>
+        <v>0.9911884119642234</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9744832339482654</v>
+        <v>0.8901671098299406</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9975799262404401</v>
+        <v>0.7027435502511595</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>13.78122329711914</v>
+        <v>0.4821679592132568</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9734836673129882</v>
+        <v>0.9913120707267371</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9740340205024219</v>
+        <v>0.9911884119642234</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9740320919679999</v>
+        <v>0.8901671098299406</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9978872640851937</v>
+        <v>0.7027435502511595</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'l1_ratio': 0.7, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>40.58893442153931</v>
+        <v>108.4727911949158</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9999436686941007</v>
+        <v>0.9999596685562091</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9998873493297286</v>
+        <v>0.9999751355245586</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9998873490080773</v>
+        <v>0.04728616597242019</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9999999619293707</v>
+        <v>0.0236837833684335</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>88.34208679199219</v>
+        <v>178.9059579372406</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9999155034749145</v>
+        <v>0.9999660970286026</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9998873493297286</v>
+        <v>0.9999751355245586</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9998873490080773</v>
+        <v>0.04728616597242019</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9999999619293707</v>
+        <v>0.0236837833684335</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': None, 'max_iter': 5000, 'class_weight': None}</t>
+          <t>{'n_estimators': 250, 'min_samples_split': 10, 'max_depth': 7, 'learning_rate': 0.3}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3330526351928711</v>
+        <v>6.135040760040283</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7986222110648104</v>
+        <v>0.99982357862805</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8060155457924975</v>
+        <v>0.9998209317977906</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7984304915439394</v>
+        <v>0.1268976817616241</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9849637004164317</v>
+        <v>0.05364276771399302</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'n_estimators': 200, 'min_child_weight': 1, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3865957260131836</v>
+        <v>7.205111026763916</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7986221448254553</v>
+        <v>0.9998247893839546</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8060155457924975</v>
+        <v>0.9998267509010639</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7984304915439394</v>
+        <v>0.1248187829825181</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9849637004164317</v>
+        <v>0.05288277202897447</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'var_smoothing': 0.0001, 'priors': None}</t>
+          <t>{'n_estimators': 250, 'min_child_weight': 3, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>11.07282543182373</v>
+        <v>11.67587733268738</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.9998235129695029</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.9997970644558954</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.1350900964123299</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.0563297772888775</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bagging</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>21.25451612472534</v>
+        <v>14.30642175674438</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.9998204407468496</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.9997970644558954</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.1350900964123299</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.0563297772888775</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'max_samples': 0.8, 'max_features': 0.8}</t>
+          <t>{'num_leaves': 50, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>248.3944759368896</v>
+        <v>37.30611491203308</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.9999687479736658</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.9999810355680122</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0.0412966070481332</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0.0109924492759083</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stacking</t>
+          <t>Bagging</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>461.5363669395447</v>
+        <v>69.11179947853088</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.9999736474855199</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.9999810355680122</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.0412966070481332</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0.0109924492759083</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'cv': 3}</t>
+          <t>{'n_estimators': 200, 'max_samples': 1.0, 'max_features': 1.0}</t>
         </is>
       </c>
     </row>
